--- a/process_sim/results/stream_results.xlsx
+++ b/process_sim/results/stream_results.xlsx
@@ -428,12 +428,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
@@ -516,7 +516,7 @@
         <v>8.804575</v>
       </c>
       <c r="F3" t="n">
-        <v>1845.390794</v>
+        <v>1845.390781</v>
       </c>
     </row>
     <row r="4">
@@ -540,7 +540,7 @@
         <v>22.011438</v>
       </c>
       <c r="F4" t="n">
-        <v>396.714518</v>
+        <v>396.714515</v>
       </c>
     </row>
     <row r="5">
@@ -564,7 +564,7 @@
         <v>22.824394</v>
       </c>
       <c r="F5" t="n">
-        <v>716.296462</v>
+        <v>716.296459</v>
       </c>
     </row>
     <row r="6">
@@ -588,7 +588,7 @@
         <v>7.991619</v>
       </c>
       <c r="F6" t="n">
-        <v>1525.808849</v>
+        <v>1525.808836</v>
       </c>
     </row>
     <row r="7">
@@ -612,7 +612,7 @@
         <v>7.998166</v>
       </c>
       <c r="F7" t="n">
-        <v>1527.552435</v>
+        <v>1527.552422</v>
       </c>
     </row>
     <row r="8">
@@ -636,7 +636,7 @@
         <v>0.399908</v>
       </c>
       <c r="F8" t="n">
-        <v>76.377622</v>
+        <v>76.377621</v>
       </c>
     </row>
     <row r="9">
@@ -660,7 +660,7 @@
         <v>7.598258</v>
       </c>
       <c r="F9" t="n">
-        <v>1451.174813</v>
+        <v>1451.174801</v>
       </c>
     </row>
     <row r="10">
@@ -684,7 +684,7 @@
         <v>0.400041</v>
       </c>
       <c r="F10" t="n">
-        <v>76.413014</v>
+        <v>76.413056</v>
       </c>
     </row>
     <row r="11">
@@ -708,7 +708,7 @@
         <v>9.467428</v>
       </c>
       <c r="F11" t="n">
-        <v>200.345321</v>
+        <v>200.345319</v>
       </c>
     </row>
     <row r="12">
@@ -756,7 +756,7 @@
         <v>9.006129</v>
       </c>
       <c r="F13" t="n">
-        <v>179.746303</v>
+        <v>179.746302</v>
       </c>
     </row>
     <row r="14">
@@ -780,7 +780,7 @@
         <v>9.632023</v>
       </c>
       <c r="F14" t="n">
-        <v>305.650226</v>
+        <v>305.650224</v>
       </c>
     </row>
     <row r="15">
@@ -996,7 +996,7 @@
         <v>6.803605</v>
       </c>
       <c r="F23" t="n">
-        <v>122.566945</v>
+        <v>122.566944</v>
       </c>
     </row>
     <row r="24">
@@ -1260,7 +1260,7 @@
         <v>9.632023</v>
       </c>
       <c r="F34" t="n">
-        <v>305.650226</v>
+        <v>305.650224</v>
       </c>
     </row>
     <row r="35">
@@ -1284,7 +1284,7 @@
         <v>9.632023</v>
       </c>
       <c r="F35" t="n">
-        <v>305.650226</v>
+        <v>305.650224</v>
       </c>
     </row>
     <row r="36">
@@ -1308,7 +1308,7 @@
         <v>9.632023</v>
       </c>
       <c r="F36" t="n">
-        <v>305.650226</v>
+        <v>305.650224</v>
       </c>
     </row>
     <row r="37">
@@ -1356,7 +1356,7 @@
         <v>3.391888</v>
       </c>
       <c r="F38" t="n">
-        <v>61.10487</v>
+        <v>61.104868</v>
       </c>
     </row>
     <row r="39">
@@ -1404,7 +1404,7 @@
         <v>15.270966</v>
       </c>
       <c r="F40" t="n">
-        <v>378.78361</v>
+        <v>378.783609</v>
       </c>
     </row>
     <row r="41">
@@ -1428,7 +1428,7 @@
         <v>9.475647</v>
       </c>
       <c r="F41" t="n">
-        <v>182.599848</v>
+        <v>182.599846</v>
       </c>
     </row>
     <row r="42">
@@ -1500,7 +1500,7 @@
         <v>30.100369</v>
       </c>
       <c r="F44" t="n">
-        <v>657.6122</v>
+        <v>657.612198</v>
       </c>
     </row>
     <row r="45">
@@ -1524,7 +1524,7 @@
         <v>30.100369</v>
       </c>
       <c r="F45" t="n">
-        <v>657.6122</v>
+        <v>657.612198</v>
       </c>
     </row>
     <row r="46">
@@ -1548,7 +1548,7 @@
         <v>24.386271</v>
       </c>
       <c r="F46" t="n">
-        <v>439.318677</v>
+        <v>439.318676</v>
       </c>
     </row>
     <row r="47">
@@ -1602,38 +1602,38 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>F-4</t>
+          <t>F-3P</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>373.15</v>
       </c>
       <c r="C49" t="n">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.125091</v>
+        <v>0.773725</v>
       </c>
       <c r="F49" t="n">
-        <v>11.411308</v>
+        <v>29.893158</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>F-40</t>
+          <t>F-3PT</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>298.15</v>
       </c>
       <c r="C50" t="n">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1641,44 +1641,44 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2.135616</v>
+        <v>0.773725</v>
       </c>
       <c r="F50" t="n">
-        <v>61.613895</v>
+        <v>29.893158</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>F-41</t>
+          <t>F-4</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>298.15</v>
+        <v>373.15</v>
       </c>
       <c r="C51" t="n">
         <v>100000</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>8.704661</v>
+        <v>0.125091</v>
       </c>
       <c r="F51" t="n">
-        <v>287.690816</v>
+        <v>11.411308</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>F-41T</t>
+          <t>F-40</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>313.15</v>
+        <v>298.15</v>
       </c>
       <c r="C52" t="n">
         <v>100000</v>
@@ -1689,20 +1689,20 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>8.704661</v>
+        <v>2.135616</v>
       </c>
       <c r="F52" t="n">
-        <v>287.690816</v>
+        <v>61.613895</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>F-42</t>
+          <t>F-41</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>313.15</v>
+        <v>298.15</v>
       </c>
       <c r="C53" t="n">
         <v>100000</v>
@@ -1713,20 +1713,20 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5.636223</v>
+        <v>8.704661</v>
       </c>
       <c r="F53" t="n">
-        <v>163.522616</v>
+        <v>287.690816</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>F-43</t>
+          <t>F-41T</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>298.15</v>
+        <v>313.15</v>
       </c>
       <c r="C54" t="n">
         <v>100000</v>
@@ -1737,20 +1737,20 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.099817</v>
+        <v>8.704661</v>
       </c>
       <c r="F54" t="n">
-        <v>1.699984</v>
+        <v>287.690816</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>F-44</t>
+          <t>F-42</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>673.15</v>
+        <v>313.15</v>
       </c>
       <c r="C55" t="n">
         <v>100000</v>
@@ -1761,64 +1761,64 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5.766786</v>
+        <v>5.636223</v>
       </c>
       <c r="F55" t="n">
-        <v>165.2226</v>
+        <v>163.522616</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>F-45</t>
+          <t>F-43</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>323.15</v>
+        <v>298.15</v>
       </c>
       <c r="C56" t="n">
         <v>100000</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.130196</v>
+        <v>0.099817</v>
       </c>
       <c r="F56" t="n">
-        <v>2.345483</v>
+        <v>1.699984</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>F-45R</t>
+          <t>F-44</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>323.15</v>
+        <v>673.15</v>
       </c>
       <c r="C57" t="n">
         <v>100000</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.123686</v>
+        <v>5.766786</v>
       </c>
       <c r="F57" t="n">
-        <v>2.228209</v>
+        <v>165.2226</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>F-46</t>
+          <t>F-45</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1829,24 +1829,24 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5.63659</v>
+        <v>0.130196</v>
       </c>
       <c r="F58" t="n">
-        <v>162.877116</v>
+        <v>2.345483</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>F-47</t>
+          <t>F-45R</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>298.15</v>
+        <v>323.15</v>
       </c>
       <c r="C59" t="n">
         <v>100000</v>
@@ -1857,16 +1857,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>38.159711</v>
+        <v>0.123686</v>
       </c>
       <c r="F59" t="n">
-        <v>687.447198</v>
+        <v>2.228209</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>F-47T</t>
+          <t>F-46</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1877,24 +1877,24 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>38.159711</v>
+        <v>5.63659</v>
       </c>
       <c r="F60" t="n">
-        <v>687.447198</v>
+        <v>162.877116</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>F-48</t>
+          <t>F-47</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>323.15</v>
+        <v>298.15</v>
       </c>
       <c r="C61" t="n">
         <v>100000</v>
@@ -1905,16 +1905,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>38.172601</v>
+        <v>38.159711</v>
       </c>
       <c r="F61" t="n">
-        <v>687.6667169999999</v>
+        <v>687.447198</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>F-49</t>
+          <t>F-47T</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1925,48 +1925,48 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5.6237</v>
+        <v>38.159711</v>
       </c>
       <c r="F62" t="n">
-        <v>162.657597</v>
+        <v>687.447198</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>F-49A</t>
+          <t>F-48</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>298.15</v>
+        <v>323.15</v>
       </c>
       <c r="C63" t="n">
         <v>100000</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5.6237</v>
+        <v>38.172601</v>
       </c>
       <c r="F63" t="n">
-        <v>162.657597</v>
+        <v>687.6667169999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>F-49B</t>
+          <t>F-49</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>298.15</v>
+        <v>323.15</v>
       </c>
       <c r="C64" t="n">
         <v>100000</v>
@@ -1977,40 +1977,40 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>5.6237</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>162.657597</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>F-5</t>
+          <t>F-49A</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>373.15</v>
+        <v>298.15</v>
       </c>
       <c r="C65" t="n">
         <v>100000</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>10.283591</v>
+        <v>5.6237</v>
       </c>
       <c r="F65" t="n">
-        <v>522.665717</v>
+        <v>162.657597</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>F-50A</t>
+          <t>F-49B</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -2025,40 +2025,40 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5.623158</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>162.520056</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>F-50B</t>
+          <t>F-5</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>298.15</v>
+        <v>373.15</v>
       </c>
       <c r="C67" t="n">
         <v>100000</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>10.283591</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>522.665716</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>F-51A</t>
+          <t>F-50A</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -2073,16 +2073,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>5.623158</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>162.520056</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>F-51B</t>
+          <t>F-50B</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -2097,16 +2097,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.010838</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0.5565020000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>F-52A</t>
+          <t>F-51A</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -2130,7 +2130,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>F-52B</t>
+          <t>F-51B</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -2145,16 +2145,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.009754000000000001</v>
+        <v>0.010838</v>
       </c>
       <c r="F71" t="n">
-        <v>0.28142</v>
+        <v>0.5565020000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>F-53</t>
+          <t>F-52A</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -2165,20 +2165,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>9.465305000000001</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>199.779915</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>F-54</t>
+          <t>F-52B</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -2189,20 +2189,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.002123</v>
+        <v>0.009754000000000001</v>
       </c>
       <c r="F73" t="n">
-        <v>0.565406</v>
+        <v>0.28142</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>F-55</t>
+          <t>F-53</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -2217,16 +2217,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.891185</v>
+        <v>9.465305000000001</v>
       </c>
       <c r="F74" t="n">
-        <v>20.94116</v>
+        <v>199.779913</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>F-56</t>
+          <t>F-54</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -2241,23 +2241,23 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.000148</v>
+        <v>0.002123</v>
       </c>
       <c r="F75" t="n">
-        <v>0.03947</v>
+        <v>0.565406</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>F-57</t>
+          <t>F-55</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>379.2</v>
+        <v>298.15</v>
       </c>
       <c r="C76" t="n">
-        <v>87290</v>
+        <v>100000</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -2265,23 +2265,23 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>22.820119</v>
+        <v>0.891185</v>
       </c>
       <c r="F76" t="n">
-        <v>715.157753</v>
+        <v>20.94116</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>F-57T</t>
+          <t>F-56</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>379.2</v>
+        <v>298.15</v>
       </c>
       <c r="C77" t="n">
-        <v>87290</v>
+        <v>100000</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -2289,16 +2289,16 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>22.820119</v>
+        <v>0.000148</v>
       </c>
       <c r="F77" t="n">
-        <v>715.157753</v>
+        <v>0.03947</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>F-58</t>
+          <t>F-57</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -2313,23 +2313,23 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.004276</v>
+        <v>22.820119</v>
       </c>
       <c r="F78" t="n">
-        <v>1.138709</v>
+        <v>715.15775</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>F-59</t>
+          <t>F-57T</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>298.15</v>
+        <v>379.2</v>
       </c>
       <c r="C79" t="n">
-        <v>100000</v>
+        <v>87290</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2337,23 +2337,23 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2.044531</v>
+        <v>22.820119</v>
       </c>
       <c r="F79" t="n">
-        <v>78.106458</v>
+        <v>715.15775</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>F-6</t>
+          <t>F-58</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>298.15</v>
+        <v>379.2</v>
       </c>
       <c r="C80" t="n">
-        <v>100000</v>
+        <v>87290</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -2361,20 +2361,20 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>10.283591</v>
+        <v>0.004276</v>
       </c>
       <c r="F80" t="n">
-        <v>522.665717</v>
+        <v>1.138709</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>F-60</t>
+          <t>F-59</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>323.15</v>
+        <v>298.15</v>
       </c>
       <c r="C81" t="n">
         <v>100000</v>
@@ -2385,16 +2385,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.00651</v>
+        <v>2.044531</v>
       </c>
       <c r="F81" t="n">
-        <v>0.117274</v>
+        <v>78.106458</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>F-61</t>
+          <t>F-6</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -2409,20 +2409,20 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.006547</v>
+        <v>10.283591</v>
       </c>
       <c r="F82" t="n">
-        <v>1.743586</v>
+        <v>522.665716</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>F-62</t>
+          <t>F-60</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>298.15</v>
+        <v>323.15</v>
       </c>
       <c r="C83" t="n">
         <v>100000</v>
@@ -2433,16 +2433,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>7.998166</v>
+        <v>0.00651</v>
       </c>
       <c r="F83" t="n">
-        <v>1527.552435</v>
+        <v>0.117274</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>F-63</t>
+          <t>F-61</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -2453,20 +2453,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.773725</v>
+        <v>0.006547</v>
       </c>
       <c r="F84" t="n">
-        <v>29.893158</v>
+        <v>1.743586</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>F-63P</t>
+          <t>F-62</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -2477,48 +2477,48 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.773725</v>
+        <v>7.998166</v>
       </c>
       <c r="F85" t="n">
-        <v>29.893158</v>
+        <v>1527.552422</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>F-64</t>
+          <t>F-63</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>383.15</v>
+        <v>298.15</v>
       </c>
       <c r="C86" t="n">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>16.47484</v>
+        <v>0.773725</v>
       </c>
       <c r="F86" t="n">
-        <v>600.535617</v>
+        <v>29.893158</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>F-65</t>
+          <t>F-63P</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>383.15</v>
+        <v>298.15</v>
       </c>
       <c r="C87" t="n">
         <v>100000</v>
@@ -2529,23 +2529,23 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6.340412</v>
+        <v>0.773725</v>
       </c>
       <c r="F87" t="n">
-        <v>114.222523</v>
+        <v>29.893158</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>F-66</t>
+          <t>F-64</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>379.2</v>
+        <v>383.15</v>
       </c>
       <c r="C88" t="n">
-        <v>87290</v>
+        <v>100000</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2553,40 +2553,40 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6.660651</v>
+        <v>16.47484</v>
       </c>
       <c r="F88" t="n">
-        <v>119.991629</v>
+        <v>600.535615</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>F-67</t>
+          <t>F-65</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>393.15</v>
+        <v>383.15</v>
       </c>
       <c r="C89" t="n">
         <v>100000</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>16.2223</v>
+        <v>6.340412</v>
       </c>
       <c r="F89" t="n">
-        <v>292.244734</v>
+        <v>114.222522</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>F-68</t>
+          <t>F-66</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -2601,16 +2601,16 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>9.814189000000001</v>
+        <v>6.660651</v>
       </c>
       <c r="F90" t="n">
-        <v>480.543989</v>
+        <v>119.991628</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>F-69</t>
+          <t>F-67</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -2634,14 +2634,14 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>F-6P</t>
+          <t>F-68</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>298.15</v>
+        <v>379.2</v>
       </c>
       <c r="C92" t="n">
-        <v>100000</v>
+        <v>87290</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -2649,20 +2649,20 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>10.283591</v>
+        <v>9.814189000000001</v>
       </c>
       <c r="F92" t="n">
-        <v>522.665717</v>
+        <v>480.543988</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>F-7</t>
+          <t>F-69</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>298.15</v>
+        <v>393.15</v>
       </c>
       <c r="C93" t="n">
         <v>100000</v>
@@ -2673,23 +2673,23 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>7.998299</v>
+        <v>16.2223</v>
       </c>
       <c r="F93" t="n">
-        <v>1527.587931</v>
+        <v>292.244734</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>F-70</t>
+          <t>F-6P</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>375</v>
+        <v>298.15</v>
       </c>
       <c r="C94" t="n">
-        <v>75260</v>
+        <v>100000</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -2697,23 +2697,23 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6.660651</v>
+        <v>10.283591</v>
       </c>
       <c r="F94" t="n">
-        <v>119.991629</v>
+        <v>522.665716</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>F-71</t>
+          <t>F-7</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>375</v>
+        <v>298.15</v>
       </c>
       <c r="C95" t="n">
-        <v>75260</v>
+        <v>100000</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -2721,105 +2721,153 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>29.223363</v>
+        <v>7.998299</v>
       </c>
       <c r="F95" t="n">
-        <v>526.458886</v>
+        <v>1527.587918</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>F-72</t>
+          <t>F-70</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>383.15</v>
+        <v>375</v>
       </c>
       <c r="C96" t="n">
-        <v>100000</v>
+        <v>75260</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6.340412</v>
+        <v>6.660651</v>
       </c>
       <c r="F96" t="n">
-        <v>114.222523</v>
+        <v>119.991628</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>F-73</t>
+          <t>F-71</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>414</v>
+        <v>375</v>
       </c>
       <c r="C97" t="n">
-        <v>100000</v>
+        <v>75260</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4.17976</v>
+        <v>29.223363</v>
       </c>
       <c r="F97" t="n">
-        <v>121.859939</v>
+        <v>526.458884</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>F-8</t>
+          <t>F-72</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>298.15</v>
+        <v>383.15</v>
       </c>
       <c r="C98" t="n">
         <v>100000</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>8.814462000000001</v>
+        <v>6.340412</v>
       </c>
       <c r="F98" t="n">
-        <v>1849.908327</v>
+        <v>114.222522</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>F-9</t>
+          <t>F-73</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>298.15</v>
+        <v>414</v>
       </c>
       <c r="C99" t="n">
         <v>100000</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>4.17976</v>
+      </c>
+      <c r="F99" t="n">
+        <v>121.859939</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>F-8</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>298.15</v>
+      </c>
+      <c r="C100" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="E99" t="n">
+      <c r="E100" t="n">
+        <v>8.814462000000001</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1849.908314</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>F-9</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>298.15</v>
+      </c>
+      <c r="C101" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
         <v>0.881446</v>
       </c>
-      <c r="F99" t="n">
+      <c r="F101" t="n">
         <v>16.463097</v>
       </c>
     </row>
@@ -2834,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ99"/>
+  <dimension ref="A1:AQ101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3314,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.71840192</v>
+        <v>1.7184019</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.27751246</v>
+        <v>6.27751241</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -3423,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>22.00747215</v>
+        <v>22.00747198</v>
       </c>
       <c r="T4" t="n">
         <v>0.00396602</v>
@@ -3556,7 +3604,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>22.00747215</v>
+        <v>22.00747198</v>
       </c>
       <c r="T5" t="n">
         <v>0.00396602</v>
@@ -3713,10 +3761,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.71410591</v>
+        <v>1.7141059</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.27751246</v>
+        <v>6.27751241</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -3846,10 +3894,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72065292</v>
+        <v>1.7206529</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.27751246</v>
+        <v>6.27751241</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -4112,10 +4160,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.63462027</v>
+        <v>1.63462026</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.96363684</v>
+        <v>5.96363679</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -4245,10 +4293,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.08616583</v>
+        <v>0.08616588</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.3138752</v>
+        <v>0.31387537</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -4354,7 +4402,7 @@
         <v>0.006234</v>
       </c>
       <c r="S11" t="n">
-        <v>8.9639284</v>
+        <v>8.96392831</v>
       </c>
       <c r="T11" t="n">
         <v>0.46497694</v>
@@ -4487,7 +4535,7 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.86953481</v>
+        <v>0.8695348000000001</v>
       </c>
       <c r="T12" t="n">
         <v>0.00794096</v>
@@ -4620,7 +4668,7 @@
         <v>0.006234</v>
       </c>
       <c r="S13" t="n">
-        <v>8.7661379</v>
+        <v>8.766137820000001</v>
       </c>
       <c r="T13" t="n">
         <v>0.20359155</v>
@@ -4753,7 +4801,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>6.69562032</v>
+        <v>6.69562023</v>
       </c>
       <c r="T14" t="n">
         <v>2.936403</v>
@@ -5019,7 +5067,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.86040562</v>
+        <v>0.86040561</v>
       </c>
       <c r="T16" t="n">
         <v>0.00495151</v>
@@ -5950,7 +5998,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>6.80360506</v>
+        <v>6.80360499</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -7413,7 +7461,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>6.69562032</v>
+        <v>6.69562023</v>
       </c>
       <c r="T34" t="n">
         <v>2.936403</v>
@@ -7546,7 +7594,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>6.69562032</v>
+        <v>6.69562023</v>
       </c>
       <c r="T35" t="n">
         <v>2.936403</v>
@@ -7679,7 +7727,7 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>6.69562032</v>
+        <v>6.69562023</v>
       </c>
       <c r="T36" t="n">
         <v>2.936403</v>
@@ -7945,7 +7993,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>3.39188843</v>
+        <v>3.39188834</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -8211,7 +8259,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>9.211271740000001</v>
+        <v>9.21127167</v>
       </c>
       <c r="T40" t="n">
         <v>0.26437484</v>
@@ -8344,7 +8392,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>9.211271740000001</v>
+        <v>9.21127167</v>
       </c>
       <c r="T41" t="n">
         <v>0.26437484</v>
@@ -8743,7 +8791,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>27.53677453</v>
+        <v>27.53677446</v>
       </c>
       <c r="T44" t="n">
         <v>2.56359434</v>
@@ -8876,7 +8924,7 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>27.53677453</v>
+        <v>27.53677446</v>
       </c>
       <c r="T45" t="n">
         <v>2.56359434</v>
@@ -9009,7 +9057,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>24.3862713</v>
+        <v>24.38627122</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -9353,7 +9401,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>F-4</t>
+          <t>F-3P</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -9390,22 +9438,22 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>0.01380778</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>0.00243865</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>0.00054191</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0.12509107</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -9414,10 +9462,10 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>0.31412884</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>0.44280813</v>
       </c>
       <c r="W49" t="n">
         <v>0</v>
@@ -9486,7 +9534,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>F-40</t>
+          <t>F-3PT</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -9523,16 +9571,16 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>0.01380778</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>0.00243865</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>0.00054191</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -9547,16 +9595,16 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>0.31412884</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>0.44280813</v>
       </c>
       <c r="W50" t="n">
-        <v>1.68713682</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0.44847941</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
         <v>0</v>
@@ -9619,7 +9667,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>F-41</t>
+          <t>F-4</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -9656,22 +9704,22 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.01380778</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0.00243865</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>0.00054191</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>0.12509107</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -9680,16 +9728,16 @@
         <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>1.92968853</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>0.44280813</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>4.67007382</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1.64530241</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
         <v>0</v>
@@ -9752,7 +9800,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>F-41T</t>
+          <t>F-40</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -9789,16 +9837,16 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.01380778</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0.00243865</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>0.00054191</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -9813,16 +9861,16 @@
         <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.92968853</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>0.44280813</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>4.67007382</v>
+        <v>1.68713682</v>
       </c>
       <c r="X52" t="n">
-        <v>1.64530241</v>
+        <v>0.44847941</v>
       </c>
       <c r="Y52" t="n">
         <v>0</v>
@@ -9885,7 +9933,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>F-42</t>
+          <t>F-41</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -9946,16 +9994,16 @@
         <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>0.01929689</v>
+        <v>1.92968853</v>
       </c>
       <c r="V53" t="n">
-        <v>0.05398027</v>
+        <v>0.44280813</v>
       </c>
       <c r="W53" t="n">
         <v>4.67007382</v>
       </c>
       <c r="X53" t="n">
-        <v>0.8760836</v>
+        <v>1.64530241</v>
       </c>
       <c r="Y53" t="n">
         <v>0</v>
@@ -10018,7 +10066,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>F-43</t>
+          <t>F-41T</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -10055,16 +10103,16 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>0.01380778</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>0.00243865</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>0.00054191</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -10079,19 +10127,19 @@
         <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.92968853</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>0.44280813</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>4.67007382</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.64530241</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.09981703</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -10151,7 +10199,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>F-44</t>
+          <t>F-42</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -10206,25 +10254,25 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.13019613</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
         <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>0.00120413</v>
+        <v>0.01929689</v>
       </c>
       <c r="V55" t="n">
-        <v>0.00336837</v>
+        <v>0.05398027</v>
       </c>
       <c r="W55" t="n">
-        <v>4.74782485</v>
+        <v>4.67007382</v>
       </c>
       <c r="X55" t="n">
-        <v>0.85438425</v>
+        <v>0.8760836</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.01301961</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
         <v>0</v>
@@ -10284,7 +10332,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>F-45</t>
+          <t>F-43</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -10339,7 +10387,7 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.13019613</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
         <v>0</v>
@@ -10357,7 +10405,7 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>0.09981703</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -10417,7 +10465,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>F-45R</t>
+          <t>F-44</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -10454,16 +10502,16 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>0.01380778</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>0.00243865</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>0.00054191</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -10472,25 +10520,25 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.12368632</v>
+        <v>0.13019613</v>
       </c>
       <c r="T57" t="n">
         <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>0.00120413</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>0.00336837</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>4.74782485</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>0.85438425</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>0.01301961</v>
       </c>
       <c r="Z57" t="n">
         <v>0</v>
@@ -10550,7 +10598,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>F-46</t>
+          <t>F-45</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -10587,16 +10635,16 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.01380778</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>0.00243865</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>0.00054191</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -10605,25 +10653,25 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>0.13019613</v>
       </c>
       <c r="T58" t="n">
         <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>0.00120413</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>0.00336837</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>4.74782485</v>
+        <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>0.85438425</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.01301961</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
@@ -10683,7 +10731,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>F-47</t>
+          <t>F-45R</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -10738,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>38.15971123</v>
+        <v>0.12368632</v>
       </c>
       <c r="T59" t="n">
         <v>0</v>
@@ -10816,7 +10864,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>F-47T</t>
+          <t>F-46</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -10853,16 +10901,16 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>0.01380778</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>0.00243865</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>0.00054191</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -10871,25 +10919,25 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>38.15971123</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
         <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>0.00120413</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>0.00336837</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>4.74782485</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>0.85438425</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>0.01301961</v>
       </c>
       <c r="Z60" t="n">
         <v>0</v>
@@ -10949,7 +10997,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>F-48</t>
+          <t>F-47</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -11022,7 +11070,7 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.01288942</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
         <v>0</v>
@@ -11082,7 +11130,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>F-49</t>
+          <t>F-47T</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -11119,16 +11167,16 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0.01380778</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>0.00243865</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>0.00054191</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -11137,25 +11185,25 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>38.15971123</v>
       </c>
       <c r="T62" t="n">
         <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>0.00120413</v>
+        <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>0.00336837</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>4.74782485</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>0.85438425</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.0001302</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
         <v>0</v>
@@ -11215,7 +11263,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>F-49A</t>
+          <t>F-48</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -11252,16 +11300,16 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0.01380778</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>0.00243865</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>0.00054191</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -11270,25 +11318,25 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>38.15971123</v>
       </c>
       <c r="T63" t="n">
         <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>0.00120413</v>
+        <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>0.00336837</v>
+        <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>4.74782485</v>
+        <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>0.85438425</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.0001302</v>
+        <v>0.01288942</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
@@ -11348,7 +11396,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>F-49B</t>
+          <t>F-49</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -11385,16 +11433,16 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>0.01380778</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>0.00243865</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>0.00054191</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -11409,19 +11457,19 @@
         <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>0.00120413</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>0.00336837</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>4.74782485</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>0.85438425</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>0.0001302</v>
       </c>
       <c r="Z64" t="n">
         <v>0</v>
@@ -11481,7 +11529,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>F-5</t>
+          <t>F-49A</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -11518,43 +11566,43 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>0.01380778</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>0.00243865</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>0.00054191</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.106e-05</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>0.006234</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>8.9639284</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>0.46497694</v>
+        <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>0.00120413</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>0.00336837</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>4.74782485</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>0.85438425</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>0.0001302</v>
       </c>
       <c r="Z65" t="n">
         <v>0</v>
@@ -11572,37 +11620,37 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0.81061497</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>0.00765862</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>0.00040357</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>0.00032183</v>
+        <v>0</v>
       </c>
       <c r="AI65" t="n">
-        <v>0.00854456</v>
+        <v>0</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0.00209422</v>
+        <v>0</v>
       </c>
       <c r="AK65" t="n">
-        <v>0.01255454</v>
+        <v>0</v>
       </c>
       <c r="AL65" t="n">
-        <v>0.00252991</v>
+        <v>0</v>
       </c>
       <c r="AM65" t="n">
-        <v>0.00036642</v>
+        <v>0</v>
       </c>
       <c r="AN65" t="n">
-        <v>0.00021248</v>
+        <v>0</v>
       </c>
       <c r="AO65" t="n">
-        <v>0.00313991</v>
+        <v>0</v>
       </c>
       <c r="AP65" t="n">
         <v>0</v>
@@ -11614,7 +11662,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>F-50A</t>
+          <t>F-49B</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -11651,10 +11699,10 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>0.01380778</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>0.00243865</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -11675,19 +11723,19 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>0.00120413</v>
+        <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>0.00336837</v>
+        <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>4.74782485</v>
+        <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>0.85438425</v>
+        <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.0001302</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
         <v>0</v>
@@ -11747,7 +11795,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>F-50B</t>
+          <t>F-5</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -11796,16 +11844,16 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>1.106e-05</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>0.006234</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>8.96392831</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>0.46497694</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -11838,37 +11886,37 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>0.81061497</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>0.00765862</v>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>0.00040357</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>0.00032183</v>
       </c>
       <c r="AI67" t="n">
-        <v>0</v>
+        <v>0.00854456</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0</v>
+        <v>0.00209422</v>
       </c>
       <c r="AK67" t="n">
-        <v>0</v>
+        <v>0.01255454</v>
       </c>
       <c r="AL67" t="n">
-        <v>0</v>
+        <v>0.00252991</v>
       </c>
       <c r="AM67" t="n">
-        <v>0</v>
+        <v>0.00036642</v>
       </c>
       <c r="AN67" t="n">
-        <v>0</v>
+        <v>0.00021248</v>
       </c>
       <c r="AO67" t="n">
-        <v>0</v>
+        <v>0.00313991</v>
       </c>
       <c r="AP67" t="n">
         <v>0</v>
@@ -11880,7 +11928,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>F-51A</t>
+          <t>F-50A</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -11917,10 +11965,10 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>0.01380778</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>0.00243865</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -11941,19 +11989,19 @@
         <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>0.00120413</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>0.00336837</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>4.74782485</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>0.85438425</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>0.0001302</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -12013,7 +12061,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>F-51B</t>
+          <t>F-50B</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -12059,7 +12107,7 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>0.00108382</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -12080,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>0.00770595</v>
+        <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>0.00204842</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
         <v>0</v>
@@ -12146,7 +12194,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>F-52A</t>
+          <t>F-51A</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -12279,7 +12327,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>F-52B</t>
+          <t>F-51B</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -12325,7 +12373,7 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>0.00108382</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -12412,7 +12460,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>F-53</t>
+          <t>F-52A</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -12461,16 +12509,16 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.106e-05</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>0.006234</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>8.9639284</v>
+        <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>0.46497694</v>
+        <v>0</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
@@ -12491,7 +12539,7 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>8.94e-05</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
         <v>0</v>
@@ -12503,37 +12551,37 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0.00081062</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>0.00055538</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
-        <v>3.625e-05</v>
+        <v>0</v>
       </c>
       <c r="AH72" t="n">
-        <v>0.00032183</v>
+        <v>0</v>
       </c>
       <c r="AI72" t="n">
-        <v>0.00854456</v>
+        <v>0</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.00209422</v>
+        <v>0</v>
       </c>
       <c r="AK72" t="n">
-        <v>0.01255454</v>
+        <v>0</v>
       </c>
       <c r="AL72" t="n">
-        <v>0.00252991</v>
+        <v>0</v>
       </c>
       <c r="AM72" t="n">
-        <v>0.00036642</v>
+        <v>0</v>
       </c>
       <c r="AN72" t="n">
-        <v>0.00021248</v>
+        <v>0</v>
       </c>
       <c r="AO72" t="n">
-        <v>0.00203921</v>
+        <v>0</v>
       </c>
       <c r="AP72" t="n">
         <v>0</v>
@@ -12545,7 +12593,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>F-54</t>
+          <t>F-52B</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -12612,10 +12660,10 @@
         <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>0.00770595</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>0.00204842</v>
       </c>
       <c r="Y73" t="n">
         <v>0</v>
@@ -12624,7 +12672,7 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.00212305</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
         <v>0</v>
@@ -12678,7 +12726,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>F-55</t>
+          <t>F-53</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -12727,16 +12775,16 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>1.106e-05</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>0.006234</v>
       </c>
       <c r="S74" t="n">
-        <v>0.86953481</v>
+        <v>8.96392831</v>
       </c>
       <c r="T74" t="n">
-        <v>0.00794096</v>
+        <v>0.46497694</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
@@ -12757,49 +12805,49 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.365e-05</v>
+        <v>8.94e-05</v>
       </c>
       <c r="AB74" t="n">
         <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>0.00397048</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0.00202451</v>
+        <v>0.00081062</v>
       </c>
       <c r="AF74" t="n">
-        <v>0.00710324</v>
+        <v>0.00055538</v>
       </c>
       <c r="AG74" t="n">
-        <v>0.00036732</v>
+        <v>3.625e-05</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>0.00032183</v>
       </c>
       <c r="AI74" t="n">
-        <v>0</v>
+        <v>0.00854456</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0</v>
+        <v>0.00209422</v>
       </c>
       <c r="AK74" t="n">
-        <v>0</v>
+        <v>0.01255454</v>
       </c>
       <c r="AL74" t="n">
-        <v>0</v>
+        <v>0.00252991</v>
       </c>
       <c r="AM74" t="n">
-        <v>0</v>
+        <v>0.00036642</v>
       </c>
       <c r="AN74" t="n">
-        <v>0</v>
+        <v>0.00021248</v>
       </c>
       <c r="AO74" t="n">
-        <v>0.00022024</v>
+        <v>0.00203921</v>
       </c>
       <c r="AP74" t="n">
         <v>0</v>
@@ -12811,7 +12859,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>F-56</t>
+          <t>F-54</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -12890,7 +12938,7 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.00014821</v>
+        <v>0.00212305</v>
       </c>
       <c r="AB75" t="n">
         <v>0</v>
@@ -12944,7 +12992,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>F-57</t>
+          <t>F-55</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -12999,10 +13047,10 @@
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>22.00747215</v>
+        <v>0.8695348000000001</v>
       </c>
       <c r="T76" t="n">
-        <v>0.00396602</v>
+        <v>0.00794096</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -13023,25 +13071,25 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.025e-05</v>
+        <v>2.365e-05</v>
       </c>
       <c r="AB76" t="n">
         <v>0</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>0.00397048</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0.80777984</v>
+        <v>0.00202451</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>0.00710324</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>0.00036732</v>
       </c>
       <c r="AH76" t="n">
         <v>0</v>
@@ -13065,7 +13113,7 @@
         <v>0</v>
       </c>
       <c r="AO76" t="n">
-        <v>0.00088043</v>
+        <v>0.00022024</v>
       </c>
       <c r="AP76" t="n">
         <v>0</v>
@@ -13077,7 +13125,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>F-57T</t>
+          <t>F-56</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -13132,10 +13180,10 @@
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>22.00747215</v>
+        <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>0.00396602</v>
+        <v>0</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -13156,7 +13204,7 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.025e-05</v>
+        <v>0.00014821</v>
       </c>
       <c r="AB77" t="n">
         <v>0</v>
@@ -13168,7 +13216,7 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0.80777984</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
         <v>0</v>
@@ -13198,7 +13246,7 @@
         <v>0</v>
       </c>
       <c r="AO77" t="n">
-        <v>0.00088043</v>
+        <v>0</v>
       </c>
       <c r="AP77" t="n">
         <v>0</v>
@@ -13210,7 +13258,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>F-58</t>
+          <t>F-57</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -13265,10 +13313,10 @@
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>22.00747198</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>0.00396602</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
@@ -13289,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.00427575</v>
+        <v>2.025e-05</v>
       </c>
       <c r="AB78" t="n">
         <v>0</v>
@@ -13301,7 +13349,7 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>0.80777984</v>
       </c>
       <c r="AF78" t="n">
         <v>0</v>
@@ -13331,7 +13379,7 @@
         <v>0</v>
       </c>
       <c r="AO78" t="n">
-        <v>0</v>
+        <v>0.00088043</v>
       </c>
       <c r="AP78" t="n">
         <v>0</v>
@@ -13343,7 +13391,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>F-59</t>
+          <t>F-57T</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -13398,10 +13446,10 @@
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>1.12726501</v>
+        <v>22.00747198</v>
       </c>
       <c r="T79" t="n">
-        <v>0.91726622</v>
+        <v>0.00396602</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -13422,7 +13470,7 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.025e-05</v>
       </c>
       <c r="AB79" t="n">
         <v>0</v>
@@ -13434,7 +13482,7 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>0.80777984</v>
       </c>
       <c r="AF79" t="n">
         <v>0</v>
@@ -13464,7 +13512,7 @@
         <v>0</v>
       </c>
       <c r="AO79" t="n">
-        <v>0</v>
+        <v>0.00088043</v>
       </c>
       <c r="AP79" t="n">
         <v>0</v>
@@ -13476,7 +13524,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>F-6</t>
+          <t>F-58</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -13525,16 +13573,16 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.106e-05</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>0.006234</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>8.9639284</v>
+        <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>0.46497694</v>
+        <v>0</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -13555,7 +13603,7 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>0.00427575</v>
       </c>
       <c r="AB80" t="n">
         <v>0</v>
@@ -13567,37 +13615,37 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0.81061497</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>0.00765862</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>0.00040357</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>0.00032183</v>
+        <v>0</v>
       </c>
       <c r="AI80" t="n">
-        <v>0.00854456</v>
+        <v>0</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0.00209422</v>
+        <v>0</v>
       </c>
       <c r="AK80" t="n">
-        <v>0.01255454</v>
+        <v>0</v>
       </c>
       <c r="AL80" t="n">
-        <v>0.00252991</v>
+        <v>0</v>
       </c>
       <c r="AM80" t="n">
-        <v>0.00036642</v>
+        <v>0</v>
       </c>
       <c r="AN80" t="n">
-        <v>0.00021248</v>
+        <v>0</v>
       </c>
       <c r="AO80" t="n">
-        <v>0.00313991</v>
+        <v>0</v>
       </c>
       <c r="AP80" t="n">
         <v>0</v>
@@ -13609,7 +13657,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>F-60</t>
+          <t>F-59</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -13664,10 +13712,10 @@
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.00650981</v>
+        <v>1.12726501</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>0.91726622</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -13742,7 +13790,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>F-61</t>
+          <t>F-6</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -13791,16 +13839,16 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>1.106e-05</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>0.006234</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>8.96392831</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>0.46497694</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
@@ -13821,7 +13869,7 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0.00654701</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
         <v>0</v>
@@ -13833,37 +13881,37 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>0.81061497</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>0.00765862</v>
       </c>
       <c r="AG82" t="n">
-        <v>0</v>
+        <v>0.00040357</v>
       </c>
       <c r="AH82" t="n">
-        <v>0</v>
+        <v>0.00032183</v>
       </c>
       <c r="AI82" t="n">
-        <v>0</v>
+        <v>0.00854456</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0</v>
+        <v>0.00209422</v>
       </c>
       <c r="AK82" t="n">
-        <v>0</v>
+        <v>0.01255454</v>
       </c>
       <c r="AL82" t="n">
-        <v>0</v>
+        <v>0.00252991</v>
       </c>
       <c r="AM82" t="n">
-        <v>0</v>
+        <v>0.00036642</v>
       </c>
       <c r="AN82" t="n">
-        <v>0</v>
+        <v>0.00021248</v>
       </c>
       <c r="AO82" t="n">
-        <v>0</v>
+        <v>0.00313991</v>
       </c>
       <c r="AP82" t="n">
         <v>0</v>
@@ -13875,7 +13923,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>F-62</t>
+          <t>F-60</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -13930,7 +13978,7 @@
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>0.00650981</v>
       </c>
       <c r="T83" t="n">
         <v>0</v>
@@ -13954,10 +14002,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.72065292</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>6.27751246</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -13966,7 +14014,7 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>7e-08</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
         <v>0</v>
@@ -13996,7 +14044,7 @@
         <v>0</v>
       </c>
       <c r="AO83" t="n">
-        <v>5.5e-07</v>
+        <v>0</v>
       </c>
       <c r="AP83" t="n">
         <v>0</v>
@@ -14008,7 +14056,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>F-63</t>
+          <t>F-61</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -14045,16 +14093,16 @@
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>0.01380778</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>0.00243865</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>0.00054191</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -14069,10 +14117,10 @@
         <v>0</v>
       </c>
       <c r="U84" t="n">
-        <v>0.31412884</v>
+        <v>0</v>
       </c>
       <c r="V84" t="n">
-        <v>0.44280813</v>
+        <v>0</v>
       </c>
       <c r="W84" t="n">
         <v>0</v>
@@ -14087,7 +14135,7 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>0.00654701</v>
       </c>
       <c r="AB84" t="n">
         <v>0</v>
@@ -14141,7 +14189,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>F-63P</t>
+          <t>F-62</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -14178,16 +14226,16 @@
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>0.01380778</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>0.00243865</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>0.00054191</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -14202,10 +14250,10 @@
         <v>0</v>
       </c>
       <c r="U85" t="n">
-        <v>0.31412884</v>
+        <v>0</v>
       </c>
       <c r="V85" t="n">
-        <v>0.44280813</v>
+        <v>0</v>
       </c>
       <c r="W85" t="n">
         <v>0</v>
@@ -14220,10 +14268,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.7206529</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>6.27751241</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -14232,7 +14280,7 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>7e-08</v>
       </c>
       <c r="AF85" t="n">
         <v>0</v>
@@ -14262,7 +14310,7 @@
         <v>0</v>
       </c>
       <c r="AO85" t="n">
-        <v>0</v>
+        <v>5.5e-07</v>
       </c>
       <c r="AP85" t="n">
         <v>0</v>
@@ -14274,7 +14322,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>F-64</t>
+          <t>F-63</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -14311,16 +14359,16 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>0.01380778</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>0.00243865</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>0.00054191</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14329,16 +14377,16 @@
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>15.6670601</v>
+        <v>0</v>
       </c>
       <c r="T86" t="n">
         <v>0</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>0.31412884</v>
       </c>
       <c r="V86" t="n">
-        <v>0</v>
+        <v>0.44280813</v>
       </c>
       <c r="W86" t="n">
         <v>0</v>
@@ -14365,7 +14413,7 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0.80777984</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
         <v>0</v>
@@ -14407,7 +14455,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>F-65</t>
+          <t>F-63P</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -14444,16 +14492,16 @@
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>0.01380778</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>0.00243865</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>0.00054191</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14462,16 +14510,16 @@
         <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>6.34041204</v>
+        <v>0</v>
       </c>
       <c r="T87" t="n">
         <v>0</v>
       </c>
       <c r="U87" t="n">
-        <v>0</v>
+        <v>0.31412884</v>
       </c>
       <c r="V87" t="n">
-        <v>0</v>
+        <v>0.44280813</v>
       </c>
       <c r="W87" t="n">
         <v>0</v>
@@ -14540,7 +14588,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>F-66</t>
+          <t>F-64</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -14595,7 +14643,7 @@
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>6.66065104</v>
+        <v>15.66705998</v>
       </c>
       <c r="T88" t="n">
         <v>0</v>
@@ -14631,7 +14679,7 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>0.80777984</v>
       </c>
       <c r="AF88" t="n">
         <v>0</v>
@@ -14673,7 +14721,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>F-67</t>
+          <t>F-65</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -14728,7 +14776,7 @@
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>16.2223</v>
+        <v>6.34041199</v>
       </c>
       <c r="T89" t="n">
         <v>0</v>
@@ -14806,7 +14854,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>F-68</t>
+          <t>F-66</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -14861,7 +14909,7 @@
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>9.006409059999999</v>
+        <v>6.66065099</v>
       </c>
       <c r="T90" t="n">
         <v>0</v>
@@ -14897,7 +14945,7 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0.80777984</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
         <v>0</v>
@@ -14939,7 +14987,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>F-69</t>
+          <t>F-67</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -15072,7 +15120,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>F-6P</t>
+          <t>F-68</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -15121,16 +15169,16 @@
         <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.106e-05</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>0.006234</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>8.9639284</v>
+        <v>9.006408990000001</v>
       </c>
       <c r="T92" t="n">
-        <v>0.46497694</v>
+        <v>0</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -15163,37 +15211,37 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0.81061497</v>
+        <v>0.80777984</v>
       </c>
       <c r="AF92" t="n">
-        <v>0.00765862</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
-        <v>0.00040357</v>
+        <v>0</v>
       </c>
       <c r="AH92" t="n">
-        <v>0.00032183</v>
+        <v>0</v>
       </c>
       <c r="AI92" t="n">
-        <v>0.00854456</v>
+        <v>0</v>
       </c>
       <c r="AJ92" t="n">
-        <v>0.00209422</v>
+        <v>0</v>
       </c>
       <c r="AK92" t="n">
-        <v>0.01255454</v>
+        <v>0</v>
       </c>
       <c r="AL92" t="n">
-        <v>0.00252991</v>
+        <v>0</v>
       </c>
       <c r="AM92" t="n">
-        <v>0.00036642</v>
+        <v>0</v>
       </c>
       <c r="AN92" t="n">
-        <v>0.00021248</v>
+        <v>0</v>
       </c>
       <c r="AO92" t="n">
-        <v>0.00313991</v>
+        <v>0</v>
       </c>
       <c r="AP92" t="n">
         <v>0</v>
@@ -15205,7 +15253,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>F-7</t>
+          <t>F-69</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -15260,7 +15308,7 @@
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>0</v>
+        <v>16.2223</v>
       </c>
       <c r="T93" t="n">
         <v>0</v>
@@ -15284,10 +15332,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.72078622</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>6.27751246</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15296,7 +15344,7 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>7e-08</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
         <v>0</v>
@@ -15326,7 +15374,7 @@
         <v>0</v>
       </c>
       <c r="AO93" t="n">
-        <v>5.2e-07</v>
+        <v>0</v>
       </c>
       <c r="AP93" t="n">
         <v>0</v>
@@ -15338,7 +15386,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>F-70</t>
+          <t>F-6P</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -15387,16 +15435,16 @@
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>1.106e-05</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>0.006234</v>
       </c>
       <c r="S94" t="n">
-        <v>6.66065104</v>
+        <v>8.96392831</v>
       </c>
       <c r="T94" t="n">
-        <v>0</v>
+        <v>0.46497694</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -15429,37 +15477,37 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>0.81061497</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>0.00765862</v>
       </c>
       <c r="AG94" t="n">
-        <v>0</v>
+        <v>0.00040357</v>
       </c>
       <c r="AH94" t="n">
-        <v>0</v>
+        <v>0.00032183</v>
       </c>
       <c r="AI94" t="n">
-        <v>0</v>
+        <v>0.00854456</v>
       </c>
       <c r="AJ94" t="n">
-        <v>0</v>
+        <v>0.00209422</v>
       </c>
       <c r="AK94" t="n">
-        <v>0</v>
+        <v>0.01255454</v>
       </c>
       <c r="AL94" t="n">
-        <v>0</v>
+        <v>0.00252991</v>
       </c>
       <c r="AM94" t="n">
-        <v>0</v>
+        <v>0.00036642</v>
       </c>
       <c r="AN94" t="n">
-        <v>0</v>
+        <v>0.00021248</v>
       </c>
       <c r="AO94" t="n">
-        <v>0</v>
+        <v>0.00313991</v>
       </c>
       <c r="AP94" t="n">
         <v>0</v>
@@ -15471,7 +15519,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>F-71</t>
+          <t>F-7</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -15526,7 +15574,7 @@
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>29.22336309</v>
+        <v>0</v>
       </c>
       <c r="T95" t="n">
         <v>0</v>
@@ -15550,10 +15598,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.72078621</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>6.27751241</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15562,7 +15610,7 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>7e-08</v>
       </c>
       <c r="AF95" t="n">
         <v>0</v>
@@ -15592,7 +15640,7 @@
         <v>0</v>
       </c>
       <c r="AO95" t="n">
-        <v>0</v>
+        <v>5.2e-07</v>
       </c>
       <c r="AP95" t="n">
         <v>0</v>
@@ -15604,7 +15652,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>F-72</t>
+          <t>F-70</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -15659,7 +15707,7 @@
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>6.34041204</v>
+        <v>6.66065099</v>
       </c>
       <c r="T96" t="n">
         <v>0</v>
@@ -15737,7 +15785,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>F-73</t>
+          <t>F-71</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -15792,7 +15840,7 @@
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>0</v>
+        <v>29.22336299</v>
       </c>
       <c r="T97" t="n">
         <v>0</v>
@@ -15804,10 +15852,10 @@
         <v>0</v>
       </c>
       <c r="W97" t="n">
-        <v>2.982937</v>
+        <v>0</v>
       </c>
       <c r="X97" t="n">
-        <v>1.196823</v>
+        <v>0</v>
       </c>
       <c r="Y97" t="n">
         <v>0</v>
@@ -15870,7 +15918,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>F-8</t>
+          <t>F-72</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -15925,7 +15973,7 @@
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>6.34041199</v>
       </c>
       <c r="T98" t="n">
         <v>0</v>
@@ -15949,10 +15997,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.71857377</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>6.27751246</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -15961,13 +16009,13 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0.80980442</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>0.00710324</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
-        <v>0.00036732</v>
+        <v>0</v>
       </c>
       <c r="AH98" t="n">
         <v>0</v>
@@ -15991,7 +16039,7 @@
         <v>0</v>
       </c>
       <c r="AO98" t="n">
-        <v>0.00110122</v>
+        <v>0</v>
       </c>
       <c r="AP98" t="n">
         <v>0</v>
@@ -16003,133 +16051,399 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>F-73</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" t="n">
+        <v>0</v>
+      </c>
+      <c r="V99" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" t="n">
+        <v>2.982937</v>
+      </c>
+      <c r="X99" t="n">
+        <v>1.196823</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>F-8</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="n">
+        <v>0</v>
+      </c>
+      <c r="T100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" t="n">
+        <v>0</v>
+      </c>
+      <c r="W100" t="n">
+        <v>0</v>
+      </c>
+      <c r="X100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>1.71857376</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>6.27751241</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>0.80980442</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>0.00710324</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>0.00036732</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>0.00110122</v>
+      </c>
+      <c r="AP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
           <t>F-9</t>
         </is>
       </c>
-      <c r="B99" t="n">
-        <v>0</v>
-      </c>
-      <c r="C99" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
-      <c r="R99" t="n">
-        <v>0</v>
-      </c>
-      <c r="S99" t="n">
-        <v>0.86953481</v>
-      </c>
-      <c r="T99" t="n">
+      <c r="B101" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="n">
+        <v>0.8695348000000001</v>
+      </c>
+      <c r="T101" t="n">
         <v>0.00794096</v>
       </c>
-      <c r="U99" t="n">
-        <v>0</v>
-      </c>
-      <c r="V99" t="n">
-        <v>0</v>
-      </c>
-      <c r="W99" t="n">
-        <v>0</v>
-      </c>
-      <c r="X99" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y99" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC99" t="n">
+      <c r="U101" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" t="n">
+        <v>0</v>
+      </c>
+      <c r="X101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC101" t="n">
         <v>0.00397048</v>
       </c>
-      <c r="AD99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ99" t="n">
+      <c r="AD101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ101" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16144,7 +16458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ99"/>
+  <dimension ref="A1:AQ101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -18196,10 +18510,10 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.43075105</v>
+        <v>0.43075104</v>
       </c>
       <c r="T15" t="n">
-        <v>0.56924895</v>
+        <v>0.56924896</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -22663,7 +22977,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>F-4</t>
+          <t>F-3P</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -22700,22 +23014,22 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>0.01784584</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>0.00315183</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>0.00070039</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -22724,10 +23038,10 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>0.4059953</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>0.57230663</v>
       </c>
       <c r="W49" t="n">
         <v>0</v>
@@ -22796,7 +23110,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>F-40</t>
+          <t>F-3PT</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -22833,16 +23147,16 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>0.01784584</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>0.00315183</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>0.00070039</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -22857,16 +23171,16 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>0.4059953</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>0.57230663</v>
       </c>
       <c r="W50" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
         <v>0</v>
@@ -22929,7 +23243,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>F-41</t>
+          <t>F-4</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -22966,22 +23280,22 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.00158625</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0.00028015</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>6.226e-05</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -22990,16 +23304,16 @@
         <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>0.22168451</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>0.05087023</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>0.53650265</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>0.18901395</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
         <v>0</v>
@@ -23062,7 +23376,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>F-41T</t>
+          <t>F-40</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -23099,16 +23413,16 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.00158625</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0.00028015</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>6.226e-05</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -23123,16 +23437,16 @@
         <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>0.22168451</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>0.05087023</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>0.53650265</v>
+        <v>0.79</v>
       </c>
       <c r="X52" t="n">
-        <v>0.18901395</v>
+        <v>0.21</v>
       </c>
       <c r="Y52" t="n">
         <v>0</v>
@@ -23195,7 +23509,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>F-42</t>
+          <t>F-41</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -23232,16 +23546,16 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.00244983</v>
+        <v>0.00158625</v>
       </c>
       <c r="N53" t="n">
-        <v>0.00043267</v>
+        <v>0.00028015</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>9.615000000000001e-05</v>
+        <v>6.226e-05</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -23256,16 +23570,16 @@
         <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>0.00342373</v>
+        <v>0.22168451</v>
       </c>
       <c r="V53" t="n">
-        <v>0.00957738</v>
+        <v>0.05087023</v>
       </c>
       <c r="W53" t="n">
-        <v>0.82858217</v>
+        <v>0.53650265</v>
       </c>
       <c r="X53" t="n">
-        <v>0.15543807</v>
+        <v>0.18901395</v>
       </c>
       <c r="Y53" t="n">
         <v>0</v>
@@ -23328,7 +23642,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>F-43</t>
+          <t>F-41T</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -23365,16 +23679,16 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>0.00158625</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>0.00028015</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>6.226e-05</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -23389,19 +23703,19 @@
         <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>0.22168451</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>0.05087023</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>0.53650265</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>0.18901395</v>
       </c>
       <c r="Y54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -23461,7 +23775,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>F-44</t>
+          <t>F-42</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -23498,16 +23812,16 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.00239436</v>
+        <v>0.00244983</v>
       </c>
       <c r="N55" t="n">
-        <v>0.00042288</v>
+        <v>0.00043267</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>9.397e-05</v>
+        <v>9.615000000000001e-05</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -23516,25 +23830,25 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0225769</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
         <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>0.0002088</v>
+        <v>0.00342373</v>
       </c>
       <c r="V55" t="n">
-        <v>0.0005841</v>
+        <v>0.00957738</v>
       </c>
       <c r="W55" t="n">
-        <v>0.82330524</v>
+        <v>0.82858217</v>
       </c>
       <c r="X55" t="n">
-        <v>0.14815606</v>
+        <v>0.15543807</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.00225769</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
         <v>0</v>
@@ -23594,7 +23908,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>F-45</t>
+          <t>F-43</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -23649,25 +23963,25 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
         <v>1</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>0</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -23727,7 +24041,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>F-45R</t>
+          <t>F-44</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -23764,16 +24078,16 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>0.00239436</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>0.00042288</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>9.397e-05</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -23782,25 +24096,25 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>0.0225769</v>
       </c>
       <c r="T57" t="n">
         <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>0.0002088</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>0.0005841</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>0.82330524</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>0.14815606</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>0.00225769</v>
       </c>
       <c r="Z57" t="n">
         <v>0</v>
@@ -23860,7 +24174,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>F-46</t>
+          <t>F-45</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -23897,16 +24211,16 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.00244967</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>0.00043265</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>9.614e-05</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -23915,25 +24229,25 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T58" t="n">
         <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>0.00021363</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>0.0005975899999999999</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>0.84232226</v>
+        <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>0.15157823</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.00230984</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
@@ -23993,7 +24307,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>F-47</t>
+          <t>F-45R</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -24126,7 +24440,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>F-47T</t>
+          <t>F-46</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -24163,16 +24477,16 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>0.00244967</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>0.00043265</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>9.614e-05</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -24181,25 +24495,25 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
         <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>0.00021363</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>0.0005975899999999999</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>0.84232226</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>0.15157823</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>0.00230984</v>
       </c>
       <c r="Z60" t="n">
         <v>0</v>
@@ -24259,7 +24573,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>F-48</t>
+          <t>F-47</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -24314,7 +24628,7 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.99966234</v>
+        <v>1</v>
       </c>
       <c r="T61" t="n">
         <v>0</v>
@@ -24332,7 +24646,7 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.00033766</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
         <v>0</v>
@@ -24392,7 +24706,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>F-49</t>
+          <t>F-47T</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -24429,16 +24743,16 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0.00245528</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>0.00043364</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>9.636000000000001e-05</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -24447,25 +24761,25 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" t="n">
         <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>0.00021412</v>
+        <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>0.0005989600000000001</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>0.8442528500000001</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>0.15192564</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.315e-05</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
         <v>0</v>
@@ -24525,7 +24839,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>F-49A</t>
+          <t>F-48</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -24562,16 +24876,16 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0.00245528</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>0.00043364</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>9.636000000000001e-05</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -24580,25 +24894,25 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>0.99966234</v>
       </c>
       <c r="T63" t="n">
         <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>0.00021412</v>
+        <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>0.0005989600000000001</v>
+        <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>0.8442528500000001</v>
+        <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>0.15192564</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.315e-05</v>
+        <v>0.00033766</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
@@ -24658,7 +24972,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>F-49B</t>
+          <t>F-49</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -24695,16 +25009,16 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>0.00245528</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>0.00043364</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>9.636000000000001e-05</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -24719,19 +25033,19 @@
         <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>0.00021412</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>0.0005989600000000001</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>0.8442528500000001</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>0.15192564</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.315e-05</v>
       </c>
       <c r="Z64" t="n">
         <v>0</v>
@@ -24791,7 +25105,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>F-5</t>
+          <t>F-49A</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -24828,43 +25142,43 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>0.00245528</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>0.00043364</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>9.636000000000001e-05</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.08e-06</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>0.00060621</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.87167294</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>0.04521542</v>
+        <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>0.00021412</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>0.0005989600000000001</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>0.8442528500000001</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>0.15192564</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>2.315e-05</v>
       </c>
       <c r="Z65" t="n">
         <v>0</v>
@@ -24882,37 +25196,37 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0.07882606</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>0.00074474</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>3.924e-05</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>3.13e-05</v>
+        <v>0</v>
       </c>
       <c r="AI65" t="n">
-        <v>0.00083089</v>
+        <v>0</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0.00020365</v>
+        <v>0</v>
       </c>
       <c r="AK65" t="n">
-        <v>0.00122083</v>
+        <v>0</v>
       </c>
       <c r="AL65" t="n">
-        <v>0.00024601</v>
+        <v>0</v>
       </c>
       <c r="AM65" t="n">
-        <v>3.563e-05</v>
+        <v>0</v>
       </c>
       <c r="AN65" t="n">
-        <v>2.066e-05</v>
+        <v>0</v>
       </c>
       <c r="AO65" t="n">
-        <v>0.00030533</v>
+        <v>0</v>
       </c>
       <c r="AP65" t="n">
         <v>0</v>
@@ -24924,7 +25238,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>F-50A</t>
+          <t>F-49B</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -24961,10 +25275,10 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>0.00245552</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>0.00043368</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -24985,19 +25299,19 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>0.00021414</v>
+        <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>0.00059902</v>
+        <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>0.84433421</v>
+        <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>0.15194028</v>
+        <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.315e-05</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
         <v>0</v>
@@ -25057,7 +25371,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>F-50B</t>
+          <t>F-5</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -25106,16 +25420,16 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>1.08e-06</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>0.00060621</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>0.87167294</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>0.04521542</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -25148,37 +25462,37 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>0.07882606</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>0.00074474</v>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>3.924e-05</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>3.13e-05</v>
       </c>
       <c r="AI67" t="n">
-        <v>0</v>
+        <v>0.00083089</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0</v>
+        <v>0.00020365</v>
       </c>
       <c r="AK67" t="n">
-        <v>0</v>
+        <v>0.00122083</v>
       </c>
       <c r="AL67" t="n">
-        <v>0</v>
+        <v>0.00024601</v>
       </c>
       <c r="AM67" t="n">
-        <v>0</v>
+        <v>3.563e-05</v>
       </c>
       <c r="AN67" t="n">
-        <v>0</v>
+        <v>2.066e-05</v>
       </c>
       <c r="AO67" t="n">
-        <v>0</v>
+        <v>0.00030533</v>
       </c>
       <c r="AP67" t="n">
         <v>0</v>
@@ -25190,7 +25504,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>F-51A</t>
+          <t>F-50A</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -25227,10 +25541,10 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>0.00245552</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>0.00043368</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -25251,19 +25565,19 @@
         <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>0.00021414</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>0.00059902</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>0.84433421</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>0.15194028</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>2.315e-05</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -25323,7 +25637,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>F-51B</t>
+          <t>F-50B</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -25369,7 +25683,7 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -25390,10 +25704,10 @@
         <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>0.711</v>
+        <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>0.189</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
         <v>0</v>
@@ -25456,7 +25770,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>F-52A</t>
+          <t>F-51A</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -25589,7 +25903,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>F-52B</t>
+          <t>F-51B</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -25635,7 +25949,7 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -25656,10 +25970,10 @@
         <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>0.79</v>
+        <v>0.711</v>
       </c>
       <c r="X71" t="n">
-        <v>0.21</v>
+        <v>0.189</v>
       </c>
       <c r="Y71" t="n">
         <v>0</v>
@@ -25722,7 +26036,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>F-53</t>
+          <t>F-52A</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -25771,16 +26085,16 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.17e-06</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>0.00065862</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0.94703004</v>
+        <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>0.04912435</v>
+        <v>0</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
@@ -25801,7 +26115,7 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>9.449999999999999e-06</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
         <v>0</v>
@@ -25813,37 +26127,37 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>8.564e-05</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>5.867e-05</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
-        <v>3.83e-06</v>
+        <v>0</v>
       </c>
       <c r="AH72" t="n">
-        <v>3.4e-05</v>
+        <v>0</v>
       </c>
       <c r="AI72" t="n">
-        <v>0.00090272</v>
+        <v>0</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.00022125</v>
+        <v>0</v>
       </c>
       <c r="AK72" t="n">
-        <v>0.00132637</v>
+        <v>0</v>
       </c>
       <c r="AL72" t="n">
-        <v>0.00026728</v>
+        <v>0</v>
       </c>
       <c r="AM72" t="n">
-        <v>3.871e-05</v>
+        <v>0</v>
       </c>
       <c r="AN72" t="n">
-        <v>2.245e-05</v>
+        <v>0</v>
       </c>
       <c r="AO72" t="n">
-        <v>0.00021544</v>
+        <v>0</v>
       </c>
       <c r="AP72" t="n">
         <v>0</v>
@@ -25855,7 +26169,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>F-54</t>
+          <t>F-52B</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -25922,10 +26236,10 @@
         <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="Y73" t="n">
         <v>0</v>
@@ -25934,7 +26248,7 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
         <v>0</v>
@@ -25988,7 +26302,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>F-55</t>
+          <t>F-53</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -26037,16 +26351,16 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>1.17e-06</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>0.00065862</v>
       </c>
       <c r="S74" t="n">
-        <v>0.97570606</v>
+        <v>0.94703004</v>
       </c>
       <c r="T74" t="n">
-        <v>0.00891056</v>
+        <v>0.04912435</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
@@ -26067,49 +26381,49 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.654e-05</v>
+        <v>9.449999999999999e-06</v>
       </c>
       <c r="AB74" t="n">
         <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>0.00445528</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0.00227171</v>
+        <v>8.564e-05</v>
       </c>
       <c r="AF74" t="n">
-        <v>0.00797056</v>
+        <v>5.867e-05</v>
       </c>
       <c r="AG74" t="n">
-        <v>0.00041217</v>
+        <v>3.83e-06</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>3.4e-05</v>
       </c>
       <c r="AI74" t="n">
-        <v>0</v>
+        <v>0.00090272</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0</v>
+        <v>0.00022125</v>
       </c>
       <c r="AK74" t="n">
-        <v>0</v>
+        <v>0.00132637</v>
       </c>
       <c r="AL74" t="n">
-        <v>0</v>
+        <v>0.00026728</v>
       </c>
       <c r="AM74" t="n">
-        <v>0</v>
+        <v>3.871e-05</v>
       </c>
       <c r="AN74" t="n">
-        <v>0</v>
+        <v>2.245e-05</v>
       </c>
       <c r="AO74" t="n">
-        <v>0.00024713</v>
+        <v>0.00021544</v>
       </c>
       <c r="AP74" t="n">
         <v>0</v>
@@ -26121,7 +26435,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>F-56</t>
+          <t>F-54</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -26254,7 +26568,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>F-57</t>
+          <t>F-55</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -26309,10 +26623,10 @@
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.96438903</v>
+        <v>0.97570606</v>
       </c>
       <c r="T76" t="n">
-        <v>0.0001738</v>
+        <v>0.00891056</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -26333,25 +26647,25 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>8.899999999999999e-07</v>
+        <v>2.654e-05</v>
       </c>
       <c r="AB76" t="n">
         <v>0</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>0.00445528</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0.03539771</v>
+        <v>0.00227171</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>0.00797056</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>0.00041217</v>
       </c>
       <c r="AH76" t="n">
         <v>0</v>
@@ -26375,7 +26689,7 @@
         <v>0</v>
       </c>
       <c r="AO76" t="n">
-        <v>3.858e-05</v>
+        <v>0.00024713</v>
       </c>
       <c r="AP76" t="n">
         <v>0</v>
@@ -26387,7 +26701,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>F-57T</t>
+          <t>F-56</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -26442,10 +26756,10 @@
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.96438903</v>
+        <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>0.0001738</v>
+        <v>0</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -26466,7 +26780,7 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>8.899999999999999e-07</v>
+        <v>1</v>
       </c>
       <c r="AB77" t="n">
         <v>0</v>
@@ -26478,7 +26792,7 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0.03539771</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
         <v>0</v>
@@ -26508,7 +26822,7 @@
         <v>0</v>
       </c>
       <c r="AO77" t="n">
-        <v>3.858e-05</v>
+        <v>0</v>
       </c>
       <c r="AP77" t="n">
         <v>0</v>
@@ -26520,7 +26834,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>F-58</t>
+          <t>F-57</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -26575,10 +26889,10 @@
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>0.96438903</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>0.0001738</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
@@ -26599,7 +26913,7 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1</v>
+        <v>8.899999999999999e-07</v>
       </c>
       <c r="AB78" t="n">
         <v>0</v>
@@ -26611,7 +26925,7 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>0.03539771</v>
       </c>
       <c r="AF78" t="n">
         <v>0</v>
@@ -26641,7 +26955,7 @@
         <v>0</v>
       </c>
       <c r="AO78" t="n">
-        <v>0</v>
+        <v>3.858e-05</v>
       </c>
       <c r="AP78" t="n">
         <v>0</v>
@@ -26653,7 +26967,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>F-59</t>
+          <t>F-57T</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -26708,10 +27022,10 @@
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.55135622</v>
+        <v>0.96438903</v>
       </c>
       <c r="T79" t="n">
-        <v>0.44864378</v>
+        <v>0.0001738</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -26732,7 +27046,7 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>8.899999999999999e-07</v>
       </c>
       <c r="AB79" t="n">
         <v>0</v>
@@ -26744,7 +27058,7 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>0.03539771</v>
       </c>
       <c r="AF79" t="n">
         <v>0</v>
@@ -26774,7 +27088,7 @@
         <v>0</v>
       </c>
       <c r="AO79" t="n">
-        <v>0</v>
+        <v>3.858e-05</v>
       </c>
       <c r="AP79" t="n">
         <v>0</v>
@@ -26786,7 +27100,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>F-6</t>
+          <t>F-58</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -26835,16 +27149,16 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.08e-06</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>0.00060621</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.87167294</v>
+        <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>0.04521542</v>
+        <v>0</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -26865,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB80" t="n">
         <v>0</v>
@@ -26877,37 +27191,37 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0.07882606</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>0.00074474</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>3.924e-05</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>3.13e-05</v>
+        <v>0</v>
       </c>
       <c r="AI80" t="n">
-        <v>0.00083089</v>
+        <v>0</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0.00020365</v>
+        <v>0</v>
       </c>
       <c r="AK80" t="n">
-        <v>0.00122083</v>
+        <v>0</v>
       </c>
       <c r="AL80" t="n">
-        <v>0.00024601</v>
+        <v>0</v>
       </c>
       <c r="AM80" t="n">
-        <v>3.563e-05</v>
+        <v>0</v>
       </c>
       <c r="AN80" t="n">
-        <v>2.066e-05</v>
+        <v>0</v>
       </c>
       <c r="AO80" t="n">
-        <v>0.00030533</v>
+        <v>0</v>
       </c>
       <c r="AP80" t="n">
         <v>0</v>
@@ -26919,7 +27233,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>F-60</t>
+          <t>F-59</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -26974,10 +27288,10 @@
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>1</v>
+        <v>0.55135622</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>0.44864378</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -27052,7 +27366,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>F-61</t>
+          <t>F-6</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -27101,16 +27415,16 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>1.08e-06</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>0.00060621</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>0.87167294</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>0.04521542</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
@@ -27131,7 +27445,7 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
         <v>0</v>
@@ -27143,37 +27457,37 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>0.07882606</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>0.00074474</v>
       </c>
       <c r="AG82" t="n">
-        <v>0</v>
+        <v>3.924e-05</v>
       </c>
       <c r="AH82" t="n">
-        <v>0</v>
+        <v>3.13e-05</v>
       </c>
       <c r="AI82" t="n">
-        <v>0</v>
+        <v>0.00083089</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0</v>
+        <v>0.00020365</v>
       </c>
       <c r="AK82" t="n">
-        <v>0</v>
+        <v>0.00122083</v>
       </c>
       <c r="AL82" t="n">
-        <v>0</v>
+        <v>0.00024601</v>
       </c>
       <c r="AM82" t="n">
-        <v>0</v>
+        <v>3.563e-05</v>
       </c>
       <c r="AN82" t="n">
-        <v>0</v>
+        <v>2.066e-05</v>
       </c>
       <c r="AO82" t="n">
-        <v>0</v>
+        <v>0.00030533</v>
       </c>
       <c r="AP82" t="n">
         <v>0</v>
@@ -27185,7 +27499,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>F-62</t>
+          <t>F-60</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -27240,7 +27554,7 @@
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T83" t="n">
         <v>0</v>
@@ -27264,10 +27578,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0.21513093</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>0.78486899</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -27276,7 +27590,7 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
         <v>0</v>
@@ -27306,7 +27620,7 @@
         <v>0</v>
       </c>
       <c r="AO83" t="n">
-        <v>7e-08</v>
+        <v>0</v>
       </c>
       <c r="AP83" t="n">
         <v>0</v>
@@ -27318,7 +27632,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>F-63</t>
+          <t>F-61</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -27355,16 +27669,16 @@
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>0.01784584</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>0.00315183</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>0.00070039</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -27379,10 +27693,10 @@
         <v>0</v>
       </c>
       <c r="U84" t="n">
-        <v>0.4059953</v>
+        <v>0</v>
       </c>
       <c r="V84" t="n">
-        <v>0.57230663</v>
+        <v>0</v>
       </c>
       <c r="W84" t="n">
         <v>0</v>
@@ -27397,7 +27711,7 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB84" t="n">
         <v>0</v>
@@ -27451,7 +27765,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>F-63P</t>
+          <t>F-62</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -27488,16 +27802,16 @@
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>0.01784584</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>0.00315183</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>0.00070039</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -27512,10 +27826,10 @@
         <v>0</v>
       </c>
       <c r="U85" t="n">
-        <v>0.4059953</v>
+        <v>0</v>
       </c>
       <c r="V85" t="n">
-        <v>0.57230663</v>
+        <v>0</v>
       </c>
       <c r="W85" t="n">
         <v>0</v>
@@ -27530,10 +27844,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>0.21513093</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>0.78486899</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -27542,7 +27856,7 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="AF85" t="n">
         <v>0</v>
@@ -27572,7 +27886,7 @@
         <v>0</v>
       </c>
       <c r="AO85" t="n">
-        <v>0</v>
+        <v>7e-08</v>
       </c>
       <c r="AP85" t="n">
         <v>0</v>
@@ -27584,7 +27898,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>F-64</t>
+          <t>F-63</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -27621,16 +27935,16 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>0.01784584</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>0.00315183</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>0.00070039</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -27639,16 +27953,16 @@
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.95096888</v>
+        <v>0</v>
       </c>
       <c r="T86" t="n">
         <v>0</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>0.4059953</v>
       </c>
       <c r="V86" t="n">
-        <v>0</v>
+        <v>0.57230663</v>
       </c>
       <c r="W86" t="n">
         <v>0</v>
@@ -27675,7 +27989,7 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0.04903112</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
         <v>0</v>
@@ -27717,7 +28031,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>F-65</t>
+          <t>F-63P</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -27754,16 +28068,16 @@
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>0.01784584</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>0.00315183</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>0.00070039</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -27772,16 +28086,16 @@
         <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T87" t="n">
         <v>0</v>
       </c>
       <c r="U87" t="n">
-        <v>0</v>
+        <v>0.4059953</v>
       </c>
       <c r="V87" t="n">
-        <v>0</v>
+        <v>0.57230663</v>
       </c>
       <c r="W87" t="n">
         <v>0</v>
@@ -27850,7 +28164,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>F-66</t>
+          <t>F-64</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -27905,7 +28219,7 @@
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>1</v>
+        <v>0.95096888</v>
       </c>
       <c r="T88" t="n">
         <v>0</v>
@@ -27941,7 +28255,7 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>0.04903112</v>
       </c>
       <c r="AF88" t="n">
         <v>0</v>
@@ -27983,7 +28297,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>F-67</t>
+          <t>F-65</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -28116,7 +28430,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>F-68</t>
+          <t>F-66</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -28171,7 +28485,7 @@
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>0.91769265</v>
+        <v>1</v>
       </c>
       <c r="T90" t="n">
         <v>0</v>
@@ -28207,7 +28521,7 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0.08230735</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
         <v>0</v>
@@ -28249,7 +28563,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>F-69</t>
+          <t>F-67</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -28382,7 +28696,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>F-6P</t>
+          <t>F-68</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -28431,16 +28745,16 @@
         <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.08e-06</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>0.00060621</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>0.87167294</v>
+        <v>0.91769265</v>
       </c>
       <c r="T92" t="n">
-        <v>0.04521542</v>
+        <v>0</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -28473,37 +28787,37 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0.07882606</v>
+        <v>0.08230735</v>
       </c>
       <c r="AF92" t="n">
-        <v>0.00074474</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
-        <v>3.924e-05</v>
+        <v>0</v>
       </c>
       <c r="AH92" t="n">
-        <v>3.13e-05</v>
+        <v>0</v>
       </c>
       <c r="AI92" t="n">
-        <v>0.00083089</v>
+        <v>0</v>
       </c>
       <c r="AJ92" t="n">
-        <v>0.00020365</v>
+        <v>0</v>
       </c>
       <c r="AK92" t="n">
-        <v>0.00122083</v>
+        <v>0</v>
       </c>
       <c r="AL92" t="n">
-        <v>0.00024601</v>
+        <v>0</v>
       </c>
       <c r="AM92" t="n">
-        <v>3.563e-05</v>
+        <v>0</v>
       </c>
       <c r="AN92" t="n">
-        <v>2.066e-05</v>
+        <v>0</v>
       </c>
       <c r="AO92" t="n">
-        <v>0.00030533</v>
+        <v>0</v>
       </c>
       <c r="AP92" t="n">
         <v>0</v>
@@ -28515,7 +28829,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>F-7</t>
+          <t>F-69</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -28570,7 +28884,7 @@
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T93" t="n">
         <v>0</v>
@@ -28594,10 +28908,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0.21514402</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>0.78485591</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -28606,7 +28920,7 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
         <v>0</v>
@@ -28636,7 +28950,7 @@
         <v>0</v>
       </c>
       <c r="AO93" t="n">
-        <v>5.999999999999999e-08</v>
+        <v>0</v>
       </c>
       <c r="AP93" t="n">
         <v>0</v>
@@ -28648,7 +28962,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>F-70</t>
+          <t>F-6P</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -28697,16 +29011,16 @@
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>1.08e-06</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>0.00060621</v>
       </c>
       <c r="S94" t="n">
-        <v>1</v>
+        <v>0.87167294</v>
       </c>
       <c r="T94" t="n">
-        <v>0</v>
+        <v>0.04521542</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -28739,37 +29053,37 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>0.07882606</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>0.00074474</v>
       </c>
       <c r="AG94" t="n">
-        <v>0</v>
+        <v>3.924e-05</v>
       </c>
       <c r="AH94" t="n">
-        <v>0</v>
+        <v>3.13e-05</v>
       </c>
       <c r="AI94" t="n">
-        <v>0</v>
+        <v>0.00083089</v>
       </c>
       <c r="AJ94" t="n">
-        <v>0</v>
+        <v>0.00020365</v>
       </c>
       <c r="AK94" t="n">
-        <v>0</v>
+        <v>0.00122083</v>
       </c>
       <c r="AL94" t="n">
-        <v>0</v>
+        <v>0.00024601</v>
       </c>
       <c r="AM94" t="n">
-        <v>0</v>
+        <v>3.563e-05</v>
       </c>
       <c r="AN94" t="n">
-        <v>0</v>
+        <v>2.066e-05</v>
       </c>
       <c r="AO94" t="n">
-        <v>0</v>
+        <v>0.00030533</v>
       </c>
       <c r="AP94" t="n">
         <v>0</v>
@@ -28781,7 +29095,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>F-71</t>
+          <t>F-7</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -28836,7 +29150,7 @@
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T95" t="n">
         <v>0</v>
@@ -28860,10 +29174,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>0.21514402</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>0.78485591</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -28872,7 +29186,7 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="AF95" t="n">
         <v>0</v>
@@ -28902,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="AO95" t="n">
-        <v>0</v>
+        <v>5.999999999999999e-08</v>
       </c>
       <c r="AP95" t="n">
         <v>0</v>
@@ -28914,7 +29228,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>F-72</t>
+          <t>F-70</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -29047,7 +29361,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>F-73</t>
+          <t>F-71</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -29102,7 +29416,7 @@
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T97" t="n">
         <v>0</v>
@@ -29114,10 +29428,10 @@
         <v>0</v>
       </c>
       <c r="W97" t="n">
-        <v>0.71366227</v>
+        <v>0</v>
       </c>
       <c r="X97" t="n">
-        <v>0.28633773</v>
+        <v>0</v>
       </c>
       <c r="Y97" t="n">
         <v>0</v>
@@ -29180,7 +29494,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>F-8</t>
+          <t>F-72</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -29235,7 +29549,7 @@
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T98" t="n">
         <v>0</v>
@@ -29259,10 +29573,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0.19497205</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>0.71218324</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -29271,13 +29585,13 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0.09187223999999999</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>0.00080586</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
-        <v>4.167e-05</v>
+        <v>0</v>
       </c>
       <c r="AH98" t="n">
         <v>0</v>
@@ -29301,7 +29615,7 @@
         <v>0</v>
       </c>
       <c r="AO98" t="n">
-        <v>0.00012493</v>
+        <v>0</v>
       </c>
       <c r="AP98" t="n">
         <v>0</v>
@@ -29313,133 +29627,399 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>F-73</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" t="n">
+        <v>0</v>
+      </c>
+      <c r="V99" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" t="n">
+        <v>0.71366227</v>
+      </c>
+      <c r="X99" t="n">
+        <v>0.28633773</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>F-8</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="n">
+        <v>0</v>
+      </c>
+      <c r="T100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" t="n">
+        <v>0</v>
+      </c>
+      <c r="W100" t="n">
+        <v>0</v>
+      </c>
+      <c r="X100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>0.19497205</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>0.71218324</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>0.09187223999999999</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>0.00080586</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>4.167e-05</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>0.00012493</v>
+      </c>
+      <c r="AP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
           <t>F-9</t>
         </is>
       </c>
-      <c r="B99" t="n">
-        <v>0</v>
-      </c>
-      <c r="C99" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
-      <c r="R99" t="n">
-        <v>0</v>
-      </c>
-      <c r="S99" t="n">
+      <c r="B101" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="n">
         <v>0.98648649</v>
       </c>
-      <c r="T99" t="n">
+      <c r="T101" t="n">
         <v>0.00900901</v>
       </c>
-      <c r="U99" t="n">
-        <v>0</v>
-      </c>
-      <c r="V99" t="n">
-        <v>0</v>
-      </c>
-      <c r="W99" t="n">
-        <v>0</v>
-      </c>
-      <c r="X99" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y99" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC99" t="n">
+      <c r="U101" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" t="n">
+        <v>0</v>
+      </c>
+      <c r="X101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC101" t="n">
         <v>0.0045045</v>
       </c>
-      <c r="AD99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ99" t="n">
+      <c r="AD101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ101" t="n">
         <v>0</v>
       </c>
     </row>
@@ -29454,7 +30034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -29678,12 +30258,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V103_OffgasSurge</t>
+          <t>V103P_OffgasPressure</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PassThrough</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -29693,7 +30273,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>out=F-63</t>
+          <t>out=F-3P</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -29701,22 +30281,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P104_OffgasBlower</t>
+          <t>V103T_OffgasTemperature</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PassThrough</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>in=F-63</t>
+          <t>in=F-3P</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>out=F-63P</t>
+          <t>out=F-3PT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -29724,22 +30304,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M114_SolventMakeupMixer</t>
+          <t>V103_OffgasSurge</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>PassThrough</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>makeup=F-16, recycle=F-15</t>
+          <t>in=F-3PT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>out=F-7</t>
+          <t>out=F-63</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -29747,22 +30327,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M_X101_feed</t>
+          <t>P104_OffgasBlower</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>PassThrough</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>aq=F-6P, org=F-7</t>
+          <t>in=F-63</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>out=F_X101</t>
+          <t>out=F-63P</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -29770,22 +30350,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X101_TBP_Extraction</t>
+          <t>M114_SolventMakeupMixer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SplitUnit</t>
+          <t>Mixer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>in=F_X101</t>
+          <t>makeup=F-16, recycle=F-15</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>organic=F-8, aqueous=F-17</t>
+          <t>out=F-7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -29793,22 +30373,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CF101_Coalescer</t>
+          <t>M_X101_feed</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Coalescer</t>
+          <t>Mixer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>in=F-17</t>
+          <t>aq=F-6P, org=F-7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>aqueous=F-53, recovered_org=F-54</t>
+          <t>out=F_X101</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -29816,49 +30396,45 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E102_RaffinateEvaporator</t>
+          <t>X101_TBP_Extraction</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Evaporator</t>
+          <t>SplitUnit</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>in=F-53</t>
+          <t>in=F_X101</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>vapour=F-20, liquid=F-19</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>F_vapour_mol_s=0.4592; F_liquid_mol_s=9.006</t>
-        </is>
-      </c>
+          <t>organic=F-8, aqueous=F-17</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M_X102_feed</t>
+          <t>CF101_Coalescer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>Coalescer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>org=F-8, aq=F-9</t>
+          <t>in=F-17</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>out=F_X102</t>
+          <t>aqueous=F-53, recovered_org=F-54</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -29866,45 +30442,49 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X102_AHA_Strip</t>
+          <t>E102_RaffinateEvaporator</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SplitUnit</t>
+          <t>Evaporator</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>in=F_X102</t>
+          <t>in=F-53</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>aqueous=F-18, organic=F-10</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>vapour=F-20, liquid=F-19</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>F_vapour_mol_s=0.4592; F_liquid_mol_s=9.006</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CF102_Coalescer</t>
+          <t>M_X102_feed</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Coalescer</t>
+          <t>Mixer</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>in=F-18</t>
+          <t>org=F-8, aq=F-9</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>aqueous=F-55, recovered_org=F-56</t>
+          <t>out=F_X102</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -29912,49 +30492,45 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EV101_PuNpEvaporator</t>
+          <t>X102_AHA_Strip</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Evaporator</t>
+          <t>SplitUnit</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>in=F-55</t>
+          <t>in=F_X102</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>vapour=F-22, liquid=F-21</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>F_vapour_mol_s=0.01212; F_liquid_mol_s=0.8811</t>
-        </is>
-      </c>
+          <t>aqueous=F-18, organic=F-10</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M201_EvapOverheadMixer</t>
+          <t>CF102_Coalescer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>Coalescer</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>e101=F-20, e102=F-22</t>
+          <t>in=F-18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>out=F-23T</t>
+          <t>aqueous=F-55, recovered_org=F-56</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -29962,30 +30538,34 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B101_OverheadBlower</t>
+          <t>EV101_PuNpEvaporator</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PassThrough</t>
+          <t>Evaporator</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>in=F-23T</t>
+          <t>in=F-55</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>out=F-23TP</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>vapour=F-22, liquid=F-21</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>F_vapour_mol_s=0.01212; F_liquid_mol_s=0.8811</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M_X103_feed</t>
+          <t>M201_EvapOverheadMixer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -29995,12 +30575,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>org=F-10, aq=F-11</t>
+          <t>e101=F-20, e102=F-22</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>out=F_X103</t>
+          <t>out=F-23T</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -30008,22 +30588,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X103_Final_Strip</t>
+          <t>B101_OverheadBlower</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SplitUnit</t>
+          <t>PassThrough</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>in=F_X103</t>
+          <t>in=F-23T</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>aqueous=F-12, organic=F-13</t>
+          <t>out=F-23TP</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -30031,22 +30611,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CF103_Coalescer</t>
+          <t>M_X103_feed</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Coalescer</t>
+          <t>Mixer</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>in=F-12</t>
+          <t>org=F-10, aq=F-11</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>aqueous=F-57, recovered_org=F-58</t>
+          <t>out=F_X103</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -30054,22 +30634,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>E107_UFeedHeater</t>
+          <t>X103_Final_Strip</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>SplitUnit</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>in=F-57</t>
+          <t>in=F_X103</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>out=F-57T</t>
+          <t>aqueous=F-12, organic=F-13</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -30077,22 +30657,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>E107_SteamCondensate</t>
+          <t>CF103_Coalescer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PassThrough</t>
+          <t>Coalescer</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>in=U67_src</t>
+          <t>in=F-12</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>out=F-67</t>
+          <t>aqueous=F-57, recovered_org=F-58</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -30100,22 +30680,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EV103A_UConcentrator1</t>
+          <t>E107_UFeedHeater</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SplitUnit</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>in=F-57T</t>
+          <t>in=F-57</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>vapour=F-65, to_raw=F-64_raw</t>
+          <t>out=F-57T</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -30123,22 +30703,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EV103A_InternalCleaner</t>
+          <t>E107_SteamCondensate</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SplitUnit</t>
+          <t>PassThrough</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>in=F-64_raw</t>
+          <t>in=U67_src</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>aux=F-64_aux, clean=F-64</t>
+          <t>out=F-67</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -30146,22 +30726,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EV103A_CondensatePass</t>
+          <t>EV103A_UConcentrator1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PassThrough</t>
+          <t>SplitUnit</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>in=F-67</t>
+          <t>in=F-57T</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>out=F-69</t>
+          <t>vapour=F-65, to_raw=F-64_raw</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -30169,7 +30749,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EV103B_UConcentrator2</t>
+          <t>EV103A_InternalCleaner</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -30179,12 +30759,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>in=F-64</t>
+          <t>in=F-64_raw</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>to_C1=F-66, to_C2=F-68</t>
+          <t>aux=F-64_aux, clean=F-64</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -30192,7 +30772,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EV103B_OverheadPass</t>
+          <t>EV103A_CondensatePass</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -30202,12 +30782,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>in=F-65</t>
+          <t>in=F-67</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>out=F-72</t>
+          <t>out=F-69</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -30215,22 +30795,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EV103C_UConcentrator3</t>
+          <t>EV103B_UConcentrator2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EV103CPerformanceStage</t>
+          <t>SplitUnit</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>light=F-66, heavy=F-68, aux=F-64_aux</t>
+          <t>in=F-64</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>product=F-24, vapour=F-25, waste=F-70, sink=F-70_sink</t>
+          <t>to_C1=F-66, to_C2=F-68</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -30238,22 +30818,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>M272_EV103_WasteMixer</t>
+          <t>EV103B_OverheadPass</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>PassThrough</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>a=F-69, b=F-72, c=F-70</t>
+          <t>in=F-65</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>out=F-71</t>
+          <t>out=F-72</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -30261,22 +30841,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>P105_UProductPump</t>
+          <t>EV103C_UConcentrator3</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PassThrough</t>
+          <t>EV103CPerformanceStage</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>in=F-24</t>
+          <t>light=F-66, heavy=F-68, aux=F-64_aux</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>out=F-24P</t>
+          <t>product=F-24, vapour=F-25, waste=F-70, sink=F-70_sink</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -30284,22 +30864,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>E109_UProductHeater</t>
+          <t>M272_EV103_WasteMixer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>Mixer</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>in=F-24P</t>
+          <t>a=F-69, b=F-72, c=F-70</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>out=F-24PT</t>
+          <t>out=F-71</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -30307,22 +30887,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>R101_ThermalReactor</t>
+          <t>P105_UProductPump</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CalcinerReactor</t>
+          <t>PassThrough</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>in=F-24PT, air=F-73</t>
+          <t>in=F-24</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>solids=F-26, offgas=F-29</t>
+          <t>out=F-24P</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -30330,22 +30910,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>P106_ReactorOffgasBlower</t>
+          <t>E109_UProductHeater</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PassThrough</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>in=F-29</t>
+          <t>in=F-24P</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>out=F-29P</t>
+          <t>out=F-24PT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -30353,22 +30933,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>E111_ReactorOffgasCooler</t>
+          <t>R101_ThermalReactor</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>CalcinerReactor</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>in=F-29P</t>
+          <t>in=F-24PT, air=F-73</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>out=F-29TP</t>
+          <t>solids=F-26, offgas=F-29</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -30376,22 +30956,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>E110_ProductCooler</t>
+          <t>P106_ReactorOffgasBlower</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>PassThrough</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>in=F-26</t>
+          <t>in=F-29</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>out=F-26T</t>
+          <t>out=F-29P</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -30399,22 +30979,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>K101_UProductSeparator</t>
+          <t>E111_ReactorOffgasCooler</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ConversionReactor</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>in=F-26T</t>
+          <t>in=F-29P</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>solid=F-27, gas=F-28, liquid=F-28</t>
+          <t>out=F-29TP</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -30422,22 +31002,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>M301_HotVapourMixer</t>
+          <t>E110_ProductCooler</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>evaps=F-23TP, ucon=F-25, calc=F-29TP</t>
+          <t>in=F-26</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>out=F-30TP</t>
+          <t>out=F-26T</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -30445,22 +31025,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>K301_Condenser</t>
+          <t>K101_UProductSeparator</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PhaseCondenser</t>
+          <t>ConversionReactor</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>in=F-30TP</t>
+          <t>in=F-26T</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>liquid=F-31, gas=F-32</t>
+          <t>solid=F-27, gas=F-28, liquid=F-28</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -30468,7 +31048,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>M302_OffgasMixer</t>
+          <t>M301_HotVapourMixer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -30478,12 +31058,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>cond=F-32, diss=F-63P, air=F-40</t>
+          <t>evaps=F-23TP, ucon=F-25, calc=F-29TP</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>out=F-41</t>
+          <t>out=F-30TP</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -30491,22 +31071,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>E113_OffgasCooler</t>
+          <t>K301_Condenser</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>PhaseCondenser</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>in=F-41</t>
+          <t>in=F-30TP</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>out=F-41T</t>
+          <t>liquid=F-31, gas=F-32</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -30514,49 +31094,45 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>D101_NO2_Absorber</t>
+          <t>M302_OffgasMixer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NOxAbsorber</t>
+          <t>Mixer</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>gas=F-41T, water=F-39</t>
+          <t>cond=F-32, diss=F-63P, air=F-40</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>gas_out=F-42, aqueous=F-35</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>NO2_captured_mol_s=1.91; NO_captured_mol_s=1.026; HNO3_produced_mol_s=2.299</t>
-        </is>
-      </c>
+          <t>out=F-41</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>M303_AcidMixer</t>
+          <t>E113_OffgasCooler</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>abs=F-35, cond=F-31</t>
+          <t>in=F-41</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>out=F-36</t>
+          <t>out=F-41T</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -30564,72 +31140,72 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>E118_AcidTrimHeater</t>
+          <t>D101_NO2_Absorber</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>NOxAbsorber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>in=F-36</t>
+          <t>gas=F-41T, water=F-39</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>out=F-36T</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>gas_out=F-42, aqueous=F-35</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>NO2_captured_mol_s=1.91; NO_captured_mol_s=1.026; HNO3_produced_mol_s=2.299</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>E104_HNO3_Concentrator</t>
+          <t>M303_AcidMixer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AcidConcentrator</t>
+          <t>Mixer</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>in=F-36T</t>
+          <t>abs=F-35, cond=F-31</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>concentrated=F-38, steam=F-37</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>H2O_evaporated_mol_s=24.39; HNO3_conc_mol_s=2.564; actual_HNO3_mass_frac=0.74</t>
-        </is>
-      </c>
+          <t>out=F-36</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>V104_AcidPurge</t>
+          <t>E118_AcidTrimHeater</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PurgeSplitter</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>in=F-38</t>
+          <t>in=F-36</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>purge=F-59, recycle=F-2R</t>
+          <t>out=F-36T</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -30637,49 +31213,49 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>R103_NOxReduction</t>
+          <t>E104_HNO3_Concentrator</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SCRReactor</t>
+          <t>AcidConcentrator</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>gas=F-42, nh3=F-43</t>
+          <t>in=F-36T</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>out=F-44</t>
+          <t>concentrated=F-38, steam=F-37</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>NO_removed_mol_s=0.05061; NO2_removed_mol_s=0.01809; NH3_consumed_mol_s=0.0868; N2_produced_mol_s=0.07775</t>
+          <t>H2O_evaporated_mol_s=24.39; HNO3_conc_mol_s=2.564; actual_HNO3_mass_frac=0.74</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KO101_KnockoutPot</t>
+          <t>V104_AcidPurge</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KnockoutPot</t>
+          <t>PurgeSplitter</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>in=F-44</t>
+          <t>in=F-38</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>gas=F-46, liquid=F-45</t>
+          <t>purge=F-59, recycle=F-2R</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -30687,45 +31263,49 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>V105_KOWaterPurge</t>
+          <t>R103_NOxReduction</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PurgeSplitter</t>
+          <t>SCRReactor</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>in=F-45</t>
+          <t>gas=F-42, nh3=F-43</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>purge=F-60, recycle=F-45R</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
+          <t>out=F-44</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>NO_removed_mol_s=0.05061; NO2_removed_mol_s=0.01809; NH3_consumed_mol_s=0.0868; N2_produced_mol_s=0.07775</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>E116_D102WaterHeater</t>
+          <t>KO101_KnockoutPot</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>KnockoutPot</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>in=F-47</t>
+          <t>in=F-44</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>out=F-47T</t>
+          <t>gas=F-46, liquid=F-45</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -30733,49 +31313,45 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>D102_NH3_Absorber</t>
+          <t>V105_KOWaterPurge</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NH3Absorber</t>
+          <t>PurgeSplitter</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>gas=F-46, water=F-47T</t>
+          <t>in=F-45</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>gas_out=F-49, aqueous=F-48</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>NH3_captured_mol_s=0.01289</t>
-        </is>
-      </c>
+          <t>purge=F-60, recycle=F-45R</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>V201_TSA_Split</t>
+          <t>E116_D102WaterHeater</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SplitUnit</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>in=F-49</t>
+          <t>in=F-47</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>A=F-49A, B=F-49B</t>
+          <t>out=F-47T</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -30783,107 +31359,111 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TSA101A</t>
+          <t>D102_NH3_Absorber</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TSAColumn</t>
+          <t>NH3Absorber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>process_gas=F-49A, regen_air=F-52A</t>
+          <t>gas=F-46, water=F-47T</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>process_out=F-50A, regen_out=F-51A</t>
+          <t>gas_out=F-49, aqueous=F-48</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>I_captured_mol_s=0.0005419; I_slip_mol_s=0</t>
+          <t>NH3_captured_mol_s=0.01289</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TSA101B</t>
+          <t>V201_TSA_Split</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TSAColumn</t>
+          <t>SplitUnit</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>process_gas=F-49B, regen_air=F-52B</t>
+          <t>in=F-49</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>process_out=F-50B, regen_out=F-51B</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>I_captured_mol_s=0; I_slip_mol_s=0</t>
-        </is>
-      </c>
+          <t>A=F-49A, B=F-49B</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>M_StackGasMixer</t>
+          <t>TSA101A</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>TSAColumn</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>A=F-50A, B=F-50B</t>
+          <t>process_gas=F-49A, regen_air=F-52A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>out=F_StackGas</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>process_out=F-50A, regen_out=F-51A</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>I_captured_mol_s=0.0005419; I_slip_mol_s=0</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>M132_SolventRecoveryMixer</t>
+          <t>TSA101B</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>TSAColumn</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>c1=F-54, c2=F-56, c3=F-58</t>
+          <t>process_gas=F-49B, regen_air=F-52B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>out=F-61</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>process_out=F-50B, regen_out=F-51B</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>I_captured_mol_s=0; I_slip_mol_s=0</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>M133_SolventMixer</t>
+          <t>M_StackGasMixer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -30893,12 +31473,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>main=F-13, rec=F-61</t>
+          <t>A=F-50A, B=F-50B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>out=F-62</t>
+          <t>out=F_StackGas</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -30906,22 +31486,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>HX133_SolventCooler</t>
+          <t>M132_SolventRecoveryMixer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>Mixer</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>in=F-62</t>
+          <t>c1=F-54, c2=F-56, c3=F-58</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>out=F-13T</t>
+          <t>out=F-61</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -30929,25 +31509,71 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>M133_SolventMixer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Mixer</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>main=F-13, rec=F-61</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>out=F-62</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>HX133_SolventCooler</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Conditioner</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>in=F-62</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>out=F-13T</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>V133_SolventPurge</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>PurgeSplitter</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>in=F-13T</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>purge=F-14, recycle=F-15</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/process_sim/results/stream_results.xlsx
+++ b/process_sim/results/stream_results.xlsx
@@ -428,12 +428,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
@@ -516,7 +516,7 @@
         <v>8.804575</v>
       </c>
       <c r="F3" t="n">
-        <v>1845.390781</v>
+        <v>1845.390794</v>
       </c>
     </row>
     <row r="4">
@@ -540,7 +540,7 @@
         <v>22.011438</v>
       </c>
       <c r="F4" t="n">
-        <v>396.714515</v>
+        <v>396.714518</v>
       </c>
     </row>
     <row r="5">
@@ -564,7 +564,7 @@
         <v>22.824394</v>
       </c>
       <c r="F5" t="n">
-        <v>716.296459</v>
+        <v>716.296462</v>
       </c>
     </row>
     <row r="6">
@@ -588,7 +588,7 @@
         <v>7.991619</v>
       </c>
       <c r="F6" t="n">
-        <v>1525.808836</v>
+        <v>1525.808849</v>
       </c>
     </row>
     <row r="7">
@@ -612,7 +612,7 @@
         <v>7.998166</v>
       </c>
       <c r="F7" t="n">
-        <v>1527.552422</v>
+        <v>1527.552435</v>
       </c>
     </row>
     <row r="8">
@@ -636,7 +636,7 @@
         <v>0.399908</v>
       </c>
       <c r="F8" t="n">
-        <v>76.377621</v>
+        <v>76.377622</v>
       </c>
     </row>
     <row r="9">
@@ -660,7 +660,7 @@
         <v>7.598258</v>
       </c>
       <c r="F9" t="n">
-        <v>1451.174801</v>
+        <v>1451.174813</v>
       </c>
     </row>
     <row r="10">
@@ -684,7 +684,7 @@
         <v>0.400041</v>
       </c>
       <c r="F10" t="n">
-        <v>76.413056</v>
+        <v>76.413014</v>
       </c>
     </row>
     <row r="11">
@@ -708,7 +708,7 @@
         <v>9.467428</v>
       </c>
       <c r="F11" t="n">
-        <v>200.345319</v>
+        <v>200.345321</v>
       </c>
     </row>
     <row r="12">
@@ -756,7 +756,7 @@
         <v>9.006129</v>
       </c>
       <c r="F13" t="n">
-        <v>179.746302</v>
+        <v>179.746303</v>
       </c>
     </row>
     <row r="14">
@@ -780,7 +780,7 @@
         <v>9.632023</v>
       </c>
       <c r="F14" t="n">
-        <v>305.650224</v>
+        <v>305.650226</v>
       </c>
     </row>
     <row r="15">
@@ -924,7 +924,7 @@
         <v>3.015401</v>
       </c>
       <c r="F20" t="n">
-        <v>358.215039</v>
+        <v>358.215153</v>
       </c>
     </row>
     <row r="21">
@@ -948,7 +948,7 @@
         <v>3.015401</v>
       </c>
       <c r="F21" t="n">
-        <v>358.215039</v>
+        <v>358.215153</v>
       </c>
     </row>
     <row r="22">
@@ -972,7 +972,7 @@
         <v>3.015401</v>
       </c>
       <c r="F22" t="n">
-        <v>358.215039</v>
+        <v>358.215153</v>
       </c>
     </row>
     <row r="23">
@@ -996,7 +996,7 @@
         <v>6.803605</v>
       </c>
       <c r="F23" t="n">
-        <v>122.566944</v>
+        <v>122.566945</v>
       </c>
     </row>
     <row r="24">
@@ -1020,7 +1020,7 @@
         <v>0.814654</v>
       </c>
       <c r="F24" t="n">
-        <v>231.321089</v>
+        <v>231.321203</v>
       </c>
     </row>
     <row r="25">
@@ -1044,7 +1044,7 @@
         <v>0.814654</v>
       </c>
       <c r="F25" t="n">
-        <v>231.321089</v>
+        <v>231.321203</v>
       </c>
     </row>
     <row r="26">
@@ -1092,7 +1092,7 @@
         <v>0.141504</v>
       </c>
       <c r="F27" t="n">
-        <v>4.582942</v>
+        <v>4.583056</v>
       </c>
     </row>
     <row r="28">
@@ -1260,7 +1260,7 @@
         <v>9.632023</v>
       </c>
       <c r="F34" t="n">
-        <v>305.650224</v>
+        <v>305.650226</v>
       </c>
     </row>
     <row r="35">
@@ -1284,7 +1284,7 @@
         <v>9.632023</v>
       </c>
       <c r="F35" t="n">
-        <v>305.650224</v>
+        <v>305.650226</v>
       </c>
     </row>
     <row r="36">
@@ -1308,7 +1308,7 @@
         <v>9.632023</v>
       </c>
       <c r="F36" t="n">
-        <v>305.650224</v>
+        <v>305.650226</v>
       </c>
     </row>
     <row r="37">
@@ -1356,7 +1356,7 @@
         <v>3.391888</v>
       </c>
       <c r="F38" t="n">
-        <v>61.104868</v>
+        <v>61.10487</v>
       </c>
     </row>
     <row r="39">
@@ -1404,7 +1404,7 @@
         <v>15.270966</v>
       </c>
       <c r="F40" t="n">
-        <v>378.783609</v>
+        <v>378.78361</v>
       </c>
     </row>
     <row r="41">
@@ -1428,7 +1428,7 @@
         <v>9.475647</v>
       </c>
       <c r="F41" t="n">
-        <v>182.599846</v>
+        <v>182.599848</v>
       </c>
     </row>
     <row r="42">
@@ -1500,7 +1500,7 @@
         <v>30.100369</v>
       </c>
       <c r="F44" t="n">
-        <v>657.612198</v>
+        <v>657.6122</v>
       </c>
     </row>
     <row r="45">
@@ -1524,7 +1524,7 @@
         <v>30.100369</v>
       </c>
       <c r="F45" t="n">
-        <v>657.612198</v>
+        <v>657.6122</v>
       </c>
     </row>
     <row r="46">
@@ -1548,7 +1548,7 @@
         <v>24.386271</v>
       </c>
       <c r="F46" t="n">
-        <v>439.318676</v>
+        <v>439.318677</v>
       </c>
     </row>
     <row r="47">
@@ -1602,38 +1602,38 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>F-3P</t>
+          <t>F-4</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>373.15</v>
       </c>
       <c r="C49" t="n">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.773725</v>
+        <v>0.125091</v>
       </c>
       <c r="F49" t="n">
-        <v>29.893158</v>
+        <v>11.411308</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>F-3PT</t>
+          <t>F-40</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>298.15</v>
       </c>
       <c r="C50" t="n">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1641,44 +1641,44 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.773725</v>
+        <v>2.135616</v>
       </c>
       <c r="F50" t="n">
-        <v>29.893158</v>
+        <v>61.613895</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>F-4</t>
+          <t>F-41</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>373.15</v>
+        <v>298.15</v>
       </c>
       <c r="C51" t="n">
         <v>100000</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.125091</v>
+        <v>8.704661</v>
       </c>
       <c r="F51" t="n">
-        <v>11.411308</v>
+        <v>287.690816</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>F-40</t>
+          <t>F-41T</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>298.15</v>
+        <v>313.15</v>
       </c>
       <c r="C52" t="n">
         <v>100000</v>
@@ -1689,20 +1689,20 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2.135616</v>
+        <v>8.704661</v>
       </c>
       <c r="F52" t="n">
-        <v>61.613895</v>
+        <v>287.690816</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>F-41</t>
+          <t>F-42</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>298.15</v>
+        <v>313.15</v>
       </c>
       <c r="C53" t="n">
         <v>100000</v>
@@ -1713,20 +1713,20 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>8.704661</v>
+        <v>5.636223</v>
       </c>
       <c r="F53" t="n">
-        <v>287.690816</v>
+        <v>163.522616</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>F-41T</t>
+          <t>F-43</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>313.15</v>
+        <v>298.15</v>
       </c>
       <c r="C54" t="n">
         <v>100000</v>
@@ -1737,20 +1737,20 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>8.704661</v>
+        <v>0.099817</v>
       </c>
       <c r="F54" t="n">
-        <v>287.690816</v>
+        <v>1.699984</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>F-42</t>
+          <t>F-44</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>313.15</v>
+        <v>673.15</v>
       </c>
       <c r="C55" t="n">
         <v>100000</v>
@@ -1761,64 +1761,64 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5.636223</v>
+        <v>5.766786</v>
       </c>
       <c r="F55" t="n">
-        <v>163.522616</v>
+        <v>165.2226</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>F-43</t>
+          <t>F-45</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>298.15</v>
+        <v>323.15</v>
       </c>
       <c r="C56" t="n">
         <v>100000</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.099817</v>
+        <v>0.130196</v>
       </c>
       <c r="F56" t="n">
-        <v>1.699984</v>
+        <v>2.345483</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>F-44</t>
+          <t>F-45R</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>673.15</v>
+        <v>323.15</v>
       </c>
       <c r="C57" t="n">
         <v>100000</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5.766786</v>
+        <v>0.123686</v>
       </c>
       <c r="F57" t="n">
-        <v>165.2226</v>
+        <v>2.228209</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>F-45</t>
+          <t>F-46</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1829,24 +1829,24 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.130196</v>
+        <v>5.63659</v>
       </c>
       <c r="F58" t="n">
-        <v>2.345483</v>
+        <v>162.877116</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>F-45R</t>
+          <t>F-47</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>323.15</v>
+        <v>298.15</v>
       </c>
       <c r="C59" t="n">
         <v>100000</v>
@@ -1857,16 +1857,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.123686</v>
+        <v>38.159711</v>
       </c>
       <c r="F59" t="n">
-        <v>2.228209</v>
+        <v>687.447198</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>F-46</t>
+          <t>F-47T</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1877,24 +1877,24 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5.63659</v>
+        <v>38.159711</v>
       </c>
       <c r="F60" t="n">
-        <v>162.877116</v>
+        <v>687.447198</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>F-47</t>
+          <t>F-48</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>298.15</v>
+        <v>323.15</v>
       </c>
       <c r="C61" t="n">
         <v>100000</v>
@@ -1905,16 +1905,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>38.159711</v>
+        <v>38.172601</v>
       </c>
       <c r="F61" t="n">
-        <v>687.447198</v>
+        <v>687.6667169999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>F-47T</t>
+          <t>F-49</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1925,48 +1925,48 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>38.159711</v>
+        <v>5.6237</v>
       </c>
       <c r="F62" t="n">
-        <v>687.447198</v>
+        <v>162.657597</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>F-48</t>
+          <t>F-49A</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>323.15</v>
+        <v>298.15</v>
       </c>
       <c r="C63" t="n">
         <v>100000</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>38.172601</v>
+        <v>5.6237</v>
       </c>
       <c r="F63" t="n">
-        <v>687.6667169999999</v>
+        <v>162.657597</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>F-49</t>
+          <t>F-49B</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>323.15</v>
+        <v>298.15</v>
       </c>
       <c r="C64" t="n">
         <v>100000</v>
@@ -1977,40 +1977,40 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5.6237</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>162.657597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>F-49A</t>
+          <t>F-5</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>298.15</v>
+        <v>373.15</v>
       </c>
       <c r="C65" t="n">
         <v>100000</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5.6237</v>
+        <v>10.283591</v>
       </c>
       <c r="F65" t="n">
-        <v>162.657597</v>
+        <v>522.665717</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>F-49B</t>
+          <t>F-50A</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -2025,40 +2025,40 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>5.623158</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>162.520056</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>F-5</t>
+          <t>F-50B</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>373.15</v>
+        <v>298.15</v>
       </c>
       <c r="C67" t="n">
         <v>100000</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>10.283591</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>522.665716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>F-50A</t>
+          <t>F-51A</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -2073,16 +2073,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5.623158</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>162.520056</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>F-50B</t>
+          <t>F-51B</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -2097,16 +2097,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>0.010838</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>0.5565020000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>F-51A</t>
+          <t>F-52A</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -2130,7 +2130,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>F-51B</t>
+          <t>F-52B</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -2145,16 +2145,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.010838</v>
+        <v>0.009754000000000001</v>
       </c>
       <c r="F71" t="n">
-        <v>0.5565020000000001</v>
+        <v>0.28142</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>F-52A</t>
+          <t>F-53</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -2165,20 +2165,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>9.465305000000001</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>199.779915</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>F-52B</t>
+          <t>F-54</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -2189,20 +2189,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.009754000000000001</v>
+        <v>0.002123</v>
       </c>
       <c r="F73" t="n">
-        <v>0.28142</v>
+        <v>0.565406</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>F-53</t>
+          <t>F-55</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -2217,16 +2217,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>9.465305000000001</v>
+        <v>0.891185</v>
       </c>
       <c r="F74" t="n">
-        <v>199.779913</v>
+        <v>20.94116</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>F-54</t>
+          <t>F-56</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -2241,23 +2241,23 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.002123</v>
+        <v>0.000148</v>
       </c>
       <c r="F75" t="n">
-        <v>0.565406</v>
+        <v>0.03947</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>F-55</t>
+          <t>F-57</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>298.15</v>
+        <v>379.2</v>
       </c>
       <c r="C76" t="n">
-        <v>100000</v>
+        <v>87290</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -2265,23 +2265,23 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.891185</v>
+        <v>22.820119</v>
       </c>
       <c r="F76" t="n">
-        <v>20.94116</v>
+        <v>715.157753</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>F-56</t>
+          <t>F-57T</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>298.15</v>
+        <v>379.2</v>
       </c>
       <c r="C77" t="n">
-        <v>100000</v>
+        <v>87290</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -2289,16 +2289,16 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.000148</v>
+        <v>22.820119</v>
       </c>
       <c r="F77" t="n">
-        <v>0.03947</v>
+        <v>715.157753</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>F-57</t>
+          <t>F-58</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -2313,23 +2313,23 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>22.820119</v>
+        <v>0.004276</v>
       </c>
       <c r="F78" t="n">
-        <v>715.15775</v>
+        <v>1.138709</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>F-57T</t>
+          <t>F-59</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>379.2</v>
+        <v>298.15</v>
       </c>
       <c r="C79" t="n">
-        <v>87290</v>
+        <v>100000</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2337,23 +2337,23 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>22.820119</v>
+        <v>2.044531</v>
       </c>
       <c r="F79" t="n">
-        <v>715.15775</v>
+        <v>78.106458</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>F-58</t>
+          <t>F-6</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>379.2</v>
+        <v>298.15</v>
       </c>
       <c r="C80" t="n">
-        <v>87290</v>
+        <v>100000</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -2361,20 +2361,20 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.004276</v>
+        <v>10.283591</v>
       </c>
       <c r="F80" t="n">
-        <v>1.138709</v>
+        <v>522.665717</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>F-59</t>
+          <t>F-60</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>298.15</v>
+        <v>323.15</v>
       </c>
       <c r="C81" t="n">
         <v>100000</v>
@@ -2385,16 +2385,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2.044531</v>
+        <v>0.00651</v>
       </c>
       <c r="F81" t="n">
-        <v>78.106458</v>
+        <v>0.117274</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>F-6</t>
+          <t>F-61</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -2409,20 +2409,20 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>10.283591</v>
+        <v>0.006547</v>
       </c>
       <c r="F82" t="n">
-        <v>522.665716</v>
+        <v>1.743586</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>F-60</t>
+          <t>F-62</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>323.15</v>
+        <v>298.15</v>
       </c>
       <c r="C83" t="n">
         <v>100000</v>
@@ -2433,16 +2433,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.00651</v>
+        <v>7.998166</v>
       </c>
       <c r="F83" t="n">
-        <v>0.117274</v>
+        <v>1527.552435</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>F-61</t>
+          <t>F-63</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -2453,20 +2453,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.006547</v>
+        <v>0.773725</v>
       </c>
       <c r="F84" t="n">
-        <v>1.743586</v>
+        <v>29.893158</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>F-62</t>
+          <t>F-63P</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -2477,48 +2477,48 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>7.998166</v>
+        <v>0.773725</v>
       </c>
       <c r="F85" t="n">
-        <v>1527.552422</v>
+        <v>29.893158</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>F-63</t>
+          <t>F-64</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>298.15</v>
+        <v>383.15</v>
       </c>
       <c r="C86" t="n">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.773725</v>
+        <v>16.47486</v>
       </c>
       <c r="F86" t="n">
-        <v>29.893158</v>
+        <v>600.541012</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>F-63P</t>
+          <t>F-65</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>298.15</v>
+        <v>383.15</v>
       </c>
       <c r="C87" t="n">
         <v>100000</v>
@@ -2529,23 +2529,23 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.773725</v>
+        <v>6.340412</v>
       </c>
       <c r="F87" t="n">
-        <v>29.893158</v>
+        <v>114.222523</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>F-64</t>
+          <t>F-66</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>383.15</v>
+        <v>379.2</v>
       </c>
       <c r="C88" t="n">
-        <v>100000</v>
+        <v>87290</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2553,40 +2553,40 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>16.47484</v>
+        <v>6.66066</v>
       </c>
       <c r="F88" t="n">
-        <v>600.535615</v>
+        <v>119.993922</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>F-65</t>
+          <t>F-67</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>383.15</v>
+        <v>393.15</v>
       </c>
       <c r="C89" t="n">
         <v>100000</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6.340412</v>
+        <v>16.2223</v>
       </c>
       <c r="F89" t="n">
-        <v>114.222522</v>
+        <v>292.244734</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>F-66</t>
+          <t>F-68</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -2601,16 +2601,16 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6.660651</v>
+        <v>9.814201000000001</v>
       </c>
       <c r="F90" t="n">
-        <v>119.991628</v>
+        <v>480.54709</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>F-67</t>
+          <t>F-69</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -2634,14 +2634,14 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>F-68</t>
+          <t>F-6P</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>379.2</v>
+        <v>298.15</v>
       </c>
       <c r="C92" t="n">
-        <v>87290</v>
+        <v>100000</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -2649,20 +2649,20 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>9.814189000000001</v>
+        <v>10.283591</v>
       </c>
       <c r="F92" t="n">
-        <v>480.543988</v>
+        <v>522.665717</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>F-69</t>
+          <t>F-7</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>393.15</v>
+        <v>298.15</v>
       </c>
       <c r="C93" t="n">
         <v>100000</v>
@@ -2673,23 +2673,23 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>16.2223</v>
+        <v>7.998299</v>
       </c>
       <c r="F93" t="n">
-        <v>292.244734</v>
+        <v>1527.587931</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>F-6P</t>
+          <t>F-70</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>298.15</v>
+        <v>375</v>
       </c>
       <c r="C94" t="n">
-        <v>100000</v>
+        <v>75260</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -2697,23 +2697,23 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>10.283591</v>
+        <v>6.660651</v>
       </c>
       <c r="F94" t="n">
-        <v>522.665716</v>
+        <v>119.991629</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>F-7</t>
+          <t>F-71</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>298.15</v>
+        <v>375</v>
       </c>
       <c r="C95" t="n">
-        <v>100000</v>
+        <v>75260</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -2721,153 +2721,105 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>7.998299</v>
+        <v>29.223363</v>
       </c>
       <c r="F95" t="n">
-        <v>1527.587918</v>
+        <v>526.458886</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>F-70</t>
+          <t>F-72</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>375</v>
+        <v>383.15</v>
       </c>
       <c r="C96" t="n">
-        <v>75260</v>
+        <v>100000</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6.660651</v>
+        <v>6.340412</v>
       </c>
       <c r="F96" t="n">
-        <v>119.991628</v>
+        <v>114.222523</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>F-71</t>
+          <t>F-73</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>375</v>
+        <v>414</v>
       </c>
       <c r="C97" t="n">
-        <v>75260</v>
+        <v>100000</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>29.223363</v>
+        <v>4.17976</v>
       </c>
       <c r="F97" t="n">
-        <v>526.458884</v>
+        <v>121.859939</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>F-72</t>
+          <t>F-8</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>383.15</v>
+        <v>298.15</v>
       </c>
       <c r="C98" t="n">
         <v>100000</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6.340412</v>
+        <v>8.814462000000001</v>
       </c>
       <c r="F98" t="n">
-        <v>114.222522</v>
+        <v>1849.908327</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>F-73</t>
+          <t>F-9</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>414</v>
+        <v>298.15</v>
       </c>
       <c r="C99" t="n">
         <v>100000</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4.17976</v>
+        <v>0.881446</v>
       </c>
       <c r="F99" t="n">
-        <v>121.859939</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>F-8</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>298.15</v>
-      </c>
-      <c r="C100" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E100" t="n">
-        <v>8.814462000000001</v>
-      </c>
-      <c r="F100" t="n">
-        <v>1849.908314</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>F-9</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>298.15</v>
-      </c>
-      <c r="C101" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
-        <v>0.881446</v>
-      </c>
-      <c r="F101" t="n">
         <v>16.463097</v>
       </c>
     </row>
@@ -2882,7 +2834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ101"/>
+  <dimension ref="A1:AQ99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3362,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7184019</v>
+        <v>1.71840192</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.27751241</v>
+        <v>6.27751246</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -3471,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>22.00747198</v>
+        <v>22.00747215</v>
       </c>
       <c r="T4" t="n">
         <v>0.00396602</v>
@@ -3604,7 +3556,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>22.00747198</v>
+        <v>22.00747215</v>
       </c>
       <c r="T5" t="n">
         <v>0.00396602</v>
@@ -3761,10 +3713,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7141059</v>
+        <v>1.71410591</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.27751241</v>
+        <v>6.27751246</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -3894,10 +3846,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.7206529</v>
+        <v>1.72065292</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.27751241</v>
+        <v>6.27751246</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -4160,10 +4112,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.63462026</v>
+        <v>1.63462027</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.96363679</v>
+        <v>5.96363684</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -4293,10 +4245,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.08616588</v>
+        <v>0.08616583</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.31387537</v>
+        <v>0.3138752</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -4402,7 +4354,7 @@
         <v>0.006234</v>
       </c>
       <c r="S11" t="n">
-        <v>8.96392831</v>
+        <v>8.9639284</v>
       </c>
       <c r="T11" t="n">
         <v>0.46497694</v>
@@ -4535,7 +4487,7 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8695348000000001</v>
+        <v>0.86953481</v>
       </c>
       <c r="T12" t="n">
         <v>0.00794096</v>
@@ -4668,7 +4620,7 @@
         <v>0.006234</v>
       </c>
       <c r="S13" t="n">
-        <v>8.766137820000001</v>
+        <v>8.7661379</v>
       </c>
       <c r="T13" t="n">
         <v>0.20359155</v>
@@ -4801,7 +4753,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>6.69562023</v>
+        <v>6.69562032</v>
       </c>
       <c r="T14" t="n">
         <v>2.936403</v>
@@ -5067,7 +5019,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.86040561</v>
+        <v>0.86040562</v>
       </c>
       <c r="T16" t="n">
         <v>0.00495151</v>
@@ -5602,7 +5554,7 @@
         <v>2.206324</v>
       </c>
       <c r="T20" t="n">
-        <v>0.000397</v>
+        <v>0.0003966</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -5623,7 +5575,7 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2e-05</v>
+        <v>2.025e-05</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -5665,7 +5617,7 @@
         <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.00088</v>
+        <v>0.00088043</v>
       </c>
       <c r="AP20" t="n">
         <v>0</v>
@@ -5735,7 +5687,7 @@
         <v>2.206324</v>
       </c>
       <c r="T21" t="n">
-        <v>0.000397</v>
+        <v>0.0003966</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -5756,7 +5708,7 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2e-05</v>
+        <v>2.025e-05</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -5798,7 +5750,7 @@
         <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.00088</v>
+        <v>0.00088043</v>
       </c>
       <c r="AP21" t="n">
         <v>0</v>
@@ -5868,7 +5820,7 @@
         <v>2.206324</v>
       </c>
       <c r="T22" t="n">
-        <v>0.000397</v>
+        <v>0.0003966</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -5889,7 +5841,7 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2e-05</v>
+        <v>2.025e-05</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -5931,7 +5883,7 @@
         <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.00088</v>
+        <v>0.00088043</v>
       </c>
       <c r="AP22" t="n">
         <v>0</v>
@@ -5998,7 +5950,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>6.80360499</v>
+        <v>6.80360506</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -6134,7 +6086,7 @@
         <v>0.005577</v>
       </c>
       <c r="T24" t="n">
-        <v>0.000397</v>
+        <v>0.0003966</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -6155,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2e-05</v>
+        <v>2.025e-05</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -6197,7 +6149,7 @@
         <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>0.00088</v>
+        <v>0.00088043</v>
       </c>
       <c r="AP24" t="n">
         <v>0.80777984</v>
@@ -6267,7 +6219,7 @@
         <v>0.005577</v>
       </c>
       <c r="T25" t="n">
-        <v>0.000397</v>
+        <v>0.0003966</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -6288,7 +6240,7 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2e-05</v>
+        <v>2.025e-05</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -6330,7 +6282,7 @@
         <v>0</v>
       </c>
       <c r="AO25" t="n">
-        <v>0.00088</v>
+        <v>0.00088043</v>
       </c>
       <c r="AP25" t="n">
         <v>0.80777984</v>
@@ -6533,7 +6485,7 @@
         <v>0.005577</v>
       </c>
       <c r="T27" t="n">
-        <v>0.000397</v>
+        <v>0.0003966</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -6554,7 +6506,7 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2e-05</v>
+        <v>2.025e-05</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -6596,7 +6548,7 @@
         <v>0</v>
       </c>
       <c r="AO27" t="n">
-        <v>0.00088</v>
+        <v>0.00088043</v>
       </c>
       <c r="AP27" t="n">
         <v>0</v>
@@ -7461,7 +7413,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>6.69562023</v>
+        <v>6.69562032</v>
       </c>
       <c r="T34" t="n">
         <v>2.936403</v>
@@ -7594,7 +7546,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>6.69562023</v>
+        <v>6.69562032</v>
       </c>
       <c r="T35" t="n">
         <v>2.936403</v>
@@ -7727,7 +7679,7 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>6.69562023</v>
+        <v>6.69562032</v>
       </c>
       <c r="T36" t="n">
         <v>2.936403</v>
@@ -7993,7 +7945,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>3.39188834</v>
+        <v>3.39188843</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -8259,7 +8211,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>9.21127167</v>
+        <v>9.211271740000001</v>
       </c>
       <c r="T40" t="n">
         <v>0.26437484</v>
@@ -8392,7 +8344,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>9.21127167</v>
+        <v>9.211271740000001</v>
       </c>
       <c r="T41" t="n">
         <v>0.26437484</v>
@@ -8791,7 +8743,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>27.53677446</v>
+        <v>27.53677453</v>
       </c>
       <c r="T44" t="n">
         <v>2.56359434</v>
@@ -8924,7 +8876,7 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>27.53677446</v>
+        <v>27.53677453</v>
       </c>
       <c r="T45" t="n">
         <v>2.56359434</v>
@@ -9057,7 +9009,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>24.38627122</v>
+        <v>24.3862713</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -9401,7 +9353,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>F-3P</t>
+          <t>F-4</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -9438,22 +9390,22 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.01380778</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>0.00243865</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0.00054191</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>0.12509107</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -9462,10 +9414,10 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>0.31412884</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>0.44280813</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
         <v>0</v>
@@ -9534,7 +9486,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>F-3PT</t>
+          <t>F-40</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -9571,16 +9523,16 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.01380778</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>0.00243865</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0.00054191</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -9595,16 +9547,16 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>0.31412884</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>0.44280813</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.68713682</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>0.44847941</v>
       </c>
       <c r="Y50" t="n">
         <v>0</v>
@@ -9667,7 +9619,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>F-4</t>
+          <t>F-41</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -9704,22 +9656,22 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>0.01380778</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>0.00243865</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>0.00054191</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>0.12509107</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -9728,16 +9680,16 @@
         <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.92968853</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>0.44280813</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>4.67007382</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.64530241</v>
       </c>
       <c r="Y51" t="n">
         <v>0</v>
@@ -9800,7 +9752,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>F-40</t>
+          <t>F-41T</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -9837,16 +9789,16 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>0.01380778</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>0.00243865</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>0.00054191</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -9861,16 +9813,16 @@
         <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.92968853</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>0.44280813</v>
       </c>
       <c r="W52" t="n">
-        <v>1.68713682</v>
+        <v>4.67007382</v>
       </c>
       <c r="X52" t="n">
-        <v>0.44847941</v>
+        <v>1.64530241</v>
       </c>
       <c r="Y52" t="n">
         <v>0</v>
@@ -9933,7 +9885,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>F-41</t>
+          <t>F-42</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -9994,16 +9946,16 @@
         <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>1.92968853</v>
+        <v>0.01929689</v>
       </c>
       <c r="V53" t="n">
-        <v>0.44280813</v>
+        <v>0.05398027</v>
       </c>
       <c r="W53" t="n">
         <v>4.67007382</v>
       </c>
       <c r="X53" t="n">
-        <v>1.64530241</v>
+        <v>0.8760836</v>
       </c>
       <c r="Y53" t="n">
         <v>0</v>
@@ -10066,7 +10018,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>F-41T</t>
+          <t>F-43</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -10103,16 +10055,16 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.01380778</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>0.00243865</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>0.00054191</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -10127,19 +10079,19 @@
         <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>1.92968853</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>0.44280813</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>4.67007382</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.64530241</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>0.09981703</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -10199,7 +10151,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>F-42</t>
+          <t>F-44</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -10254,25 +10206,25 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>0.13019613</v>
       </c>
       <c r="T55" t="n">
         <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>0.01929689</v>
+        <v>0.00120413</v>
       </c>
       <c r="V55" t="n">
-        <v>0.05398027</v>
+        <v>0.00336837</v>
       </c>
       <c r="W55" t="n">
-        <v>4.67007382</v>
+        <v>4.74782485</v>
       </c>
       <c r="X55" t="n">
-        <v>0.8760836</v>
+        <v>0.85438425</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>0.01301961</v>
       </c>
       <c r="Z55" t="n">
         <v>0</v>
@@ -10332,7 +10284,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>F-43</t>
+          <t>F-45</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -10387,7 +10339,7 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>0.13019613</v>
       </c>
       <c r="T56" t="n">
         <v>0</v>
@@ -10405,7 +10357,7 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.09981703</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -10465,7 +10417,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>F-44</t>
+          <t>F-45R</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -10502,16 +10454,16 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.01380778</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>0.00243865</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>0.00054191</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -10520,25 +10472,25 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.13019613</v>
+        <v>0.12368632</v>
       </c>
       <c r="T57" t="n">
         <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>0.00120413</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>0.00336837</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>4.74782485</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>0.85438425</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.01301961</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
         <v>0</v>
@@ -10598,7 +10550,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>F-45</t>
+          <t>F-46</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -10635,16 +10587,16 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>0.01380778</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>0.00243865</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>0.00054191</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -10653,25 +10605,25 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.13019613</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
         <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>0.00120413</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>0.00336837</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>4.74782485</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>0.85438425</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>0.01301961</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
@@ -10731,7 +10683,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>F-45R</t>
+          <t>F-47</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -10786,7 +10738,7 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.12368632</v>
+        <v>38.15971123</v>
       </c>
       <c r="T59" t="n">
         <v>0</v>
@@ -10864,7 +10816,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>F-46</t>
+          <t>F-47T</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -10901,16 +10853,16 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0.01380778</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>0.00243865</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>0.00054191</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -10919,25 +10871,25 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>38.15971123</v>
       </c>
       <c r="T60" t="n">
         <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>0.00120413</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>0.00336837</v>
+        <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>4.74782485</v>
+        <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>0.85438425</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.01301961</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
         <v>0</v>
@@ -10997,7 +10949,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>F-47</t>
+          <t>F-48</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -11070,7 +11022,7 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>0.01288942</v>
       </c>
       <c r="Z61" t="n">
         <v>0</v>
@@ -11130,7 +11082,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>F-47T</t>
+          <t>F-49</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -11167,16 +11119,16 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>0.01380778</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>0.00243865</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>0.00054191</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -11185,25 +11137,25 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>38.15971123</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
         <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>0.00120413</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>0.00336837</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>4.74782485</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>0.85438425</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>0.0001302</v>
       </c>
       <c r="Z62" t="n">
         <v>0</v>
@@ -11263,7 +11215,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>F-48</t>
+          <t>F-49A</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -11300,16 +11252,16 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>0.01380778</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>0.00243865</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>0.00054191</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -11318,25 +11270,25 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>38.15971123</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
         <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>0.00120413</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>0.00336837</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>4.74782485</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>0.85438425</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.01288942</v>
+        <v>0.0001302</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
@@ -11396,7 +11348,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>F-49</t>
+          <t>F-49B</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -11433,16 +11385,16 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0.01380778</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>0.00243865</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>0.00054191</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -11457,19 +11409,19 @@
         <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>0.00120413</v>
+        <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>0.00336837</v>
+        <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>4.74782485</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>0.85438425</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0.0001302</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
         <v>0</v>
@@ -11529,7 +11481,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>F-49A</t>
+          <t>F-5</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -11566,43 +11518,43 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>0.01380778</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>0.00243865</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>0.00054191</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>1.106e-05</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>0.006234</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>8.9639284</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>0.46497694</v>
       </c>
       <c r="U65" t="n">
-        <v>0.00120413</v>
+        <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>0.00336837</v>
+        <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>4.74782485</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>0.85438425</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0.0001302</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
         <v>0</v>
@@ -11620,37 +11572,37 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>0.81061497</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>0.00765862</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>0.00040357</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>0.00032183</v>
       </c>
       <c r="AI65" t="n">
-        <v>0</v>
+        <v>0.00854456</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0</v>
+        <v>0.00209422</v>
       </c>
       <c r="AK65" t="n">
-        <v>0</v>
+        <v>0.01255454</v>
       </c>
       <c r="AL65" t="n">
-        <v>0</v>
+        <v>0.00252991</v>
       </c>
       <c r="AM65" t="n">
-        <v>0</v>
+        <v>0.00036642</v>
       </c>
       <c r="AN65" t="n">
-        <v>0</v>
+        <v>0.00021248</v>
       </c>
       <c r="AO65" t="n">
-        <v>0</v>
+        <v>0.00313991</v>
       </c>
       <c r="AP65" t="n">
         <v>0</v>
@@ -11662,7 +11614,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>F-49B</t>
+          <t>F-50A</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -11699,10 +11651,10 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>0.01380778</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>0.00243865</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -11723,19 +11675,19 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>0.00120413</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>0.00336837</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>4.74782485</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>0.85438425</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>0.0001302</v>
       </c>
       <c r="Z66" t="n">
         <v>0</v>
@@ -11795,7 +11747,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>F-5</t>
+          <t>F-50B</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -11844,16 +11796,16 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.106e-05</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>0.006234</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>8.96392831</v>
+        <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>0.46497694</v>
+        <v>0</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -11886,37 +11838,37 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0.81061497</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>0.00765862</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
-        <v>0.00040357</v>
+        <v>0</v>
       </c>
       <c r="AH67" t="n">
-        <v>0.00032183</v>
+        <v>0</v>
       </c>
       <c r="AI67" t="n">
-        <v>0.00854456</v>
+        <v>0</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0.00209422</v>
+        <v>0</v>
       </c>
       <c r="AK67" t="n">
-        <v>0.01255454</v>
+        <v>0</v>
       </c>
       <c r="AL67" t="n">
-        <v>0.00252991</v>
+        <v>0</v>
       </c>
       <c r="AM67" t="n">
-        <v>0.00036642</v>
+        <v>0</v>
       </c>
       <c r="AN67" t="n">
-        <v>0.00021248</v>
+        <v>0</v>
       </c>
       <c r="AO67" t="n">
-        <v>0.00313991</v>
+        <v>0</v>
       </c>
       <c r="AP67" t="n">
         <v>0</v>
@@ -11928,7 +11880,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>F-50A</t>
+          <t>F-51A</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -11965,10 +11917,10 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0.01380778</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0.00243865</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -11989,19 +11941,19 @@
         <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>0.00120413</v>
+        <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>0.00336837</v>
+        <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>4.74782485</v>
+        <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>0.85438425</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.0001302</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -12061,7 +12013,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>F-50B</t>
+          <t>F-51B</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -12107,7 +12059,7 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>0.00108382</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -12128,10 +12080,10 @@
         <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>0.00770595</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>0.00204842</v>
       </c>
       <c r="Y69" t="n">
         <v>0</v>
@@ -12194,7 +12146,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>F-51A</t>
+          <t>F-52A</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -12327,7 +12279,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>F-51B</t>
+          <t>F-52B</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -12373,7 +12325,7 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>0.00108382</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -12460,7 +12412,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>F-52A</t>
+          <t>F-53</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -12509,16 +12461,16 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>1.106e-05</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>0.006234</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>8.9639284</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>0.46497694</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
@@ -12539,7 +12491,7 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>8.94e-05</v>
       </c>
       <c r="AB72" t="n">
         <v>0</v>
@@ -12551,37 +12503,37 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>0.00081062</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>0.00055538</v>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>3.625e-05</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>0.00032183</v>
       </c>
       <c r="AI72" t="n">
-        <v>0</v>
+        <v>0.00854456</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0</v>
+        <v>0.00209422</v>
       </c>
       <c r="AK72" t="n">
-        <v>0</v>
+        <v>0.01255454</v>
       </c>
       <c r="AL72" t="n">
-        <v>0</v>
+        <v>0.00252991</v>
       </c>
       <c r="AM72" t="n">
-        <v>0</v>
+        <v>0.00036642</v>
       </c>
       <c r="AN72" t="n">
-        <v>0</v>
+        <v>0.00021248</v>
       </c>
       <c r="AO72" t="n">
-        <v>0</v>
+        <v>0.00203921</v>
       </c>
       <c r="AP72" t="n">
         <v>0</v>
@@ -12593,7 +12545,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>F-52B</t>
+          <t>F-54</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -12660,10 +12612,10 @@
         <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>0.00770595</v>
+        <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>0.00204842</v>
+        <v>0</v>
       </c>
       <c r="Y73" t="n">
         <v>0</v>
@@ -12672,7 +12624,7 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>0.00212305</v>
       </c>
       <c r="AB73" t="n">
         <v>0</v>
@@ -12726,7 +12678,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>F-53</t>
+          <t>F-55</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -12775,16 +12727,16 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.106e-05</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>0.006234</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>8.96392831</v>
+        <v>0.86953481</v>
       </c>
       <c r="T74" t="n">
-        <v>0.46497694</v>
+        <v>0.00794096</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
@@ -12805,49 +12757,49 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>8.94e-05</v>
+        <v>2.365e-05</v>
       </c>
       <c r="AB74" t="n">
         <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>0.00397048</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0.00081062</v>
+        <v>0.00202451</v>
       </c>
       <c r="AF74" t="n">
-        <v>0.00055538</v>
+        <v>0.00710324</v>
       </c>
       <c r="AG74" t="n">
-        <v>3.625e-05</v>
+        <v>0.00036732</v>
       </c>
       <c r="AH74" t="n">
-        <v>0.00032183</v>
+        <v>0</v>
       </c>
       <c r="AI74" t="n">
-        <v>0.00854456</v>
+        <v>0</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.00209422</v>
+        <v>0</v>
       </c>
       <c r="AK74" t="n">
-        <v>0.01255454</v>
+        <v>0</v>
       </c>
       <c r="AL74" t="n">
-        <v>0.00252991</v>
+        <v>0</v>
       </c>
       <c r="AM74" t="n">
-        <v>0.00036642</v>
+        <v>0</v>
       </c>
       <c r="AN74" t="n">
-        <v>0.00021248</v>
+        <v>0</v>
       </c>
       <c r="AO74" t="n">
-        <v>0.00203921</v>
+        <v>0.00022024</v>
       </c>
       <c r="AP74" t="n">
         <v>0</v>
@@ -12859,7 +12811,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>F-54</t>
+          <t>F-56</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -12938,7 +12890,7 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.00212305</v>
+        <v>0.00014821</v>
       </c>
       <c r="AB75" t="n">
         <v>0</v>
@@ -12992,7 +12944,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>F-55</t>
+          <t>F-57</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -13047,10 +12999,10 @@
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.8695348000000001</v>
+        <v>22.00747215</v>
       </c>
       <c r="T76" t="n">
-        <v>0.00794096</v>
+        <v>0.00396602</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -13071,25 +13023,25 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.365e-05</v>
+        <v>2.025e-05</v>
       </c>
       <c r="AB76" t="n">
         <v>0</v>
       </c>
       <c r="AC76" t="n">
-        <v>0.00397048</v>
+        <v>0</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0.00202451</v>
+        <v>0.80777984</v>
       </c>
       <c r="AF76" t="n">
-        <v>0.00710324</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>0.00036732</v>
+        <v>0</v>
       </c>
       <c r="AH76" t="n">
         <v>0</v>
@@ -13113,7 +13065,7 @@
         <v>0</v>
       </c>
       <c r="AO76" t="n">
-        <v>0.00022024</v>
+        <v>0.00088043</v>
       </c>
       <c r="AP76" t="n">
         <v>0</v>
@@ -13125,7 +13077,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>F-56</t>
+          <t>F-57T</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -13180,10 +13132,10 @@
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>22.00747215</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>0.00396602</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -13204,7 +13156,7 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.00014821</v>
+        <v>2.025e-05</v>
       </c>
       <c r="AB77" t="n">
         <v>0</v>
@@ -13216,7 +13168,7 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>0.80777984</v>
       </c>
       <c r="AF77" t="n">
         <v>0</v>
@@ -13246,7 +13198,7 @@
         <v>0</v>
       </c>
       <c r="AO77" t="n">
-        <v>0</v>
+        <v>0.00088043</v>
       </c>
       <c r="AP77" t="n">
         <v>0</v>
@@ -13258,7 +13210,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>F-57</t>
+          <t>F-58</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -13313,10 +13265,10 @@
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>22.00747198</v>
+        <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>0.00396602</v>
+        <v>0</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
@@ -13337,7 +13289,7 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.025e-05</v>
+        <v>0.00427575</v>
       </c>
       <c r="AB78" t="n">
         <v>0</v>
@@ -13349,7 +13301,7 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0.80777984</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
         <v>0</v>
@@ -13379,7 +13331,7 @@
         <v>0</v>
       </c>
       <c r="AO78" t="n">
-        <v>0.00088043</v>
+        <v>0</v>
       </c>
       <c r="AP78" t="n">
         <v>0</v>
@@ -13391,7 +13343,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>F-57T</t>
+          <t>F-59</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -13446,10 +13398,10 @@
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>22.00747198</v>
+        <v>1.12726501</v>
       </c>
       <c r="T79" t="n">
-        <v>0.00396602</v>
+        <v>0.91726622</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -13470,7 +13422,7 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.025e-05</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
         <v>0</v>
@@ -13482,7 +13434,7 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0.80777984</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
         <v>0</v>
@@ -13512,7 +13464,7 @@
         <v>0</v>
       </c>
       <c r="AO79" t="n">
-        <v>0.00088043</v>
+        <v>0</v>
       </c>
       <c r="AP79" t="n">
         <v>0</v>
@@ -13524,7 +13476,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>F-58</t>
+          <t>F-6</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -13573,16 +13525,16 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>1.106e-05</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>0.006234</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>8.9639284</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>0.46497694</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -13603,7 +13555,7 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.00427575</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
         <v>0</v>
@@ -13615,37 +13567,37 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>0.81061497</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>0.00765862</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>0.00040357</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>0.00032183</v>
       </c>
       <c r="AI80" t="n">
-        <v>0</v>
+        <v>0.00854456</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0</v>
+        <v>0.00209422</v>
       </c>
       <c r="AK80" t="n">
-        <v>0</v>
+        <v>0.01255454</v>
       </c>
       <c r="AL80" t="n">
-        <v>0</v>
+        <v>0.00252991</v>
       </c>
       <c r="AM80" t="n">
-        <v>0</v>
+        <v>0.00036642</v>
       </c>
       <c r="AN80" t="n">
-        <v>0</v>
+        <v>0.00021248</v>
       </c>
       <c r="AO80" t="n">
-        <v>0</v>
+        <v>0.00313991</v>
       </c>
       <c r="AP80" t="n">
         <v>0</v>
@@ -13657,7 +13609,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>F-59</t>
+          <t>F-60</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -13712,10 +13664,10 @@
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>1.12726501</v>
+        <v>0.00650981</v>
       </c>
       <c r="T81" t="n">
-        <v>0.91726622</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -13790,7 +13742,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>F-6</t>
+          <t>F-61</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -13839,16 +13791,16 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>1.106e-05</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>0.006234</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>8.96392831</v>
+        <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>0.46497694</v>
+        <v>0</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
@@ -13869,7 +13821,7 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>0.00654701</v>
       </c>
       <c r="AB82" t="n">
         <v>0</v>
@@ -13881,37 +13833,37 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0.81061497</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>0.00765862</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
-        <v>0.00040357</v>
+        <v>0</v>
       </c>
       <c r="AH82" t="n">
-        <v>0.00032183</v>
+        <v>0</v>
       </c>
       <c r="AI82" t="n">
-        <v>0.00854456</v>
+        <v>0</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.00209422</v>
+        <v>0</v>
       </c>
       <c r="AK82" t="n">
-        <v>0.01255454</v>
+        <v>0</v>
       </c>
       <c r="AL82" t="n">
-        <v>0.00252991</v>
+        <v>0</v>
       </c>
       <c r="AM82" t="n">
-        <v>0.00036642</v>
+        <v>0</v>
       </c>
       <c r="AN82" t="n">
-        <v>0.00021248</v>
+        <v>0</v>
       </c>
       <c r="AO82" t="n">
-        <v>0.00313991</v>
+        <v>0</v>
       </c>
       <c r="AP82" t="n">
         <v>0</v>
@@ -13923,7 +13875,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>F-60</t>
+          <t>F-62</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -13978,7 +13930,7 @@
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.00650981</v>
+        <v>0</v>
       </c>
       <c r="T83" t="n">
         <v>0</v>
@@ -14002,10 +13954,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.72065292</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>6.27751246</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -14014,7 +13966,7 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>7e-08</v>
       </c>
       <c r="AF83" t="n">
         <v>0</v>
@@ -14044,7 +13996,7 @@
         <v>0</v>
       </c>
       <c r="AO83" t="n">
-        <v>0</v>
+        <v>5.5e-07</v>
       </c>
       <c r="AP83" t="n">
         <v>0</v>
@@ -14056,7 +14008,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>F-61</t>
+          <t>F-63</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -14093,16 +14045,16 @@
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>0.01380778</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>0.00243865</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>0.00054191</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -14117,10 +14069,10 @@
         <v>0</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
+        <v>0.31412884</v>
       </c>
       <c r="V84" t="n">
-        <v>0</v>
+        <v>0.44280813</v>
       </c>
       <c r="W84" t="n">
         <v>0</v>
@@ -14135,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0.00654701</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
         <v>0</v>
@@ -14189,7 +14141,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>F-62</t>
+          <t>F-63P</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -14226,16 +14178,16 @@
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>0.01380778</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>0.00243865</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>0.00054191</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -14250,10 +14202,10 @@
         <v>0</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>0.31412884</v>
       </c>
       <c r="V85" t="n">
-        <v>0</v>
+        <v>0.44280813</v>
       </c>
       <c r="W85" t="n">
         <v>0</v>
@@ -14268,10 +14220,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.7206529</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>6.27751241</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -14280,7 +14232,7 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>7e-08</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
         <v>0</v>
@@ -14310,7 +14262,7 @@
         <v>0</v>
       </c>
       <c r="AO85" t="n">
-        <v>5.5e-07</v>
+        <v>0</v>
       </c>
       <c r="AP85" t="n">
         <v>0</v>
@@ -14322,7 +14274,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>F-63</t>
+          <t>F-64</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -14359,16 +14311,16 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>0.01380778</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>0.00243865</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>0.00054191</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14377,16 +14329,16 @@
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>15.6670601</v>
       </c>
       <c r="T86" t="n">
         <v>0</v>
       </c>
       <c r="U86" t="n">
-        <v>0.31412884</v>
+        <v>0</v>
       </c>
       <c r="V86" t="n">
-        <v>0.44280813</v>
+        <v>0</v>
       </c>
       <c r="W86" t="n">
         <v>0</v>
@@ -14401,7 +14353,7 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>2.025e-05</v>
       </c>
       <c r="AB86" t="n">
         <v>0</v>
@@ -14413,7 +14365,7 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>0.80777984</v>
       </c>
       <c r="AF86" t="n">
         <v>0</v>
@@ -14455,7 +14407,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>F-63P</t>
+          <t>F-65</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -14492,16 +14444,16 @@
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>0.01380778</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>0.00243865</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>0.00054191</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14510,16 +14462,16 @@
         <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>0</v>
+        <v>6.34041204</v>
       </c>
       <c r="T87" t="n">
         <v>0</v>
       </c>
       <c r="U87" t="n">
-        <v>0.31412884</v>
+        <v>0</v>
       </c>
       <c r="V87" t="n">
-        <v>0.44280813</v>
+        <v>0</v>
       </c>
       <c r="W87" t="n">
         <v>0</v>
@@ -14588,7 +14540,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>F-64</t>
+          <t>F-66</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -14643,7 +14595,7 @@
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>15.66705998</v>
+        <v>6.66065104</v>
       </c>
       <c r="T88" t="n">
         <v>0</v>
@@ -14667,7 +14619,7 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>8.610000000000001e-06</v>
       </c>
       <c r="AB88" t="n">
         <v>0</v>
@@ -14679,7 +14631,7 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0.80777984</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
         <v>0</v>
@@ -14721,7 +14673,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>F-65</t>
+          <t>F-67</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -14776,7 +14728,7 @@
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>6.34041199</v>
+        <v>16.2223</v>
       </c>
       <c r="T89" t="n">
         <v>0</v>
@@ -14854,7 +14806,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>F-66</t>
+          <t>F-68</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -14909,7 +14861,7 @@
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>6.66065099</v>
+        <v>9.006409059999999</v>
       </c>
       <c r="T90" t="n">
         <v>0</v>
@@ -14933,7 +14885,7 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.164e-05</v>
       </c>
       <c r="AB90" t="n">
         <v>0</v>
@@ -14945,7 +14897,7 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>0.80777984</v>
       </c>
       <c r="AF90" t="n">
         <v>0</v>
@@ -14987,7 +14939,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>F-67</t>
+          <t>F-69</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -15120,7 +15072,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>F-68</t>
+          <t>F-6P</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -15169,16 +15121,16 @@
         <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>1.106e-05</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>0.006234</v>
       </c>
       <c r="S92" t="n">
-        <v>9.006408990000001</v>
+        <v>8.9639284</v>
       </c>
       <c r="T92" t="n">
-        <v>0</v>
+        <v>0.46497694</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -15211,37 +15163,37 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0.80777984</v>
+        <v>0.81061497</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>0.00765862</v>
       </c>
       <c r="AG92" t="n">
-        <v>0</v>
+        <v>0.00040357</v>
       </c>
       <c r="AH92" t="n">
-        <v>0</v>
+        <v>0.00032183</v>
       </c>
       <c r="AI92" t="n">
-        <v>0</v>
+        <v>0.00854456</v>
       </c>
       <c r="AJ92" t="n">
-        <v>0</v>
+        <v>0.00209422</v>
       </c>
       <c r="AK92" t="n">
-        <v>0</v>
+        <v>0.01255454</v>
       </c>
       <c r="AL92" t="n">
-        <v>0</v>
+        <v>0.00252991</v>
       </c>
       <c r="AM92" t="n">
-        <v>0</v>
+        <v>0.00036642</v>
       </c>
       <c r="AN92" t="n">
-        <v>0</v>
+        <v>0.00021248</v>
       </c>
       <c r="AO92" t="n">
-        <v>0</v>
+        <v>0.00313991</v>
       </c>
       <c r="AP92" t="n">
         <v>0</v>
@@ -15253,7 +15205,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>F-69</t>
+          <t>F-7</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -15308,7 +15260,7 @@
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>16.2223</v>
+        <v>0</v>
       </c>
       <c r="T93" t="n">
         <v>0</v>
@@ -15332,10 +15284,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.72078622</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>6.27751246</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15344,7 +15296,7 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>7e-08</v>
       </c>
       <c r="AF93" t="n">
         <v>0</v>
@@ -15374,7 +15326,7 @@
         <v>0</v>
       </c>
       <c r="AO93" t="n">
-        <v>0</v>
+        <v>5.2e-07</v>
       </c>
       <c r="AP93" t="n">
         <v>0</v>
@@ -15386,7 +15338,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>F-6P</t>
+          <t>F-70</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -15435,16 +15387,16 @@
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>1.106e-05</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>0.006234</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>8.96392831</v>
+        <v>6.66065104</v>
       </c>
       <c r="T94" t="n">
-        <v>0.46497694</v>
+        <v>0</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -15477,37 +15429,37 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0.81061497</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>0.00765862</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
-        <v>0.00040357</v>
+        <v>0</v>
       </c>
       <c r="AH94" t="n">
-        <v>0.00032183</v>
+        <v>0</v>
       </c>
       <c r="AI94" t="n">
-        <v>0.00854456</v>
+        <v>0</v>
       </c>
       <c r="AJ94" t="n">
-        <v>0.00209422</v>
+        <v>0</v>
       </c>
       <c r="AK94" t="n">
-        <v>0.01255454</v>
+        <v>0</v>
       </c>
       <c r="AL94" t="n">
-        <v>0.00252991</v>
+        <v>0</v>
       </c>
       <c r="AM94" t="n">
-        <v>0.00036642</v>
+        <v>0</v>
       </c>
       <c r="AN94" t="n">
-        <v>0.00021248</v>
+        <v>0</v>
       </c>
       <c r="AO94" t="n">
-        <v>0.00313991</v>
+        <v>0</v>
       </c>
       <c r="AP94" t="n">
         <v>0</v>
@@ -15519,7 +15471,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>F-7</t>
+          <t>F-71</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -15574,7 +15526,7 @@
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>0</v>
+        <v>29.22336309</v>
       </c>
       <c r="T95" t="n">
         <v>0</v>
@@ -15598,10 +15550,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.72078621</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>6.27751241</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15610,7 +15562,7 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>7e-08</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
         <v>0</v>
@@ -15640,7 +15592,7 @@
         <v>0</v>
       </c>
       <c r="AO95" t="n">
-        <v>5.2e-07</v>
+        <v>0</v>
       </c>
       <c r="AP95" t="n">
         <v>0</v>
@@ -15652,7 +15604,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>F-70</t>
+          <t>F-72</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -15707,7 +15659,7 @@
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>6.66065099</v>
+        <v>6.34041204</v>
       </c>
       <c r="T96" t="n">
         <v>0</v>
@@ -15785,7 +15737,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>F-71</t>
+          <t>F-73</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -15840,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>29.22336299</v>
+        <v>0</v>
       </c>
       <c r="T97" t="n">
         <v>0</v>
@@ -15852,10 +15804,10 @@
         <v>0</v>
       </c>
       <c r="W97" t="n">
-        <v>0</v>
+        <v>2.982937</v>
       </c>
       <c r="X97" t="n">
-        <v>0</v>
+        <v>1.196823</v>
       </c>
       <c r="Y97" t="n">
         <v>0</v>
@@ -15918,7 +15870,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>F-72</t>
+          <t>F-8</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -15973,7 +15925,7 @@
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>6.34041199</v>
+        <v>0</v>
       </c>
       <c r="T98" t="n">
         <v>0</v>
@@ -15997,10 +15949,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.71857377</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>6.27751246</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16009,13 +15961,13 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>0.80980442</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>0.00710324</v>
       </c>
       <c r="AG98" t="n">
-        <v>0</v>
+        <v>0.00036732</v>
       </c>
       <c r="AH98" t="n">
         <v>0</v>
@@ -16039,7 +15991,7 @@
         <v>0</v>
       </c>
       <c r="AO98" t="n">
-        <v>0</v>
+        <v>0.00110122</v>
       </c>
       <c r="AP98" t="n">
         <v>0</v>
@@ -16051,7 +16003,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>F-73</t>
+          <t>F-9</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -16106,10 +16058,10 @@
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>0</v>
+        <v>0.86953481</v>
       </c>
       <c r="T99" t="n">
-        <v>0</v>
+        <v>0.00794096</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
@@ -16118,10 +16070,10 @@
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>2.982937</v>
+        <v>0</v>
       </c>
       <c r="X99" t="n">
-        <v>1.196823</v>
+        <v>0</v>
       </c>
       <c r="Y99" t="n">
         <v>0</v>
@@ -16136,7 +16088,7 @@
         <v>0</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>0.00397048</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -16178,272 +16130,6 @@
         <v>0</v>
       </c>
       <c r="AQ99" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>F-8</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>0</v>
-      </c>
-      <c r="C100" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" t="n">
-        <v>0</v>
-      </c>
-      <c r="S100" t="n">
-        <v>0</v>
-      </c>
-      <c r="T100" t="n">
-        <v>0</v>
-      </c>
-      <c r="U100" t="n">
-        <v>0</v>
-      </c>
-      <c r="V100" t="n">
-        <v>0</v>
-      </c>
-      <c r="W100" t="n">
-        <v>0</v>
-      </c>
-      <c r="X100" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y100" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA100" t="n">
-        <v>1.71857376</v>
-      </c>
-      <c r="AB100" t="n">
-        <v>6.27751241</v>
-      </c>
-      <c r="AC100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE100" t="n">
-        <v>0.80980442</v>
-      </c>
-      <c r="AF100" t="n">
-        <v>0.00710324</v>
-      </c>
-      <c r="AG100" t="n">
-        <v>0.00036732</v>
-      </c>
-      <c r="AH100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO100" t="n">
-        <v>0.00110122</v>
-      </c>
-      <c r="AP100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ100" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>F-9</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>0</v>
-      </c>
-      <c r="C101" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0</v>
-      </c>
-      <c r="S101" t="n">
-        <v>0.8695348000000001</v>
-      </c>
-      <c r="T101" t="n">
-        <v>0.00794096</v>
-      </c>
-      <c r="U101" t="n">
-        <v>0</v>
-      </c>
-      <c r="V101" t="n">
-        <v>0</v>
-      </c>
-      <c r="W101" t="n">
-        <v>0</v>
-      </c>
-      <c r="X101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC101" t="n">
-        <v>0.00397048</v>
-      </c>
-      <c r="AD101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ101" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16458,7 +16144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ101"/>
+  <dimension ref="A1:AQ99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -18510,10 +18196,10 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.43075104</v>
+        <v>0.43075105</v>
       </c>
       <c r="T15" t="n">
-        <v>0.56924896</v>
+        <v>0.56924895</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -19175,10 +18861,10 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.73168514</v>
+        <v>0.73168507</v>
       </c>
       <c r="T20" t="n">
-        <v>0.00013166</v>
+        <v>0.00013153</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -19199,7 +18885,7 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>6.63e-06</v>
+        <v>6.72e-06</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -19211,7 +18897,7 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.26788473</v>
+        <v>0.2678847</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -19241,7 +18927,7 @@
         <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.00029184</v>
+        <v>0.00029198</v>
       </c>
       <c r="AP20" t="n">
         <v>0</v>
@@ -19308,10 +18994,10 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.73168514</v>
+        <v>0.73168507</v>
       </c>
       <c r="T21" t="n">
-        <v>0.00013166</v>
+        <v>0.00013153</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -19332,7 +19018,7 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>6.63e-06</v>
+        <v>6.72e-06</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -19344,7 +19030,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.26788473</v>
+        <v>0.2678847</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -19374,7 +19060,7 @@
         <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.00029184</v>
+        <v>0.00029198</v>
       </c>
       <c r="AP21" t="n">
         <v>0</v>
@@ -19441,10 +19127,10 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.73168514</v>
+        <v>0.73168507</v>
       </c>
       <c r="T22" t="n">
-        <v>0.00013166</v>
+        <v>0.00013153</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -19465,7 +19151,7 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>6.63e-06</v>
+        <v>6.72e-06</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -19477,7 +19163,7 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.26788473</v>
+        <v>0.2678847</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -19507,7 +19193,7 @@
         <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.00029184</v>
+        <v>0.00029198</v>
       </c>
       <c r="AP22" t="n">
         <v>0</v>
@@ -19710,7 +19396,7 @@
         <v>0.00684585</v>
       </c>
       <c r="T24" t="n">
-        <v>0.00048732</v>
+        <v>0.00048683</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -19731,7 +19417,7 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.455e-05</v>
+        <v>2.486e-05</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -19773,10 +19459,10 @@
         <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>0.00108021</v>
+        <v>0.00108074</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.99156206</v>
+        <v>0.99156171</v>
       </c>
       <c r="AQ24" t="n">
         <v>0</v>
@@ -19843,7 +19529,7 @@
         <v>0.00684585</v>
       </c>
       <c r="T25" t="n">
-        <v>0.00048732</v>
+        <v>0.00048683</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -19864,7 +19550,7 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.455e-05</v>
+        <v>2.486e-05</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -19906,10 +19592,10 @@
         <v>0</v>
       </c>
       <c r="AO25" t="n">
-        <v>0.00108021</v>
+        <v>0.00108074</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.99156206</v>
+        <v>0.99156171</v>
       </c>
       <c r="AQ25" t="n">
         <v>0</v>
@@ -20106,10 +19792,10 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.03941232</v>
+        <v>0.03941224</v>
       </c>
       <c r="T27" t="n">
-        <v>0.00280557</v>
+        <v>0.00280276</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -20121,7 +19807,7 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0.95142186</v>
+        <v>0.95141993</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -20130,7 +19816,7 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.00014134</v>
+        <v>0.00014313</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -20172,7 +19858,7 @@
         <v>0</v>
       </c>
       <c r="AO27" t="n">
-        <v>0.00621891</v>
+        <v>0.00622194</v>
       </c>
       <c r="AP27" t="n">
         <v>0</v>
@@ -22977,7 +22663,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>F-3P</t>
+          <t>F-4</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -23014,22 +22700,22 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.01784584</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>0.00315183</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0.00070039</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -23038,10 +22724,10 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>0.4059953</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>0.57230663</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
         <v>0</v>
@@ -23110,7 +22796,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>F-3PT</t>
+          <t>F-40</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -23147,16 +22833,16 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.01784584</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>0.00315183</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0.00070039</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -23171,16 +22857,16 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>0.4059953</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>0.57230663</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="Y50" t="n">
         <v>0</v>
@@ -23243,7 +22929,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>F-4</t>
+          <t>F-41</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -23280,22 +22966,22 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>0.00158625</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>0.00028015</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>6.226e-05</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -23304,16 +22990,16 @@
         <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>0.22168451</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>0.05087023</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>0.53650265</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>0.18901395</v>
       </c>
       <c r="Y51" t="n">
         <v>0</v>
@@ -23376,7 +23062,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>F-40</t>
+          <t>F-41T</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -23413,16 +23099,16 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>0.00158625</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>0.00028015</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>6.226e-05</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -23437,16 +23123,16 @@
         <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>0.22168451</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>0.05087023</v>
       </c>
       <c r="W52" t="n">
-        <v>0.79</v>
+        <v>0.53650265</v>
       </c>
       <c r="X52" t="n">
-        <v>0.21</v>
+        <v>0.18901395</v>
       </c>
       <c r="Y52" t="n">
         <v>0</v>
@@ -23509,7 +23195,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>F-41</t>
+          <t>F-42</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -23546,16 +23232,16 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.00158625</v>
+        <v>0.00244983</v>
       </c>
       <c r="N53" t="n">
-        <v>0.00028015</v>
+        <v>0.00043267</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>6.226e-05</v>
+        <v>9.615000000000001e-05</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -23570,16 +23256,16 @@
         <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>0.22168451</v>
+        <v>0.00342373</v>
       </c>
       <c r="V53" t="n">
-        <v>0.05087023</v>
+        <v>0.00957738</v>
       </c>
       <c r="W53" t="n">
-        <v>0.53650265</v>
+        <v>0.82858217</v>
       </c>
       <c r="X53" t="n">
-        <v>0.18901395</v>
+        <v>0.15543807</v>
       </c>
       <c r="Y53" t="n">
         <v>0</v>
@@ -23642,7 +23328,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>F-41T</t>
+          <t>F-43</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -23679,16 +23365,16 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.00158625</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>0.00028015</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>6.226e-05</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -23703,19 +23389,19 @@
         <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>0.22168451</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>0.05087023</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>0.53650265</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>0.18901395</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -23775,7 +23461,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>F-42</t>
+          <t>F-44</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -23812,16 +23498,16 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.00244983</v>
+        <v>0.00239436</v>
       </c>
       <c r="N55" t="n">
-        <v>0.00043267</v>
+        <v>0.00042288</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>9.615000000000001e-05</v>
+        <v>9.397e-05</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -23830,25 +23516,25 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>0.0225769</v>
       </c>
       <c r="T55" t="n">
         <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>0.00342373</v>
+        <v>0.0002088</v>
       </c>
       <c r="V55" t="n">
-        <v>0.00957738</v>
+        <v>0.0005841</v>
       </c>
       <c r="W55" t="n">
-        <v>0.82858217</v>
+        <v>0.82330524</v>
       </c>
       <c r="X55" t="n">
-        <v>0.15543807</v>
+        <v>0.14815606</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>0.00225769</v>
       </c>
       <c r="Z55" t="n">
         <v>0</v>
@@ -23908,7 +23594,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>F-43</t>
+          <t>F-45</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -23963,7 +23649,7 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" t="n">
         <v>0</v>
@@ -23981,7 +23667,7 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -24041,7 +23727,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>F-44</t>
+          <t>F-45R</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -24078,16 +23764,16 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.00239436</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>0.00042288</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>9.397e-05</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -24096,25 +23782,25 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0225769</v>
+        <v>1</v>
       </c>
       <c r="T57" t="n">
         <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>0.0002088</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>0.0005841</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>0.82330524</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>0.14815606</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.00225769</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
         <v>0</v>
@@ -24174,7 +23860,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>F-45</t>
+          <t>F-46</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -24211,16 +23897,16 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>0.00244967</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>0.00043265</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>9.614e-05</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -24229,25 +23915,25 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
         <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>0.00021363</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>0.0005975899999999999</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>0.84232226</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>0.15157823</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>0.00230984</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
@@ -24307,7 +23993,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>F-45R</t>
+          <t>F-47</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -24440,7 +24126,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>F-46</t>
+          <t>F-47T</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -24477,16 +24163,16 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0.00244967</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>0.00043265</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>9.614e-05</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -24495,25 +24181,25 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T60" t="n">
         <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>0.00021363</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>0.0005975899999999999</v>
+        <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>0.84232226</v>
+        <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>0.15157823</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.00230984</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
         <v>0</v>
@@ -24573,7 +24259,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>F-47</t>
+          <t>F-48</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -24628,7 +24314,7 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>0.99966234</v>
       </c>
       <c r="T61" t="n">
         <v>0</v>
@@ -24646,7 +24332,7 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>0.00033766</v>
       </c>
       <c r="Z61" t="n">
         <v>0</v>
@@ -24706,7 +24392,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>F-47T</t>
+          <t>F-49</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -24743,16 +24429,16 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>0.00245528</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>0.00043364</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>9.636000000000001e-05</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -24761,25 +24447,25 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
         <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>0.00021412</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>0.0005989600000000001</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>0.8442528500000001</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>0.15192564</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>2.315e-05</v>
       </c>
       <c r="Z62" t="n">
         <v>0</v>
@@ -24839,7 +24525,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>F-48</t>
+          <t>F-49A</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -24876,16 +24562,16 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>0.00245528</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>0.00043364</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>9.636000000000001e-05</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -24894,25 +24580,25 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.99966234</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
         <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>0.00021412</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>0.0005989600000000001</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>0.8442528500000001</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>0.15192564</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.00033766</v>
+        <v>2.315e-05</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
@@ -24972,7 +24658,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>F-49</t>
+          <t>F-49B</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -25009,16 +24695,16 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0.00245528</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>0.00043364</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>9.636000000000001e-05</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -25033,19 +24719,19 @@
         <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>0.00021412</v>
+        <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>0.0005989600000000001</v>
+        <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>0.8442528500000001</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>0.15192564</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.315e-05</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
         <v>0</v>
@@ -25105,7 +24791,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>F-49A</t>
+          <t>F-5</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -25142,43 +24828,43 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>0.00245528</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>0.00043364</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>9.636000000000001e-05</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>1.08e-06</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>0.00060621</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>0.87167294</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>0.04521542</v>
       </c>
       <c r="U65" t="n">
-        <v>0.00021412</v>
+        <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>0.0005989600000000001</v>
+        <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>0.8442528500000001</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>0.15192564</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.315e-05</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
         <v>0</v>
@@ -25196,37 +24882,37 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>0.07882606</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>0.00074474</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>3.924e-05</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>3.13e-05</v>
       </c>
       <c r="AI65" t="n">
-        <v>0</v>
+        <v>0.00083089</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0</v>
+        <v>0.00020365</v>
       </c>
       <c r="AK65" t="n">
-        <v>0</v>
+        <v>0.00122083</v>
       </c>
       <c r="AL65" t="n">
-        <v>0</v>
+        <v>0.00024601</v>
       </c>
       <c r="AM65" t="n">
-        <v>0</v>
+        <v>3.563e-05</v>
       </c>
       <c r="AN65" t="n">
-        <v>0</v>
+        <v>2.066e-05</v>
       </c>
       <c r="AO65" t="n">
-        <v>0</v>
+        <v>0.00030533</v>
       </c>
       <c r="AP65" t="n">
         <v>0</v>
@@ -25238,7 +24924,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>F-49B</t>
+          <t>F-50A</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -25275,10 +24961,10 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>0.00245552</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>0.00043368</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -25299,19 +24985,19 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>0.00021414</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>0.00059902</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>0.84433421</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>0.15194028</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>2.315e-05</v>
       </c>
       <c r="Z66" t="n">
         <v>0</v>
@@ -25371,7 +25057,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>F-5</t>
+          <t>F-50B</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -25420,16 +25106,16 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.08e-06</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>0.00060621</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.87167294</v>
+        <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>0.04521542</v>
+        <v>0</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -25462,37 +25148,37 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0.07882606</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>0.00074474</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
-        <v>3.924e-05</v>
+        <v>0</v>
       </c>
       <c r="AH67" t="n">
-        <v>3.13e-05</v>
+        <v>0</v>
       </c>
       <c r="AI67" t="n">
-        <v>0.00083089</v>
+        <v>0</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0.00020365</v>
+        <v>0</v>
       </c>
       <c r="AK67" t="n">
-        <v>0.00122083</v>
+        <v>0</v>
       </c>
       <c r="AL67" t="n">
-        <v>0.00024601</v>
+        <v>0</v>
       </c>
       <c r="AM67" t="n">
-        <v>3.563e-05</v>
+        <v>0</v>
       </c>
       <c r="AN67" t="n">
-        <v>2.066e-05</v>
+        <v>0</v>
       </c>
       <c r="AO67" t="n">
-        <v>0.00030533</v>
+        <v>0</v>
       </c>
       <c r="AP67" t="n">
         <v>0</v>
@@ -25504,7 +25190,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>F-50A</t>
+          <t>F-51A</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -25541,10 +25227,10 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0.00245552</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0.00043368</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -25565,19 +25251,19 @@
         <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>0.00021414</v>
+        <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>0.00059902</v>
+        <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>0.84433421</v>
+        <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>0.15194028</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.315e-05</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -25637,7 +25323,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>F-50B</t>
+          <t>F-51B</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -25683,7 +25369,7 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -25704,10 +25390,10 @@
         <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>0.711</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>0.189</v>
       </c>
       <c r="Y69" t="n">
         <v>0</v>
@@ -25770,7 +25456,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>F-51A</t>
+          <t>F-52A</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -25903,7 +25589,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>F-51B</t>
+          <t>F-52B</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -25949,7 +25635,7 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -25970,10 +25656,10 @@
         <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>0.711</v>
+        <v>0.79</v>
       </c>
       <c r="X71" t="n">
-        <v>0.189</v>
+        <v>0.21</v>
       </c>
       <c r="Y71" t="n">
         <v>0</v>
@@ -26036,7 +25722,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>F-52A</t>
+          <t>F-53</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -26085,16 +25771,16 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>1.17e-06</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>0.00065862</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>0.94703004</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>0.04912435</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
@@ -26115,7 +25801,7 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>9.449999999999999e-06</v>
       </c>
       <c r="AB72" t="n">
         <v>0</v>
@@ -26127,37 +25813,37 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>8.564e-05</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>5.867e-05</v>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>3.83e-06</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>3.4e-05</v>
       </c>
       <c r="AI72" t="n">
-        <v>0</v>
+        <v>0.00090272</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0</v>
+        <v>0.00022125</v>
       </c>
       <c r="AK72" t="n">
-        <v>0</v>
+        <v>0.00132637</v>
       </c>
       <c r="AL72" t="n">
-        <v>0</v>
+        <v>0.00026728</v>
       </c>
       <c r="AM72" t="n">
-        <v>0</v>
+        <v>3.871e-05</v>
       </c>
       <c r="AN72" t="n">
-        <v>0</v>
+        <v>2.245e-05</v>
       </c>
       <c r="AO72" t="n">
-        <v>0</v>
+        <v>0.00021544</v>
       </c>
       <c r="AP72" t="n">
         <v>0</v>
@@ -26169,7 +25855,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>F-52B</t>
+          <t>F-54</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -26236,10 +25922,10 @@
         <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="Y73" t="n">
         <v>0</v>
@@ -26248,7 +25934,7 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB73" t="n">
         <v>0</v>
@@ -26302,7 +25988,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>F-53</t>
+          <t>F-55</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -26351,16 +26037,16 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.17e-06</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>0.00065862</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0.94703004</v>
+        <v>0.97570606</v>
       </c>
       <c r="T74" t="n">
-        <v>0.04912435</v>
+        <v>0.00891056</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
@@ -26381,49 +26067,49 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>9.449999999999999e-06</v>
+        <v>2.654e-05</v>
       </c>
       <c r="AB74" t="n">
         <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>0.00445528</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>8.564e-05</v>
+        <v>0.00227171</v>
       </c>
       <c r="AF74" t="n">
-        <v>5.867e-05</v>
+        <v>0.00797056</v>
       </c>
       <c r="AG74" t="n">
-        <v>3.83e-06</v>
+        <v>0.00041217</v>
       </c>
       <c r="AH74" t="n">
-        <v>3.4e-05</v>
+        <v>0</v>
       </c>
       <c r="AI74" t="n">
-        <v>0.00090272</v>
+        <v>0</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.00022125</v>
+        <v>0</v>
       </c>
       <c r="AK74" t="n">
-        <v>0.00132637</v>
+        <v>0</v>
       </c>
       <c r="AL74" t="n">
-        <v>0.00026728</v>
+        <v>0</v>
       </c>
       <c r="AM74" t="n">
-        <v>3.871e-05</v>
+        <v>0</v>
       </c>
       <c r="AN74" t="n">
-        <v>2.245e-05</v>
+        <v>0</v>
       </c>
       <c r="AO74" t="n">
-        <v>0.00021544</v>
+        <v>0.00024713</v>
       </c>
       <c r="AP74" t="n">
         <v>0</v>
@@ -26435,7 +26121,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>F-54</t>
+          <t>F-56</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -26568,7 +26254,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>F-55</t>
+          <t>F-57</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -26623,10 +26309,10 @@
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.97570606</v>
+        <v>0.96438903</v>
       </c>
       <c r="T76" t="n">
-        <v>0.00891056</v>
+        <v>0.0001738</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -26647,25 +26333,25 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.654e-05</v>
+        <v>8.899999999999999e-07</v>
       </c>
       <c r="AB76" t="n">
         <v>0</v>
       </c>
       <c r="AC76" t="n">
-        <v>0.00445528</v>
+        <v>0</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0.00227171</v>
+        <v>0.03539771</v>
       </c>
       <c r="AF76" t="n">
-        <v>0.00797056</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>0.00041217</v>
+        <v>0</v>
       </c>
       <c r="AH76" t="n">
         <v>0</v>
@@ -26689,7 +26375,7 @@
         <v>0</v>
       </c>
       <c r="AO76" t="n">
-        <v>0.00024713</v>
+        <v>3.858e-05</v>
       </c>
       <c r="AP76" t="n">
         <v>0</v>
@@ -26701,7 +26387,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>F-56</t>
+          <t>F-57T</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -26756,10 +26442,10 @@
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>0.96438903</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>0.0001738</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -26780,7 +26466,7 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1</v>
+        <v>8.899999999999999e-07</v>
       </c>
       <c r="AB77" t="n">
         <v>0</v>
@@ -26792,7 +26478,7 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>0.03539771</v>
       </c>
       <c r="AF77" t="n">
         <v>0</v>
@@ -26822,7 +26508,7 @@
         <v>0</v>
       </c>
       <c r="AO77" t="n">
-        <v>0</v>
+        <v>3.858e-05</v>
       </c>
       <c r="AP77" t="n">
         <v>0</v>
@@ -26834,7 +26520,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>F-57</t>
+          <t>F-58</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -26889,10 +26575,10 @@
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0.96438903</v>
+        <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>0.0001738</v>
+        <v>0</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
@@ -26913,7 +26599,7 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>8.899999999999999e-07</v>
+        <v>1</v>
       </c>
       <c r="AB78" t="n">
         <v>0</v>
@@ -26925,7 +26611,7 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0.03539771</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
         <v>0</v>
@@ -26955,7 +26641,7 @@
         <v>0</v>
       </c>
       <c r="AO78" t="n">
-        <v>3.858e-05</v>
+        <v>0</v>
       </c>
       <c r="AP78" t="n">
         <v>0</v>
@@ -26967,7 +26653,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>F-57T</t>
+          <t>F-59</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -27022,10 +26708,10 @@
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.96438903</v>
+        <v>0.55135622</v>
       </c>
       <c r="T79" t="n">
-        <v>0.0001738</v>
+        <v>0.44864378</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -27046,7 +26732,7 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>8.899999999999999e-07</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
         <v>0</v>
@@ -27058,7 +26744,7 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0.03539771</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
         <v>0</v>
@@ -27088,7 +26774,7 @@
         <v>0</v>
       </c>
       <c r="AO79" t="n">
-        <v>3.858e-05</v>
+        <v>0</v>
       </c>
       <c r="AP79" t="n">
         <v>0</v>
@@ -27100,7 +26786,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>F-58</t>
+          <t>F-6</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -27149,16 +26835,16 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>1.08e-06</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>0.00060621</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>0.87167294</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>0.04521542</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -27179,7 +26865,7 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
         <v>0</v>
@@ -27191,37 +26877,37 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>0.07882606</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>0.00074474</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>3.924e-05</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>3.13e-05</v>
       </c>
       <c r="AI80" t="n">
-        <v>0</v>
+        <v>0.00083089</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0</v>
+        <v>0.00020365</v>
       </c>
       <c r="AK80" t="n">
-        <v>0</v>
+        <v>0.00122083</v>
       </c>
       <c r="AL80" t="n">
-        <v>0</v>
+        <v>0.00024601</v>
       </c>
       <c r="AM80" t="n">
-        <v>0</v>
+        <v>3.563e-05</v>
       </c>
       <c r="AN80" t="n">
-        <v>0</v>
+        <v>2.066e-05</v>
       </c>
       <c r="AO80" t="n">
-        <v>0</v>
+        <v>0.00030533</v>
       </c>
       <c r="AP80" t="n">
         <v>0</v>
@@ -27233,7 +26919,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>F-59</t>
+          <t>F-60</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -27288,10 +26974,10 @@
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.55135622</v>
+        <v>1</v>
       </c>
       <c r="T81" t="n">
-        <v>0.44864378</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -27366,7 +27052,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>F-6</t>
+          <t>F-61</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -27415,16 +27101,16 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>1.08e-06</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>0.00060621</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.87167294</v>
+        <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>0.04521542</v>
+        <v>0</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
@@ -27445,7 +27131,7 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB82" t="n">
         <v>0</v>
@@ -27457,37 +27143,37 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0.07882606</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>0.00074474</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
-        <v>3.924e-05</v>
+        <v>0</v>
       </c>
       <c r="AH82" t="n">
-        <v>3.13e-05</v>
+        <v>0</v>
       </c>
       <c r="AI82" t="n">
-        <v>0.00083089</v>
+        <v>0</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.00020365</v>
+        <v>0</v>
       </c>
       <c r="AK82" t="n">
-        <v>0.00122083</v>
+        <v>0</v>
       </c>
       <c r="AL82" t="n">
-        <v>0.00024601</v>
+        <v>0</v>
       </c>
       <c r="AM82" t="n">
-        <v>3.563e-05</v>
+        <v>0</v>
       </c>
       <c r="AN82" t="n">
-        <v>2.066e-05</v>
+        <v>0</v>
       </c>
       <c r="AO82" t="n">
-        <v>0.00030533</v>
+        <v>0</v>
       </c>
       <c r="AP82" t="n">
         <v>0</v>
@@ -27499,7 +27185,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>F-60</t>
+          <t>F-62</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -27554,7 +27240,7 @@
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T83" t="n">
         <v>0</v>
@@ -27578,10 +27264,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>0.21513093</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>0.78486899</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -27590,7 +27276,7 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="AF83" t="n">
         <v>0</v>
@@ -27620,7 +27306,7 @@
         <v>0</v>
       </c>
       <c r="AO83" t="n">
-        <v>0</v>
+        <v>7e-08</v>
       </c>
       <c r="AP83" t="n">
         <v>0</v>
@@ -27632,7 +27318,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>F-61</t>
+          <t>F-63</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -27669,16 +27355,16 @@
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>0.01784584</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>0.00315183</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>0.00070039</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -27693,10 +27379,10 @@
         <v>0</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
+        <v>0.4059953</v>
       </c>
       <c r="V84" t="n">
-        <v>0</v>
+        <v>0.57230663</v>
       </c>
       <c r="W84" t="n">
         <v>0</v>
@@ -27711,7 +27397,7 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
         <v>0</v>
@@ -27765,7 +27451,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>F-62</t>
+          <t>F-63P</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -27802,16 +27488,16 @@
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>0.01784584</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>0.00315183</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>0.00070039</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -27826,10 +27512,10 @@
         <v>0</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>0.4059953</v>
       </c>
       <c r="V85" t="n">
-        <v>0</v>
+        <v>0.57230663</v>
       </c>
       <c r="W85" t="n">
         <v>0</v>
@@ -27844,10 +27530,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0.21513093</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>0.78486899</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -27856,7 +27542,7 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
         <v>0</v>
@@ -27886,7 +27572,7 @@
         <v>0</v>
       </c>
       <c r="AO85" t="n">
-        <v>7e-08</v>
+        <v>0</v>
       </c>
       <c r="AP85" t="n">
         <v>0</v>
@@ -27898,7 +27584,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>F-63</t>
+          <t>F-64</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -27935,16 +27621,16 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>0.01784584</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>0.00315183</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>0.00070039</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -27953,16 +27639,16 @@
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>0.95096771</v>
       </c>
       <c r="T86" t="n">
         <v>0</v>
       </c>
       <c r="U86" t="n">
-        <v>0.4059953</v>
+        <v>0</v>
       </c>
       <c r="V86" t="n">
-        <v>0.57230663</v>
+        <v>0</v>
       </c>
       <c r="W86" t="n">
         <v>0</v>
@@ -27977,7 +27663,7 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.23e-06</v>
       </c>
       <c r="AB86" t="n">
         <v>0</v>
@@ -27989,7 +27675,7 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>0.04903106</v>
       </c>
       <c r="AF86" t="n">
         <v>0</v>
@@ -28031,7 +27717,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>F-63P</t>
+          <t>F-65</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -28068,16 +27754,16 @@
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>0.01784584</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>0.00315183</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>0.00070039</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -28086,16 +27772,16 @@
         <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T87" t="n">
         <v>0</v>
       </c>
       <c r="U87" t="n">
-        <v>0.4059953</v>
+        <v>0</v>
       </c>
       <c r="V87" t="n">
-        <v>0.57230663</v>
+        <v>0</v>
       </c>
       <c r="W87" t="n">
         <v>0</v>
@@ -28164,7 +27850,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>F-64</t>
+          <t>F-66</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -28219,7 +27905,7 @@
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>0.95096888</v>
+        <v>0.99999871</v>
       </c>
       <c r="T88" t="n">
         <v>0</v>
@@ -28243,7 +27929,7 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.29e-06</v>
       </c>
       <c r="AB88" t="n">
         <v>0</v>
@@ -28255,7 +27941,7 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0.04903112</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
         <v>0</v>
@@ -28297,7 +27983,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>F-65</t>
+          <t>F-67</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -28430,7 +28116,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>F-66</t>
+          <t>F-68</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -28485,7 +28171,7 @@
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>1</v>
+        <v>0.91769157</v>
       </c>
       <c r="T90" t="n">
         <v>0</v>
@@ -28509,7 +28195,7 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.19e-06</v>
       </c>
       <c r="AB90" t="n">
         <v>0</v>
@@ -28521,7 +28207,7 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>0.08230725</v>
       </c>
       <c r="AF90" t="n">
         <v>0</v>
@@ -28563,7 +28249,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>F-67</t>
+          <t>F-69</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -28696,7 +28382,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>F-68</t>
+          <t>F-6P</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -28745,16 +28431,16 @@
         <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>1.08e-06</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>0.00060621</v>
       </c>
       <c r="S92" t="n">
-        <v>0.91769265</v>
+        <v>0.87167294</v>
       </c>
       <c r="T92" t="n">
-        <v>0</v>
+        <v>0.04521542</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -28787,37 +28473,37 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0.08230735</v>
+        <v>0.07882606</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>0.00074474</v>
       </c>
       <c r="AG92" t="n">
-        <v>0</v>
+        <v>3.924e-05</v>
       </c>
       <c r="AH92" t="n">
-        <v>0</v>
+        <v>3.13e-05</v>
       </c>
       <c r="AI92" t="n">
-        <v>0</v>
+        <v>0.00083089</v>
       </c>
       <c r="AJ92" t="n">
-        <v>0</v>
+        <v>0.00020365</v>
       </c>
       <c r="AK92" t="n">
-        <v>0</v>
+        <v>0.00122083</v>
       </c>
       <c r="AL92" t="n">
-        <v>0</v>
+        <v>0.00024601</v>
       </c>
       <c r="AM92" t="n">
-        <v>0</v>
+        <v>3.563e-05</v>
       </c>
       <c r="AN92" t="n">
-        <v>0</v>
+        <v>2.066e-05</v>
       </c>
       <c r="AO92" t="n">
-        <v>0</v>
+        <v>0.00030533</v>
       </c>
       <c r="AP92" t="n">
         <v>0</v>
@@ -28829,7 +28515,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>F-69</t>
+          <t>F-7</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -28884,7 +28570,7 @@
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T93" t="n">
         <v>0</v>
@@ -28908,10 +28594,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>0.21514402</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>0.78485591</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -28920,7 +28606,7 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="AF93" t="n">
         <v>0</v>
@@ -28950,7 +28636,7 @@
         <v>0</v>
       </c>
       <c r="AO93" t="n">
-        <v>0</v>
+        <v>5.999999999999999e-08</v>
       </c>
       <c r="AP93" t="n">
         <v>0</v>
@@ -28962,7 +28648,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>F-6P</t>
+          <t>F-70</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -29011,16 +28697,16 @@
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>1.08e-06</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>0.00060621</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>0.87167294</v>
+        <v>1</v>
       </c>
       <c r="T94" t="n">
-        <v>0.04521542</v>
+        <v>0</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -29053,37 +28739,37 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0.07882606</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>0.00074474</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
-        <v>3.924e-05</v>
+        <v>0</v>
       </c>
       <c r="AH94" t="n">
-        <v>3.13e-05</v>
+        <v>0</v>
       </c>
       <c r="AI94" t="n">
-        <v>0.00083089</v>
+        <v>0</v>
       </c>
       <c r="AJ94" t="n">
-        <v>0.00020365</v>
+        <v>0</v>
       </c>
       <c r="AK94" t="n">
-        <v>0.00122083</v>
+        <v>0</v>
       </c>
       <c r="AL94" t="n">
-        <v>0.00024601</v>
+        <v>0</v>
       </c>
       <c r="AM94" t="n">
-        <v>3.563e-05</v>
+        <v>0</v>
       </c>
       <c r="AN94" t="n">
-        <v>2.066e-05</v>
+        <v>0</v>
       </c>
       <c r="AO94" t="n">
-        <v>0.00030533</v>
+        <v>0</v>
       </c>
       <c r="AP94" t="n">
         <v>0</v>
@@ -29095,7 +28781,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>F-7</t>
+          <t>F-71</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -29150,7 +28836,7 @@
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T95" t="n">
         <v>0</v>
@@ -29174,10 +28860,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0.21514402</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>0.78485591</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -29186,7 +28872,7 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
         <v>0</v>
@@ -29216,7 +28902,7 @@
         <v>0</v>
       </c>
       <c r="AO95" t="n">
-        <v>5.999999999999999e-08</v>
+        <v>0</v>
       </c>
       <c r="AP95" t="n">
         <v>0</v>
@@ -29228,7 +28914,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>F-70</t>
+          <t>F-72</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -29361,7 +29047,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>F-71</t>
+          <t>F-73</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -29416,7 +29102,7 @@
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T97" t="n">
         <v>0</v>
@@ -29428,10 +29114,10 @@
         <v>0</v>
       </c>
       <c r="W97" t="n">
-        <v>0</v>
+        <v>0.71366227</v>
       </c>
       <c r="X97" t="n">
-        <v>0</v>
+        <v>0.28633773</v>
       </c>
       <c r="Y97" t="n">
         <v>0</v>
@@ -29494,7 +29180,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>F-72</t>
+          <t>F-8</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -29549,7 +29235,7 @@
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T98" t="n">
         <v>0</v>
@@ -29573,10 +29259,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>0.19497205</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>0.71218324</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -29585,13 +29271,13 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>0.09187223999999999</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>0.00080586</v>
       </c>
       <c r="AG98" t="n">
-        <v>0</v>
+        <v>4.167e-05</v>
       </c>
       <c r="AH98" t="n">
         <v>0</v>
@@ -29615,7 +29301,7 @@
         <v>0</v>
       </c>
       <c r="AO98" t="n">
-        <v>0</v>
+        <v>0.00012493</v>
       </c>
       <c r="AP98" t="n">
         <v>0</v>
@@ -29627,7 +29313,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>F-73</t>
+          <t>F-9</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -29682,10 +29368,10 @@
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>0</v>
+        <v>0.98648649</v>
       </c>
       <c r="T99" t="n">
-        <v>0</v>
+        <v>0.00900901</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
@@ -29694,10 +29380,10 @@
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>0.71366227</v>
+        <v>0</v>
       </c>
       <c r="X99" t="n">
-        <v>0.28633773</v>
+        <v>0</v>
       </c>
       <c r="Y99" t="n">
         <v>0</v>
@@ -29712,7 +29398,7 @@
         <v>0</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>0.0045045</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -29754,272 +29440,6 @@
         <v>0</v>
       </c>
       <c r="AQ99" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>F-8</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>0</v>
-      </c>
-      <c r="C100" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" t="n">
-        <v>0</v>
-      </c>
-      <c r="S100" t="n">
-        <v>0</v>
-      </c>
-      <c r="T100" t="n">
-        <v>0</v>
-      </c>
-      <c r="U100" t="n">
-        <v>0</v>
-      </c>
-      <c r="V100" t="n">
-        <v>0</v>
-      </c>
-      <c r="W100" t="n">
-        <v>0</v>
-      </c>
-      <c r="X100" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y100" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA100" t="n">
-        <v>0.19497205</v>
-      </c>
-      <c r="AB100" t="n">
-        <v>0.71218324</v>
-      </c>
-      <c r="AC100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE100" t="n">
-        <v>0.09187223999999999</v>
-      </c>
-      <c r="AF100" t="n">
-        <v>0.00080586</v>
-      </c>
-      <c r="AG100" t="n">
-        <v>4.167e-05</v>
-      </c>
-      <c r="AH100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO100" t="n">
-        <v>0.00012493</v>
-      </c>
-      <c r="AP100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ100" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>F-9</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>0</v>
-      </c>
-      <c r="C101" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0</v>
-      </c>
-      <c r="S101" t="n">
-        <v>0.98648649</v>
-      </c>
-      <c r="T101" t="n">
-        <v>0.00900901</v>
-      </c>
-      <c r="U101" t="n">
-        <v>0</v>
-      </c>
-      <c r="V101" t="n">
-        <v>0</v>
-      </c>
-      <c r="W101" t="n">
-        <v>0</v>
-      </c>
-      <c r="X101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC101" t="n">
-        <v>0.0045045</v>
-      </c>
-      <c r="AD101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ101" t="n">
         <v>0</v>
       </c>
     </row>
@@ -30034,7 +29454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -30258,12 +29678,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V103P_OffgasPressure</t>
+          <t>V103_OffgasSurge</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>PassThrough</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -30273,7 +29693,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>out=F-3P</t>
+          <t>out=F-63</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -30281,22 +29701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V103T_OffgasTemperature</t>
+          <t>P104_OffgasBlower</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>PassThrough</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>in=F-3P</t>
+          <t>in=F-63</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>out=F-3PT</t>
+          <t>out=F-63P</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -30304,22 +29724,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V103_OffgasSurge</t>
+          <t>M114_SolventMakeupMixer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PassThrough</t>
+          <t>Mixer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>in=F-3PT</t>
+          <t>makeup=F-16, recycle=F-15</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>out=F-63</t>
+          <t>out=F-7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -30327,22 +29747,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P104_OffgasBlower</t>
+          <t>M_X101_feed</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PassThrough</t>
+          <t>Mixer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>in=F-63</t>
+          <t>aq=F-6P, org=F-7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>out=F-63P</t>
+          <t>out=F_X101</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -30350,22 +29770,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M114_SolventMakeupMixer</t>
+          <t>X101_TBP_Extraction</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>SplitUnit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>makeup=F-16, recycle=F-15</t>
+          <t>in=F_X101</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>out=F-7</t>
+          <t>organic=F-8, aqueous=F-17</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -30373,22 +29793,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M_X101_feed</t>
+          <t>CF101_Coalescer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>Coalescer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>aq=F-6P, org=F-7</t>
+          <t>in=F-17</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>out=F_X101</t>
+          <t>aqueous=F-53, recovered_org=F-54</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -30396,45 +29816,49 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X101_TBP_Extraction</t>
+          <t>E102_RaffinateEvaporator</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SplitUnit</t>
+          <t>Evaporator</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>in=F_X101</t>
+          <t>in=F-53</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>organic=F-8, aqueous=F-17</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>vapour=F-20, liquid=F-19</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>F_vapour_mol_s=0.4592; F_liquid_mol_s=9.006</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CF101_Coalescer</t>
+          <t>M_X102_feed</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Coalescer</t>
+          <t>Mixer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>in=F-17</t>
+          <t>org=F-8, aq=F-9</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>aqueous=F-53, recovered_org=F-54</t>
+          <t>out=F_X102</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -30442,49 +29866,45 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E102_RaffinateEvaporator</t>
+          <t>X102_AHA_Strip</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Evaporator</t>
+          <t>SplitUnit</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>in=F-53</t>
+          <t>in=F_X102</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>vapour=F-20, liquid=F-19</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>F_vapour_mol_s=0.4592; F_liquid_mol_s=9.006</t>
-        </is>
-      </c>
+          <t>aqueous=F-18, organic=F-10</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M_X102_feed</t>
+          <t>CF102_Coalescer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>Coalescer</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>org=F-8, aq=F-9</t>
+          <t>in=F-18</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>out=F_X102</t>
+          <t>aqueous=F-55, recovered_org=F-56</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -30492,45 +29912,49 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X102_AHA_Strip</t>
+          <t>EV101_PuNpEvaporator</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SplitUnit</t>
+          <t>Evaporator</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>in=F_X102</t>
+          <t>in=F-55</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>aqueous=F-18, organic=F-10</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>vapour=F-22, liquid=F-21</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>F_vapour_mol_s=0.01212; F_liquid_mol_s=0.8811</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CF102_Coalescer</t>
+          <t>M201_EvapOverheadMixer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Coalescer</t>
+          <t>Mixer</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>in=F-18</t>
+          <t>e101=F-20, e102=F-22</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>aqueous=F-55, recovered_org=F-56</t>
+          <t>out=F-23T</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -30538,34 +29962,30 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EV101_PuNpEvaporator</t>
+          <t>B101_OverheadBlower</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Evaporator</t>
+          <t>PassThrough</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>in=F-55</t>
+          <t>in=F-23T</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>vapour=F-22, liquid=F-21</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>F_vapour_mol_s=0.01212; F_liquid_mol_s=0.8811</t>
-        </is>
-      </c>
+          <t>out=F-23TP</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M201_EvapOverheadMixer</t>
+          <t>M_X103_feed</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -30575,12 +29995,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>e101=F-20, e102=F-22</t>
+          <t>org=F-10, aq=F-11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>out=F-23T</t>
+          <t>out=F_X103</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -30588,22 +30008,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B101_OverheadBlower</t>
+          <t>X103_Final_Strip</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PassThrough</t>
+          <t>SplitUnit</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>in=F-23T</t>
+          <t>in=F_X103</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>out=F-23TP</t>
+          <t>aqueous=F-12, organic=F-13</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -30611,22 +30031,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M_X103_feed</t>
+          <t>CF103_Coalescer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>Coalescer</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>org=F-10, aq=F-11</t>
+          <t>in=F-12</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>out=F_X103</t>
+          <t>aqueous=F-57, recovered_org=F-58</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -30634,22 +30054,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X103_Final_Strip</t>
+          <t>E107_UFeedHeater</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SplitUnit</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>in=F_X103</t>
+          <t>in=F-57</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>aqueous=F-12, organic=F-13</t>
+          <t>out=F-57T</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -30657,22 +30077,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CF103_Coalescer</t>
+          <t>E107_SteamCondensate</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Coalescer</t>
+          <t>PassThrough</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>in=F-12</t>
+          <t>in=U67_src</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>aqueous=F-57, recovered_org=F-58</t>
+          <t>out=F-67</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -30680,22 +30100,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E107_UFeedHeater</t>
+          <t>EV103A_UConcentrator1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>SplitUnit</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>in=F-57</t>
+          <t>in=F-57T</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>out=F-57T</t>
+          <t>vapour=F-65, to_raw=F-64_raw</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -30703,22 +30123,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>E107_SteamCondensate</t>
+          <t>EV103A_InternalCleaner</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PassThrough</t>
+          <t>SplitUnit</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>in=U67_src</t>
+          <t>in=F-64_raw</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>out=F-67</t>
+          <t>aux=F-64_aux, clean=F-64</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -30726,22 +30146,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EV103A_UConcentrator1</t>
+          <t>EV103A_CondensatePass</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SplitUnit</t>
+          <t>PassThrough</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>in=F-57T</t>
+          <t>in=F-67</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>vapour=F-65, to_raw=F-64_raw</t>
+          <t>out=F-69</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -30749,7 +30169,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EV103A_InternalCleaner</t>
+          <t>EV103B_UConcentrator2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -30759,12 +30179,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>in=F-64_raw</t>
+          <t>in=F-64</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>aux=F-64_aux, clean=F-64</t>
+          <t>to_C1=F-66, to_C2=F-68</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -30772,7 +30192,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EV103A_CondensatePass</t>
+          <t>EV103B_OverheadPass</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -30782,12 +30202,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>in=F-67</t>
+          <t>in=F-65</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>out=F-69</t>
+          <t>out=F-72</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -30795,22 +30215,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EV103B_UConcentrator2</t>
+          <t>EV103C_UConcentrator3</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SplitUnit</t>
+          <t>EV103CPerformanceStage</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>in=F-64</t>
+          <t>light=F-66, heavy=F-68, aux=F-64_aux</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>to_C1=F-66, to_C2=F-68</t>
+          <t>product=F-24, vapour=F-25, waste=F-70, sink=F-70_sink</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -30818,22 +30238,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EV103B_OverheadPass</t>
+          <t>M272_EV103_WasteMixer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PassThrough</t>
+          <t>Mixer</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>in=F-65</t>
+          <t>a=F-69, b=F-72, c=F-70</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>out=F-72</t>
+          <t>out=F-71</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -30841,22 +30261,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EV103C_UConcentrator3</t>
+          <t>P105_UProductPump</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EV103CPerformanceStage</t>
+          <t>PassThrough</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>light=F-66, heavy=F-68, aux=F-64_aux</t>
+          <t>in=F-24</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>product=F-24, vapour=F-25, waste=F-70, sink=F-70_sink</t>
+          <t>out=F-24P</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -30864,22 +30284,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>M272_EV103_WasteMixer</t>
+          <t>E109_UProductHeater</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>a=F-69, b=F-72, c=F-70</t>
+          <t>in=F-24P</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>out=F-71</t>
+          <t>out=F-24PT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -30887,22 +30307,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>P105_UProductPump</t>
+          <t>R101_ThermalReactor</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PassThrough</t>
+          <t>CalcinerReactor</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>in=F-24</t>
+          <t>in=F-24PT, air=F-73</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>out=F-24P</t>
+          <t>solids=F-26, offgas=F-29</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -30910,22 +30330,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>E109_UProductHeater</t>
+          <t>P106_ReactorOffgasBlower</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>PassThrough</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>in=F-24P</t>
+          <t>in=F-29</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>out=F-24PT</t>
+          <t>out=F-29P</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -30933,22 +30353,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>R101_ThermalReactor</t>
+          <t>E111_ReactorOffgasCooler</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CalcinerReactor</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>in=F-24PT, air=F-73</t>
+          <t>in=F-29P</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>solids=F-26, offgas=F-29</t>
+          <t>out=F-29TP</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -30956,22 +30376,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>P106_ReactorOffgasBlower</t>
+          <t>E110_ProductCooler</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PassThrough</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>in=F-29</t>
+          <t>in=F-26</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>out=F-29P</t>
+          <t>out=F-26T</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -30979,22 +30399,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>E111_ReactorOffgasCooler</t>
+          <t>K101_UProductSeparator</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>ConversionReactor</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>in=F-29P</t>
+          <t>in=F-26T</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>out=F-29TP</t>
+          <t>solid=F-27, gas=F-28, liquid=F-28</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -31002,22 +30422,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>E110_ProductCooler</t>
+          <t>M301_HotVapourMixer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>Mixer</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>in=F-26</t>
+          <t>evaps=F-23TP, ucon=F-25, calc=F-29TP</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>out=F-26T</t>
+          <t>out=F-30TP</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -31025,22 +30445,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>K101_UProductSeparator</t>
+          <t>K301_Condenser</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ConversionReactor</t>
+          <t>PhaseCondenser</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>in=F-26T</t>
+          <t>in=F-30TP</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>solid=F-27, gas=F-28, liquid=F-28</t>
+          <t>liquid=F-31, gas=F-32</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -31048,7 +30468,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>M301_HotVapourMixer</t>
+          <t>M302_OffgasMixer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -31058,12 +30478,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>evaps=F-23TP, ucon=F-25, calc=F-29TP</t>
+          <t>cond=F-32, diss=F-63P, air=F-40</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>out=F-30TP</t>
+          <t>out=F-41</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -31071,22 +30491,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>K301_Condenser</t>
+          <t>E113_OffgasCooler</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PhaseCondenser</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>in=F-30TP</t>
+          <t>in=F-41</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>liquid=F-31, gas=F-32</t>
+          <t>out=F-41T</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -31094,45 +30514,49 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>M302_OffgasMixer</t>
+          <t>D101_NO2_Absorber</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>NOxAbsorber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>cond=F-32, diss=F-63P, air=F-40</t>
+          <t>gas=F-41T, water=F-39</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>out=F-41</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
+          <t>gas_out=F-42, aqueous=F-35</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>NO2_captured_mol_s=1.91; NO_captured_mol_s=1.026; HNO3_produced_mol_s=2.299</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>E113_OffgasCooler</t>
+          <t>M303_AcidMixer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>Mixer</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>in=F-41</t>
+          <t>abs=F-35, cond=F-31</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>out=F-41T</t>
+          <t>out=F-36</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -31140,72 +30564,72 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>D101_NO2_Absorber</t>
+          <t>E118_AcidTrimHeater</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NOxAbsorber</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>gas=F-41T, water=F-39</t>
+          <t>in=F-36</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>gas_out=F-42, aqueous=F-35</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>NO2_captured_mol_s=1.91; NO_captured_mol_s=1.026; HNO3_produced_mol_s=2.299</t>
-        </is>
-      </c>
+          <t>out=F-36T</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>M303_AcidMixer</t>
+          <t>E104_HNO3_Concentrator</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>AcidConcentrator</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>abs=F-35, cond=F-31</t>
+          <t>in=F-36T</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>out=F-36</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
+          <t>concentrated=F-38, steam=F-37</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>H2O_evaporated_mol_s=24.39; HNO3_conc_mol_s=2.564; actual_HNO3_mass_frac=0.74</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>E118_AcidTrimHeater</t>
+          <t>V104_AcidPurge</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>PurgeSplitter</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>in=F-36</t>
+          <t>in=F-38</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>out=F-36T</t>
+          <t>purge=F-59, recycle=F-2R</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -31213,49 +30637,49 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>E104_HNO3_Concentrator</t>
+          <t>R103_NOxReduction</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AcidConcentrator</t>
+          <t>SCRReactor</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>in=F-36T</t>
+          <t>gas=F-42, nh3=F-43</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>concentrated=F-38, steam=F-37</t>
+          <t>out=F-44</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>H2O_evaporated_mol_s=24.39; HNO3_conc_mol_s=2.564; actual_HNO3_mass_frac=0.74</t>
+          <t>NO_removed_mol_s=0.05061; NO2_removed_mol_s=0.01809; NH3_consumed_mol_s=0.0868; N2_produced_mol_s=0.07775</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>V104_AcidPurge</t>
+          <t>KO101_KnockoutPot</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PurgeSplitter</t>
+          <t>KnockoutPot</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>in=F-38</t>
+          <t>in=F-44</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>purge=F-59, recycle=F-2R</t>
+          <t>gas=F-46, liquid=F-45</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -31263,49 +30687,45 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>R103_NOxReduction</t>
+          <t>V105_KOWaterPurge</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SCRReactor</t>
+          <t>PurgeSplitter</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>gas=F-42, nh3=F-43</t>
+          <t>in=F-45</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>out=F-44</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>NO_removed_mol_s=0.05061; NO2_removed_mol_s=0.01809; NH3_consumed_mol_s=0.0868; N2_produced_mol_s=0.07775</t>
-        </is>
-      </c>
+          <t>purge=F-60, recycle=F-45R</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>KO101_KnockoutPot</t>
+          <t>E116_D102WaterHeater</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>KnockoutPot</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>in=F-44</t>
+          <t>in=F-47</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>gas=F-46, liquid=F-45</t>
+          <t>out=F-47T</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -31313,45 +30733,49 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>V105_KOWaterPurge</t>
+          <t>D102_NH3_Absorber</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PurgeSplitter</t>
+          <t>NH3Absorber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>in=F-45</t>
+          <t>gas=F-46, water=F-47T</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>purge=F-60, recycle=F-45R</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>gas_out=F-49, aqueous=F-48</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>NH3_captured_mol_s=0.01289</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>E116_D102WaterHeater</t>
+          <t>V201_TSA_Split</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>SplitUnit</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>in=F-47</t>
+          <t>in=F-49</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>out=F-47T</t>
+          <t>A=F-49A, B=F-49B</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -31359,111 +30783,107 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>D102_NH3_Absorber</t>
+          <t>TSA101A</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NH3Absorber</t>
+          <t>TSAColumn</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>gas=F-46, water=F-47T</t>
+          <t>process_gas=F-49A, regen_air=F-52A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>gas_out=F-49, aqueous=F-48</t>
+          <t>process_out=F-50A, regen_out=F-51A</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>NH3_captured_mol_s=0.01289</t>
+          <t>I_captured_mol_s=0.0005419; I_slip_mol_s=0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>V201_TSA_Split</t>
+          <t>TSA101B</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SplitUnit</t>
+          <t>TSAColumn</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>in=F-49</t>
+          <t>process_gas=F-49B, regen_air=F-52B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>A=F-49A, B=F-49B</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
+          <t>process_out=F-50B, regen_out=F-51B</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>I_captured_mol_s=0; I_slip_mol_s=0</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TSA101A</t>
+          <t>M_StackGasMixer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TSAColumn</t>
+          <t>Mixer</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>process_gas=F-49A, regen_air=F-52A</t>
+          <t>A=F-50A, B=F-50B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>process_out=F-50A, regen_out=F-51A</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>I_captured_mol_s=0.0005419; I_slip_mol_s=0</t>
-        </is>
-      </c>
+          <t>out=F_StackGas</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TSA101B</t>
+          <t>M132_SolventRecoveryMixer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TSAColumn</t>
+          <t>Mixer</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>process_gas=F-49B, regen_air=F-52B</t>
+          <t>c1=F-54, c2=F-56, c3=F-58</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>process_out=F-50B, regen_out=F-51B</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>I_captured_mol_s=0; I_slip_mol_s=0</t>
-        </is>
-      </c>
+          <t>out=F-61</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>M_StackGasMixer</t>
+          <t>M133_SolventMixer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -31473,12 +30893,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>A=F-50A, B=F-50B</t>
+          <t>main=F-13, rec=F-61</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>out=F_StackGas</t>
+          <t>out=F-62</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -31486,22 +30906,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>M132_SolventRecoveryMixer</t>
+          <t>HX133_SolventCooler</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>c1=F-54, c2=F-56, c3=F-58</t>
+          <t>in=F-62</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>out=F-61</t>
+          <t>out=F-13T</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -31509,71 +30929,25 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>M133_SolventMixer</t>
+          <t>V133_SolventPurge</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>PurgeSplitter</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>main=F-13, rec=F-61</t>
+          <t>in=F-13T</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>out=F-62</t>
+          <t>purge=F-14, recycle=F-15</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>HX133_SolventCooler</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Conditioner</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>in=F-62</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>out=F-13T</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>V133_SolventPurge</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>PurgeSplitter</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>in=F-13T</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>purge=F-14, recycle=F-15</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/process_sim/results/stream_results.xlsx
+++ b/process_sim/results/stream_results.xlsx
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>475</v>
+        <v>650</v>
       </c>
       <c r="C30" t="n">
         <v>100000</v>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>475</v>
+        <v>650</v>
       </c>
       <c r="C31" t="n">
         <v>100000</v>

--- a/process_sim/results/stream_results.xlsx
+++ b/process_sim/results/stream_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Streams" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MolarFlows" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoleFractions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Streams" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="MolarFlows" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MoleFractions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Units" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
@@ -1386,11 +1386,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>F-2STP</t>
+          <t>F-2W</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>373.15</v>
+        <v>298.15</v>
       </c>
       <c r="C40" t="n">
         <v>100000</v>
@@ -1401,16 +1401,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>9.632023</v>
+        <v>3.268202</v>
       </c>
       <c r="F40" t="n">
-        <v>305.650226</v>
+        <v>58.876661</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>F-2W</t>
+          <t>F-2WM</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1425,40 +1425,40 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3.268202</v>
+        <v>3.391888</v>
       </c>
       <c r="F41" t="n">
-        <v>58.876661</v>
+        <v>61.10487</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>F-2WM</t>
+          <t>F-3</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>298.15</v>
+        <v>373.15</v>
       </c>
       <c r="C42" t="n">
         <v>100000</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3.391888</v>
+        <v>0.773725</v>
       </c>
       <c r="F42" t="n">
-        <v>61.10487</v>
+        <v>29.893158</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>F-3</t>
+          <t>F-30</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1473,23 +1473,23 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.773725</v>
+        <v>15.270966</v>
       </c>
       <c r="F43" t="n">
-        <v>29.893158</v>
+        <v>378.78361</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>F-30</t>
+          <t>F-30P</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>373.15</v>
       </c>
       <c r="C44" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1506,14 +1506,14 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>F-30P</t>
+          <t>F-30TP</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>373.15</v>
+        <v>298.15</v>
       </c>
       <c r="C45" t="n">
-        <v>110000</v>
+        <v>100000</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>F-30TP</t>
+          <t>F-31</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1541,27 +1541,27 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>15.270966</v>
+        <v>9.475647</v>
       </c>
       <c r="F46" t="n">
-        <v>378.78361</v>
+        <v>182.599848</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>F-31</t>
+          <t>F-31P</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>298.15</v>
       </c>
       <c r="C47" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1578,38 +1578,38 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>F-31P</t>
+          <t>F-32</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>298.15</v>
       </c>
       <c r="C48" t="n">
-        <v>110000</v>
+        <v>100000</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>9.475647</v>
+        <v>5.79532</v>
       </c>
       <c r="F48" t="n">
-        <v>182.599848</v>
+        <v>196.183763</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>F-32</t>
+          <t>F-32P</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>298.15</v>
       </c>
       <c r="C49" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1626,31 +1626,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>F-32P</t>
+          <t>F-35</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>298.15</v>
+        <v>313.15</v>
       </c>
       <c r="C50" t="n">
-        <v>110000</v>
+        <v>100000</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5.79532</v>
+        <v>20.624722</v>
       </c>
       <c r="F50" t="n">
-        <v>196.183763</v>
+        <v>475.012352</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>F-35</t>
+          <t>F-36</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1665,16 +1665,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>20.624722</v>
+        <v>30.100369</v>
       </c>
       <c r="F51" t="n">
-        <v>475.012352</v>
+        <v>657.6122</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>F-36</t>
+          <t>F-36T</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1698,31 +1698,31 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>F-36T</t>
+          <t>F-37</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>313.15</v>
+        <v>373.15</v>
       </c>
       <c r="C53" t="n">
         <v>100000</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>30.100369</v>
+        <v>24.386271</v>
       </c>
       <c r="F53" t="n">
-        <v>657.6122</v>
+        <v>439.318677</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>F-37</t>
+          <t>F-38</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1733,24 +1733,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>24.386271</v>
+        <v>5.714098</v>
       </c>
       <c r="F54" t="n">
-        <v>439.318677</v>
+        <v>218.293522</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>F-38</t>
+          <t>F-39</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>373.15</v>
+        <v>298.15</v>
       </c>
       <c r="C55" t="n">
         <v>100000</v>
@@ -1761,47 +1761,47 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5.714098</v>
+        <v>19.475113</v>
       </c>
       <c r="F55" t="n">
-        <v>218.293522</v>
+        <v>350.844152</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>F-39</t>
+          <t>F-3P</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>298.15</v>
+        <v>373.15</v>
       </c>
       <c r="C56" t="n">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>19.475113</v>
+        <v>0.773725</v>
       </c>
       <c r="F56" t="n">
-        <v>350.844152</v>
+        <v>29.893158</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>F-3T</t>
+          <t>F-3PT</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>298.15</v>
       </c>
       <c r="C57" t="n">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>F-45</t>
+          <t>F-44T</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -2045,20 +2045,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.130196</v>
+        <v>5.766786</v>
       </c>
       <c r="F67" t="n">
-        <v>2.345483</v>
+        <v>165.2226</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>F-45R</t>
+          <t>F-45</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -2073,16 +2073,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.123686</v>
+        <v>0.130196</v>
       </c>
       <c r="F68" t="n">
-        <v>2.228209</v>
+        <v>2.345483</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>F-46</t>
+          <t>F-45R</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -2093,48 +2093,48 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5.63659</v>
+        <v>0.123686</v>
       </c>
       <c r="F69" t="n">
-        <v>162.877116</v>
+        <v>2.228209</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>F-47</t>
+          <t>F-46</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>298.15</v>
+        <v>323.15</v>
       </c>
       <c r="C70" t="n">
         <v>100000</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>38.159711</v>
+        <v>5.63659</v>
       </c>
       <c r="F70" t="n">
-        <v>687.447198</v>
+        <v>162.877116</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>F-47T</t>
+          <t>F-47</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>323.15</v>
+        <v>298.15</v>
       </c>
       <c r="C71" t="n">
         <v>100000</v>
@@ -2154,7 +2154,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>F-48</t>
+          <t>F-47T</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -2169,16 +2169,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>38.172601</v>
+        <v>38.159711</v>
       </c>
       <c r="F72" t="n">
-        <v>687.6667169999999</v>
+        <v>687.447198</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>F-49</t>
+          <t>F-48</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -2189,24 +2189,24 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5.6237</v>
+        <v>38.172601</v>
       </c>
       <c r="F73" t="n">
-        <v>162.657597</v>
+        <v>687.6667169999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>F-49A</t>
+          <t>F-49</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>298.15</v>
+        <v>323.15</v>
       </c>
       <c r="C74" t="n">
         <v>100000</v>
@@ -2226,7 +2226,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>F-49B</t>
+          <t>F-49A</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -2241,64 +2241,64 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>5.6237</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>162.657597</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>F-5</t>
+          <t>F-49B</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>373.15</v>
+        <v>298.15</v>
       </c>
       <c r="C76" t="n">
         <v>100000</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>10.283591</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>522.665717</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>F-50A</t>
+          <t>F-5</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>298.15</v>
+        <v>373.15</v>
       </c>
       <c r="C77" t="n">
         <v>100000</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5.623158</v>
+        <v>10.283591</v>
       </c>
       <c r="F77" t="n">
-        <v>162.520056</v>
+        <v>522.665717</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>F-50B</t>
+          <t>F-50A</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -2313,16 +2313,16 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>5.623158</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>162.520056</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>F-51A</t>
+          <t>F-50B</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2346,7 +2346,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>F-51B</t>
+          <t>F-51A</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2361,16 +2361,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.010838</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0.5565020000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>F-52A</t>
+          <t>F-51B</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2385,16 +2385,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>0.010838</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>0.5565020000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>F-52B</t>
+          <t>F-52A</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -2409,16 +2409,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.009754000000000001</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0.28142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>F-53</t>
+          <t>F-52B</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -2429,27 +2429,27 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>9.465305000000001</v>
+        <v>0.009754000000000001</v>
       </c>
       <c r="F83" t="n">
-        <v>199.779915</v>
+        <v>0.28142</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>F-53PT</t>
+          <t>F-53</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>318.15</v>
+        <v>298.15</v>
       </c>
       <c r="C84" t="n">
-        <v>9332.57</v>
+        <v>100000</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -2466,14 +2466,14 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>F-54</t>
+          <t>F-53PT</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>298.15</v>
+        <v>318.15</v>
       </c>
       <c r="C85" t="n">
-        <v>100000</v>
+        <v>9332.57</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -2481,16 +2481,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.002123</v>
+        <v>9.465305000000001</v>
       </c>
       <c r="F85" t="n">
-        <v>0.565406</v>
+        <v>199.779915</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>F-55</t>
+          <t>F-54</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -2505,23 +2505,23 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.891185</v>
+        <v>0.002123</v>
       </c>
       <c r="F86" t="n">
-        <v>20.94116</v>
+        <v>0.565406</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>F-55PT</t>
+          <t>F-55</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>318.15</v>
+        <v>298.15</v>
       </c>
       <c r="C87" t="n">
-        <v>9332.57</v>
+        <v>100000</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -2538,14 +2538,14 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>F-56</t>
+          <t>F-55PT</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>298.15</v>
+        <v>318.15</v>
       </c>
       <c r="C88" t="n">
-        <v>100000</v>
+        <v>9332.57</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2553,23 +2553,23 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.000148</v>
+        <v>0.891185</v>
       </c>
       <c r="F88" t="n">
-        <v>0.03947</v>
+        <v>20.94116</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>F-57</t>
+          <t>F-56</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>379.2</v>
+        <v>298.15</v>
       </c>
       <c r="C89" t="n">
-        <v>87290</v>
+        <v>100000</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -2577,20 +2577,20 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>22.820119</v>
+        <v>0.000148</v>
       </c>
       <c r="F89" t="n">
-        <v>715.157753</v>
+        <v>0.03947</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>F-57T</t>
+          <t>F-57</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>379.2</v>
+        <v>343.15</v>
       </c>
       <c r="C90" t="n">
         <v>87290</v>
@@ -2614,7 +2614,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>379.2</v>
+        <v>343.15</v>
       </c>
       <c r="C91" t="n">
         <v>87290</v>
@@ -2785,7 +2785,7 @@
         <v>298.15</v>
       </c>
       <c r="C98" t="n">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>298.15</v>
       </c>
       <c r="C99" t="n">
-        <v>110000</v>
+        <v>100000</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>F-2STP</t>
+          <t>F-2W</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -8547,10 +8547,10 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>6.69562032</v>
+        <v>3.26820211</v>
       </c>
       <c r="T40" t="n">
-        <v>2.936403</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -8625,7 +8625,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>F-2W</t>
+          <t>F-2WM</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -8680,7 +8680,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.26820211</v>
+        <v>3.39188843</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -8758,7 +8758,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>F-2WM</t>
+          <t>F-3</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -8795,16 +8795,16 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>0.01380778</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>0.00243865</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>0.00054191</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -8813,16 +8813,16 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>3.39188843</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>0.31412884</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>0.44280813</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
@@ -8891,7 +8891,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>F-3</t>
+          <t>F-30</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -8928,16 +8928,16 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.01380778</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0.00243865</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0.00054191</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -8946,22 +8946,22 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>9.211271740000001</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>0.26437484</v>
       </c>
       <c r="U43" t="n">
-        <v>0.31412884</v>
+        <v>1.61555968</v>
       </c>
       <c r="V43" t="n">
-        <v>0.44280813</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>2.982937</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.196823</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
@@ -9024,7 +9024,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>F-30</t>
+          <t>F-30P</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -9157,7 +9157,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>F-30P</t>
+          <t>F-30TP</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -9290,7 +9290,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>F-30TP</t>
+          <t>F-31</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -9351,16 +9351,16 @@
         <v>0.26437484</v>
       </c>
       <c r="U46" t="n">
-        <v>1.61555968</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>2.982937</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.196823</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
         <v>0</v>
@@ -9423,7 +9423,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>F-31</t>
+          <t>F-31P</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -9556,7 +9556,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>F-31P</t>
+          <t>F-32</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -9611,22 +9611,22 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>9.211271740000001</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>0.26437484</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.61555968</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>2.982937</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.196823</v>
       </c>
       <c r="Y48" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>F-32</t>
+          <t>F-32P</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -9822,7 +9822,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>F-32P</t>
+          <t>F-35</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -9877,22 +9877,22 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>18.32550279</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.2992195</v>
       </c>
       <c r="U50" t="n">
-        <v>1.61555968</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>2.982937</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1.196823</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
         <v>0</v>
@@ -9955,7 +9955,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>F-35</t>
+          <t>F-36</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -10010,10 +10010,10 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>18.32550279</v>
+        <v>27.53677453</v>
       </c>
       <c r="T51" t="n">
-        <v>2.2992195</v>
+        <v>2.56359434</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -10088,7 +10088,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>F-36</t>
+          <t>F-36T</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -10221,7 +10221,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>F-36T</t>
+          <t>F-37</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -10276,10 +10276,10 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>27.53677453</v>
+        <v>24.3862713</v>
       </c>
       <c r="T53" t="n">
-        <v>2.56359434</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -10354,7 +10354,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>F-37</t>
+          <t>F-38</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -10409,10 +10409,10 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>24.3862713</v>
+        <v>3.15050324</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.56359434</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -10487,7 +10487,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>F-38</t>
+          <t>F-39</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -10542,10 +10542,10 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>3.15050324</v>
+        <v>19.47511254</v>
       </c>
       <c r="T55" t="n">
-        <v>2.56359434</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -10620,7 +10620,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>F-39</t>
+          <t>F-3P</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -10657,16 +10657,16 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>0.01380778</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>0.00243865</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>0.00054191</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -10675,16 +10675,16 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>19.47511254</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
         <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>0.31412884</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>0.44280813</v>
       </c>
       <c r="W56" t="n">
         <v>0</v>
@@ -10753,7 +10753,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>F-3T</t>
+          <t>F-3PT</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -12083,7 +12083,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>F-45</t>
+          <t>F-44T</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -12120,16 +12120,16 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>0.01380778</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>0.00243865</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>0.00054191</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -12144,19 +12144,19 @@
         <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>0.00120413</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>0.00336837</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>4.74782485</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>0.85438425</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>0.01301961</v>
       </c>
       <c r="Z67" t="n">
         <v>0</v>
@@ -12216,7 +12216,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>F-45R</t>
+          <t>F-45</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -12271,7 +12271,7 @@
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.12368632</v>
+        <v>0.13019613</v>
       </c>
       <c r="T68" t="n">
         <v>0</v>
@@ -12349,7 +12349,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>F-46</t>
+          <t>F-45R</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -12386,16 +12386,16 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>0.01380778</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>0.00243865</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>0.00054191</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -12404,25 +12404,25 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>0.12368632</v>
       </c>
       <c r="T69" t="n">
         <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>0.00120413</v>
+        <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>0.00336837</v>
+        <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>4.74782485</v>
+        <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>0.85438425</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0.01301961</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
         <v>0</v>
@@ -12482,7 +12482,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>F-47</t>
+          <t>F-46</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -12519,16 +12519,16 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>0.01380778</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>0.00243865</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>0.00054191</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -12537,25 +12537,25 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>38.15971123</v>
+        <v>0</v>
       </c>
       <c r="T70" t="n">
         <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>0.00120413</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>0.00336837</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>4.74782485</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>0.85438425</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>0.01301961</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -12615,7 +12615,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>F-47T</t>
+          <t>F-47</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -12748,7 +12748,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>F-48</t>
+          <t>F-47T</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -12821,7 +12821,7 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0.01288942</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -12881,7 +12881,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>F-49</t>
+          <t>F-48</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -12918,16 +12918,16 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>0.01380778</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>0.00243865</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>0.00054191</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12936,25 +12936,25 @@
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>38.15971123</v>
       </c>
       <c r="T73" t="n">
         <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>0.00120413</v>
+        <v>0</v>
       </c>
       <c r="V73" t="n">
-        <v>0.00336837</v>
+        <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>4.74782485</v>
+        <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>0.85438425</v>
+        <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0.0001302</v>
+        <v>0.01288942</v>
       </c>
       <c r="Z73" t="n">
         <v>0</v>
@@ -13014,7 +13014,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>F-49A</t>
+          <t>F-49</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -13147,7 +13147,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>F-49B</t>
+          <t>F-49A</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -13184,16 +13184,16 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>0.01380778</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>0.00243865</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>0.00054191</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -13208,19 +13208,19 @@
         <v>0</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>0.00120413</v>
       </c>
       <c r="V75" t="n">
-        <v>0</v>
+        <v>0.00336837</v>
       </c>
       <c r="W75" t="n">
-        <v>0</v>
+        <v>4.74782485</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>0.85438425</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>0.0001302</v>
       </c>
       <c r="Z75" t="n">
         <v>0</v>
@@ -13280,7 +13280,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>F-5</t>
+          <t>F-49B</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -13329,16 +13329,16 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.106e-05</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>0.006234</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>8.9639284</v>
+        <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>0.46497694</v>
+        <v>0</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -13371,37 +13371,37 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0.81061497</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>0.00765862</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>0.00040357</v>
+        <v>0</v>
       </c>
       <c r="AH76" t="n">
-        <v>0.00032183</v>
+        <v>0</v>
       </c>
       <c r="AI76" t="n">
-        <v>0.00854456</v>
+        <v>0</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.00209422</v>
+        <v>0</v>
       </c>
       <c r="AK76" t="n">
-        <v>0.01255454</v>
+        <v>0</v>
       </c>
       <c r="AL76" t="n">
-        <v>0.00252991</v>
+        <v>0</v>
       </c>
       <c r="AM76" t="n">
-        <v>0.00036642</v>
+        <v>0</v>
       </c>
       <c r="AN76" t="n">
-        <v>0.00021248</v>
+        <v>0</v>
       </c>
       <c r="AO76" t="n">
-        <v>0.00313991</v>
+        <v>0</v>
       </c>
       <c r="AP76" t="n">
         <v>0</v>
@@ -13413,7 +13413,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>F-50A</t>
+          <t>F-5</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -13450,10 +13450,10 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>0.01380778</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>0.00243865</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -13462,31 +13462,31 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>1.106e-05</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>0.006234</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>8.9639284</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>0.46497694</v>
       </c>
       <c r="U77" t="n">
-        <v>0.00120413</v>
+        <v>0</v>
       </c>
       <c r="V77" t="n">
-        <v>0.00336837</v>
+        <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>4.74782485</v>
+        <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>0.85438425</v>
+        <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0.0001302</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
         <v>0</v>
@@ -13504,37 +13504,37 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>0.81061497</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>0.00765862</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>0.00040357</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>0.00032183</v>
       </c>
       <c r="AI77" t="n">
-        <v>0</v>
+        <v>0.00854456</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0</v>
+        <v>0.00209422</v>
       </c>
       <c r="AK77" t="n">
-        <v>0</v>
+        <v>0.01255454</v>
       </c>
       <c r="AL77" t="n">
-        <v>0</v>
+        <v>0.00252991</v>
       </c>
       <c r="AM77" t="n">
-        <v>0</v>
+        <v>0.00036642</v>
       </c>
       <c r="AN77" t="n">
-        <v>0</v>
+        <v>0.00021248</v>
       </c>
       <c r="AO77" t="n">
-        <v>0</v>
+        <v>0.00313991</v>
       </c>
       <c r="AP77" t="n">
         <v>0</v>
@@ -13546,7 +13546,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>F-50B</t>
+          <t>F-50A</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -13583,10 +13583,10 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>0.01380778</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>0.00243865</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -13607,19 +13607,19 @@
         <v>0</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>0.00120413</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>0.00336837</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>4.74782485</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>0.85438425</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>0.0001302</v>
       </c>
       <c r="Z78" t="n">
         <v>0</v>
@@ -13679,7 +13679,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>F-51A</t>
+          <t>F-50B</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -13812,7 +13812,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>F-51B</t>
+          <t>F-51A</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -13858,7 +13858,7 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>0.00108382</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13879,10 +13879,10 @@
         <v>0</v>
       </c>
       <c r="W80" t="n">
-        <v>0.00770595</v>
+        <v>0</v>
       </c>
       <c r="X80" t="n">
-        <v>0.00204842</v>
+        <v>0</v>
       </c>
       <c r="Y80" t="n">
         <v>0</v>
@@ -13945,7 +13945,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>F-52A</t>
+          <t>F-51B</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -13991,7 +13991,7 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>0.00108382</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -14012,10 +14012,10 @@
         <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>0.00770595</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>0.00204842</v>
       </c>
       <c r="Y81" t="n">
         <v>0</v>
@@ -14078,7 +14078,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>F-52B</t>
+          <t>F-52A</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -14145,10 +14145,10 @@
         <v>0</v>
       </c>
       <c r="W82" t="n">
-        <v>0.00770595</v>
+        <v>0</v>
       </c>
       <c r="X82" t="n">
-        <v>0.00204842</v>
+        <v>0</v>
       </c>
       <c r="Y82" t="n">
         <v>0</v>
@@ -14211,7 +14211,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>F-53</t>
+          <t>F-52B</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -14260,16 +14260,16 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.106e-05</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>0.006234</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>8.9639284</v>
+        <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>0.46497694</v>
+        <v>0</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -14278,10 +14278,10 @@
         <v>0</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>0.00770595</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>0.00204842</v>
       </c>
       <c r="Y83" t="n">
         <v>0</v>
@@ -14290,7 +14290,7 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>8.94e-05</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
         <v>0</v>
@@ -14302,37 +14302,37 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0.00081062</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>0.00055538</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
-        <v>3.625e-05</v>
+        <v>0</v>
       </c>
       <c r="AH83" t="n">
-        <v>0.00032183</v>
+        <v>0</v>
       </c>
       <c r="AI83" t="n">
-        <v>0.00854456</v>
+        <v>0</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0.00209422</v>
+        <v>0</v>
       </c>
       <c r="AK83" t="n">
-        <v>0.01255454</v>
+        <v>0</v>
       </c>
       <c r="AL83" t="n">
-        <v>0.00252991</v>
+        <v>0</v>
       </c>
       <c r="AM83" t="n">
-        <v>0.00036642</v>
+        <v>0</v>
       </c>
       <c r="AN83" t="n">
-        <v>0.00021248</v>
+        <v>0</v>
       </c>
       <c r="AO83" t="n">
-        <v>0.00203921</v>
+        <v>0</v>
       </c>
       <c r="AP83" t="n">
         <v>0</v>
@@ -14344,7 +14344,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>F-53PT</t>
+          <t>F-53</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -14477,7 +14477,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>F-54</t>
+          <t>F-53PT</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -14526,16 +14526,16 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>1.106e-05</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>0.006234</v>
       </c>
       <c r="S85" t="n">
-        <v>0</v>
+        <v>8.9639284</v>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>0.46497694</v>
       </c>
       <c r="U85" t="n">
         <v>0</v>
@@ -14556,7 +14556,7 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0.00212305</v>
+        <v>8.94e-05</v>
       </c>
       <c r="AB85" t="n">
         <v>0</v>
@@ -14568,37 +14568,37 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>0.00081062</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>0.00055538</v>
       </c>
       <c r="AG85" t="n">
-        <v>0</v>
+        <v>3.625e-05</v>
       </c>
       <c r="AH85" t="n">
-        <v>0</v>
+        <v>0.00032183</v>
       </c>
       <c r="AI85" t="n">
-        <v>0</v>
+        <v>0.00854456</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0</v>
+        <v>0.00209422</v>
       </c>
       <c r="AK85" t="n">
-        <v>0</v>
+        <v>0.01255454</v>
       </c>
       <c r="AL85" t="n">
-        <v>0</v>
+        <v>0.00252991</v>
       </c>
       <c r="AM85" t="n">
-        <v>0</v>
+        <v>0.00036642</v>
       </c>
       <c r="AN85" t="n">
-        <v>0</v>
+        <v>0.00021248</v>
       </c>
       <c r="AO85" t="n">
-        <v>0</v>
+        <v>0.00203921</v>
       </c>
       <c r="AP85" t="n">
         <v>0</v>
@@ -14610,7 +14610,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>F-55</t>
+          <t>F-54</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -14665,10 +14665,10 @@
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.86953481</v>
+        <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>0.00794096</v>
+        <v>0</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -14689,25 +14689,25 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.365e-05</v>
+        <v>0.00212305</v>
       </c>
       <c r="AB86" t="n">
         <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>0.00397048</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0.00202451</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>0.00710324</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>0.00036732</v>
+        <v>0</v>
       </c>
       <c r="AH86" t="n">
         <v>0</v>
@@ -14731,7 +14731,7 @@
         <v>0</v>
       </c>
       <c r="AO86" t="n">
-        <v>0.00022024</v>
+        <v>0</v>
       </c>
       <c r="AP86" t="n">
         <v>0</v>
@@ -14743,7 +14743,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>F-55PT</t>
+          <t>F-55</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -14876,7 +14876,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>F-56</t>
+          <t>F-55PT</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -14931,10 +14931,10 @@
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>0.86953481</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>0.00794096</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -14955,25 +14955,25 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0.00014821</v>
+        <v>2.365e-05</v>
       </c>
       <c r="AB88" t="n">
         <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>0.00397048</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>0.00202451</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>0.00710324</v>
       </c>
       <c r="AG88" t="n">
-        <v>0</v>
+        <v>0.00036732</v>
       </c>
       <c r="AH88" t="n">
         <v>0</v>
@@ -14997,7 +14997,7 @@
         <v>0</v>
       </c>
       <c r="AO88" t="n">
-        <v>0</v>
+        <v>0.00022024</v>
       </c>
       <c r="AP88" t="n">
         <v>0</v>
@@ -15009,7 +15009,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>F-57</t>
+          <t>F-56</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -15064,10 +15064,10 @@
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>22.00747215</v>
+        <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>0.00396602</v>
+        <v>0</v>
       </c>
       <c r="U89" t="n">
         <v>0</v>
@@ -15088,7 +15088,7 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>2.025e-05</v>
+        <v>0.00014821</v>
       </c>
       <c r="AB89" t="n">
         <v>0</v>
@@ -15100,7 +15100,7 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0.80777984</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>0</v>
       </c>
       <c r="AO89" t="n">
-        <v>0.00088043</v>
+        <v>0</v>
       </c>
       <c r="AP89" t="n">
         <v>0</v>
@@ -15142,7 +15142,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>F-57T</t>
+          <t>F-57</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -23664,7 +23664,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>F-2STP</t>
+          <t>F-2W</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -23719,10 +23719,10 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.69514162</v>
+        <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>0.30485838</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -23797,7 +23797,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>F-2W</t>
+          <t>F-2WM</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -23930,7 +23930,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>F-2WM</t>
+          <t>F-3</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -23967,16 +23967,16 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>0.01784584</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>0.00315183</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>0.00070039</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -23985,16 +23985,16 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>0.4059953</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>0.57230663</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
@@ -24063,7 +24063,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>F-3</t>
+          <t>F-30</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -24100,16 +24100,16 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.01784584</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0.00315183</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0.00070039</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -24118,22 +24118,22 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>0.6031885299999999</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>0.01731225</v>
       </c>
       <c r="U43" t="n">
-        <v>0.4059953</v>
+        <v>0.10579289</v>
       </c>
       <c r="V43" t="n">
-        <v>0.57230663</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>0.19533387</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>0.07837245</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>F-30</t>
+          <t>F-30P</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -24329,7 +24329,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>F-30P</t>
+          <t>F-30TP</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -24462,7 +24462,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>F-30TP</t>
+          <t>F-31</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -24517,22 +24517,22 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.6031885299999999</v>
+        <v>0.97209955</v>
       </c>
       <c r="T46" t="n">
-        <v>0.01731225</v>
+        <v>0.02790045</v>
       </c>
       <c r="U46" t="n">
-        <v>0.10579289</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0.19533387</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0.07837245</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
         <v>0</v>
@@ -24595,7 +24595,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>F-31</t>
+          <t>F-31P</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -24728,7 +24728,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>F-31P</t>
+          <t>F-32</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -24783,22 +24783,22 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.97209955</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>0.02790045</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>0.27876973</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>0.51471483</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>0.20651544</v>
       </c>
       <c r="Y48" t="n">
         <v>0</v>
@@ -24861,7 +24861,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>F-32</t>
+          <t>F-32P</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -24994,7 +24994,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>F-32P</t>
+          <t>F-35</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -25049,22 +25049,22 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>0.88852119</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>0.11147881</v>
       </c>
       <c r="U50" t="n">
-        <v>0.27876973</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>0.51471483</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0.20651544</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
         <v>0</v>
@@ -25127,7 +25127,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>F-35</t>
+          <t>F-36</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -25182,10 +25182,10 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.88852119</v>
+        <v>0.9148318</v>
       </c>
       <c r="T51" t="n">
-        <v>0.11147881</v>
+        <v>0.0851682</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -25260,7 +25260,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>F-36</t>
+          <t>F-36T</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -25393,7 +25393,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>F-36T</t>
+          <t>F-37</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -25448,10 +25448,10 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.9148318</v>
+        <v>1</v>
       </c>
       <c r="T53" t="n">
-        <v>0.0851682</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -25526,7 +25526,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>F-37</t>
+          <t>F-38</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -25581,10 +25581,10 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>0.55135622</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>0.44864378</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -25659,7 +25659,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>F-38</t>
+          <t>F-39</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -25714,10 +25714,10 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.55135622</v>
+        <v>1</v>
       </c>
       <c r="T55" t="n">
-        <v>0.44864378</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -25792,7 +25792,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>F-39</t>
+          <t>F-3P</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -25829,16 +25829,16 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>0.01784584</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>0.00315183</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>0.00070039</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -25847,16 +25847,16 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
         <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>0.4059953</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>0.57230663</v>
       </c>
       <c r="W56" t="n">
         <v>0</v>
@@ -25925,7 +25925,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>F-3T</t>
+          <t>F-3PT</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -27255,7 +27255,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>F-45</t>
+          <t>F-44T</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -27292,16 +27292,16 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>0.00239436</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>0.00042288</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>9.397e-05</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -27310,25 +27310,25 @@
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>0.0225769</v>
       </c>
       <c r="T67" t="n">
         <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>0.0002088</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>0.0005841</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>0.82330524</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>0.14815606</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>0.00225769</v>
       </c>
       <c r="Z67" t="n">
         <v>0</v>
@@ -27388,7 +27388,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>F-45R</t>
+          <t>F-45</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -27521,7 +27521,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>F-46</t>
+          <t>F-45R</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -27558,16 +27558,16 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>0.00244967</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>0.00043265</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>9.614e-05</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -27576,25 +27576,25 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T69" t="n">
         <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>0.00021363</v>
+        <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>0.0005975899999999999</v>
+        <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>0.84232226</v>
+        <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>0.15157823</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0.00230984</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
         <v>0</v>
@@ -27654,7 +27654,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>F-47</t>
+          <t>F-46</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -27691,16 +27691,16 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>0.00244967</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>0.00043265</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>9.614e-05</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -27709,25 +27709,25 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T70" t="n">
         <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>0.00021363</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>0.0005975899999999999</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>0.84232226</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>0.15157823</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>0.00230984</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -27787,7 +27787,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>F-47T</t>
+          <t>F-47</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -27920,7 +27920,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>F-48</t>
+          <t>F-47T</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -27975,7 +27975,7 @@
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0.99966234</v>
+        <v>1</v>
       </c>
       <c r="T72" t="n">
         <v>0</v>
@@ -27993,7 +27993,7 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0.00033766</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -28053,7 +28053,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>F-49</t>
+          <t>F-48</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -28090,16 +28090,16 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>0.00245528</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>0.00043364</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>9.636000000000001e-05</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -28108,25 +28108,25 @@
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>0.99966234</v>
       </c>
       <c r="T73" t="n">
         <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>0.00021412</v>
+        <v>0</v>
       </c>
       <c r="V73" t="n">
-        <v>0.0005989600000000001</v>
+        <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>0.8442528500000001</v>
+        <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>0.15192564</v>
+        <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.315e-05</v>
+        <v>0.00033766</v>
       </c>
       <c r="Z73" t="n">
         <v>0</v>
@@ -28186,7 +28186,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>F-49A</t>
+          <t>F-49</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -28319,7 +28319,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>F-49B</t>
+          <t>F-49A</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -28356,16 +28356,16 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>0.00245528</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>0.00043364</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>9.636000000000001e-05</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -28380,19 +28380,19 @@
         <v>0</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>0.00021412</v>
       </c>
       <c r="V75" t="n">
-        <v>0</v>
+        <v>0.0005989600000000001</v>
       </c>
       <c r="W75" t="n">
-        <v>0</v>
+        <v>0.8442528500000001</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>0.15192564</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>2.315e-05</v>
       </c>
       <c r="Z75" t="n">
         <v>0</v>
@@ -28452,7 +28452,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>F-5</t>
+          <t>F-49B</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -28501,16 +28501,16 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.08e-06</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>0.00060621</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.87167294</v>
+        <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>0.04521542</v>
+        <v>0</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -28543,37 +28543,37 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0.07882606</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>0.00074474</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>3.924e-05</v>
+        <v>0</v>
       </c>
       <c r="AH76" t="n">
-        <v>3.13e-05</v>
+        <v>0</v>
       </c>
       <c r="AI76" t="n">
-        <v>0.00083089</v>
+        <v>0</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.00020365</v>
+        <v>0</v>
       </c>
       <c r="AK76" t="n">
-        <v>0.00122083</v>
+        <v>0</v>
       </c>
       <c r="AL76" t="n">
-        <v>0.00024601</v>
+        <v>0</v>
       </c>
       <c r="AM76" t="n">
-        <v>3.563e-05</v>
+        <v>0</v>
       </c>
       <c r="AN76" t="n">
-        <v>2.066e-05</v>
+        <v>0</v>
       </c>
       <c r="AO76" t="n">
-        <v>0.00030533</v>
+        <v>0</v>
       </c>
       <c r="AP76" t="n">
         <v>0</v>
@@ -28585,7 +28585,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>F-50A</t>
+          <t>F-5</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -28622,10 +28622,10 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>0.00245552</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>0.00043368</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -28634,31 +28634,31 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>1.08e-06</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>0.00060621</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>0.87167294</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>0.04521542</v>
       </c>
       <c r="U77" t="n">
-        <v>0.00021414</v>
+        <v>0</v>
       </c>
       <c r="V77" t="n">
-        <v>0.00059902</v>
+        <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>0.84433421</v>
+        <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>0.15194028</v>
+        <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>2.315e-05</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
         <v>0</v>
@@ -28676,37 +28676,37 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>0.07882606</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>0.00074474</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>3.924e-05</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>3.13e-05</v>
       </c>
       <c r="AI77" t="n">
-        <v>0</v>
+        <v>0.00083089</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0</v>
+        <v>0.00020365</v>
       </c>
       <c r="AK77" t="n">
-        <v>0</v>
+        <v>0.00122083</v>
       </c>
       <c r="AL77" t="n">
-        <v>0</v>
+        <v>0.00024601</v>
       </c>
       <c r="AM77" t="n">
-        <v>0</v>
+        <v>3.563e-05</v>
       </c>
       <c r="AN77" t="n">
-        <v>0</v>
+        <v>2.066e-05</v>
       </c>
       <c r="AO77" t="n">
-        <v>0</v>
+        <v>0.00030533</v>
       </c>
       <c r="AP77" t="n">
         <v>0</v>
@@ -28718,7 +28718,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>F-50B</t>
+          <t>F-50A</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -28755,10 +28755,10 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>0.00245552</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>0.00043368</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -28779,19 +28779,19 @@
         <v>0</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>0.00021414</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>0.00059902</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>0.84433421</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>0.15194028</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>2.315e-05</v>
       </c>
       <c r="Z78" t="n">
         <v>0</v>
@@ -28851,7 +28851,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>F-51A</t>
+          <t>F-50B</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -28984,7 +28984,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>F-51B</t>
+          <t>F-51A</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -29030,7 +29030,7 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -29051,10 +29051,10 @@
         <v>0</v>
       </c>
       <c r="W80" t="n">
-        <v>0.711</v>
+        <v>0</v>
       </c>
       <c r="X80" t="n">
-        <v>0.189</v>
+        <v>0</v>
       </c>
       <c r="Y80" t="n">
         <v>0</v>
@@ -29117,7 +29117,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>F-52A</t>
+          <t>F-51B</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -29163,7 +29163,7 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -29184,10 +29184,10 @@
         <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>0.711</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>0.189</v>
       </c>
       <c r="Y81" t="n">
         <v>0</v>
@@ -29250,7 +29250,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>F-52B</t>
+          <t>F-52A</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -29317,10 +29317,10 @@
         <v>0</v>
       </c>
       <c r="W82" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="X82" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="Y82" t="n">
         <v>0</v>
@@ -29383,7 +29383,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>F-53</t>
+          <t>F-52B</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -29432,16 +29432,16 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.17e-06</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>0.00065862</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.94703004</v>
+        <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>0.04912435</v>
+        <v>0</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -29450,10 +29450,10 @@
         <v>0</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="Y83" t="n">
         <v>0</v>
@@ -29462,7 +29462,7 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>9.449999999999999e-06</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
         <v>0</v>
@@ -29474,37 +29474,37 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>8.564e-05</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>5.867e-05</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
-        <v>3.83e-06</v>
+        <v>0</v>
       </c>
       <c r="AH83" t="n">
-        <v>3.4e-05</v>
+        <v>0</v>
       </c>
       <c r="AI83" t="n">
-        <v>0.00090272</v>
+        <v>0</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0.00022125</v>
+        <v>0</v>
       </c>
       <c r="AK83" t="n">
-        <v>0.00132637</v>
+        <v>0</v>
       </c>
       <c r="AL83" t="n">
-        <v>0.00026728</v>
+        <v>0</v>
       </c>
       <c r="AM83" t="n">
-        <v>3.871e-05</v>
+        <v>0</v>
       </c>
       <c r="AN83" t="n">
-        <v>2.245e-05</v>
+        <v>0</v>
       </c>
       <c r="AO83" t="n">
-        <v>0.00021544</v>
+        <v>0</v>
       </c>
       <c r="AP83" t="n">
         <v>0</v>
@@ -29516,7 +29516,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>F-53PT</t>
+          <t>F-53</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -29649,7 +29649,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>F-54</t>
+          <t>F-53PT</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -29698,16 +29698,16 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>1.17e-06</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>0.00065862</v>
       </c>
       <c r="S85" t="n">
-        <v>0</v>
+        <v>0.94703004</v>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>0.04912435</v>
       </c>
       <c r="U85" t="n">
         <v>0</v>
@@ -29728,7 +29728,7 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1</v>
+        <v>9.449999999999999e-06</v>
       </c>
       <c r="AB85" t="n">
         <v>0</v>
@@ -29740,37 +29740,37 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>8.564e-05</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>5.867e-05</v>
       </c>
       <c r="AG85" t="n">
-        <v>0</v>
+        <v>3.83e-06</v>
       </c>
       <c r="AH85" t="n">
-        <v>0</v>
+        <v>3.4e-05</v>
       </c>
       <c r="AI85" t="n">
-        <v>0</v>
+        <v>0.00090272</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0</v>
+        <v>0.00022125</v>
       </c>
       <c r="AK85" t="n">
-        <v>0</v>
+        <v>0.00132637</v>
       </c>
       <c r="AL85" t="n">
-        <v>0</v>
+        <v>0.00026728</v>
       </c>
       <c r="AM85" t="n">
-        <v>0</v>
+        <v>3.871e-05</v>
       </c>
       <c r="AN85" t="n">
-        <v>0</v>
+        <v>2.245e-05</v>
       </c>
       <c r="AO85" t="n">
-        <v>0</v>
+        <v>0.00021544</v>
       </c>
       <c r="AP85" t="n">
         <v>0</v>
@@ -29782,7 +29782,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>F-55</t>
+          <t>F-54</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -29837,10 +29837,10 @@
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.97570606</v>
+        <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>0.00891056</v>
+        <v>0</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -29861,25 +29861,25 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.654e-05</v>
+        <v>1</v>
       </c>
       <c r="AB86" t="n">
         <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>0.00445528</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0.00227171</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>0.00797056</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>0.00041217</v>
+        <v>0</v>
       </c>
       <c r="AH86" t="n">
         <v>0</v>
@@ -29903,7 +29903,7 @@
         <v>0</v>
       </c>
       <c r="AO86" t="n">
-        <v>0.00024713</v>
+        <v>0</v>
       </c>
       <c r="AP86" t="n">
         <v>0</v>
@@ -29915,7 +29915,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>F-55PT</t>
+          <t>F-55</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -30048,7 +30048,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>F-56</t>
+          <t>F-55PT</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -30103,10 +30103,10 @@
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>0.97570606</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>0.00891056</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -30127,25 +30127,25 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1</v>
+        <v>2.654e-05</v>
       </c>
       <c r="AB88" t="n">
         <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>0.00445528</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>0.00227171</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>0.00797056</v>
       </c>
       <c r="AG88" t="n">
-        <v>0</v>
+        <v>0.00041217</v>
       </c>
       <c r="AH88" t="n">
         <v>0</v>
@@ -30169,7 +30169,7 @@
         <v>0</v>
       </c>
       <c r="AO88" t="n">
-        <v>0</v>
+        <v>0.00024713</v>
       </c>
       <c r="AP88" t="n">
         <v>0</v>
@@ -30181,7 +30181,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>F-57</t>
+          <t>F-56</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -30236,10 +30236,10 @@
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.96438903</v>
+        <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>0.0001738</v>
+        <v>0</v>
       </c>
       <c r="U89" t="n">
         <v>0</v>
@@ -30260,7 +30260,7 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>8.899999999999999e-07</v>
+        <v>1</v>
       </c>
       <c r="AB89" t="n">
         <v>0</v>
@@ -30272,7 +30272,7 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0.03539771</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
         <v>0</v>
@@ -30302,7 +30302,7 @@
         <v>0</v>
       </c>
       <c r="AO89" t="n">
-        <v>3.858e-05</v>
+        <v>0</v>
       </c>
       <c r="AP89" t="n">
         <v>0</v>
@@ -30314,7 +30314,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>F-57T</t>
+          <t>F-57</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -33646,22 +33646,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E101_AcidHeater</t>
+          <t>DS101_104_DissolverTrain</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>DissolutionReactor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>in=F-2SP</t>
+          <t>fuel=F-1, acid=F-2SP, cleaning_water=F-2B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>out=F-2STP</t>
+          <t>offgas=F-3, aq=F-5, solids=F-4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -33669,22 +33669,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DS101_104_DissolverTrain</t>
+          <t>C104_OffgasCompressor</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DissolutionReactor</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fuel=F-1, acid=F-2STP, cleaning_water=F-2B</t>
+          <t>in=F-3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>offgas=F-3, aq=F-5, solids=F-4</t>
+          <t>out=F-3P</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -33692,7 +33692,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E102_DissolverLiquorCooler</t>
+          <t>E117_DissolverOffgasCooler</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -33702,12 +33702,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>in=F-5</t>
+          <t>in=F-3P</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>out=F-5T</t>
+          <t>out=F-3PT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -33715,7 +33715,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V102_DissolverHold</t>
+          <t>V103_OffgasSurge</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -33725,12 +33725,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>in=F-5T</t>
+          <t>in=F-3PT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>out=F-6</t>
+          <t>out=F-63</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -33738,7 +33738,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P108_ToX101</t>
+          <t>P104_OffgasChokeValve</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -33748,12 +33748,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>in=F-6</t>
+          <t>in=F-63</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>out=F-6P</t>
+          <t>out=F-63P</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -33761,7 +33761,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E117_DissolverOffgasCooler</t>
+          <t>E102_DissolverLiquorCooler</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -33771,12 +33771,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>in=F-3</t>
+          <t>in=F-5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>out=F-3T</t>
+          <t>out=F-5T</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -33784,7 +33784,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V103_OffgasSurge</t>
+          <t>V102_DissolverHold</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -33794,12 +33794,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>in=F-3T</t>
+          <t>in=F-5T</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>out=F-63</t>
+          <t>out=F-6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -33807,7 +33807,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P104_OffgasBlower</t>
+          <t>P108_ToX101</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -33817,12 +33817,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>in=F-63</t>
+          <t>in=F-6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>out=F-63P</t>
+          <t>out=F-6P</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -34275,22 +34275,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>E107_UFeedHeater</t>
+          <t>E107_SteamCondensate</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>PassThrough</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>in=F-57</t>
+          <t>in=U67_src</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>out=F-57T</t>
+          <t>out=F-67</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -34298,22 +34298,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>E107_SteamCondensate</t>
+          <t>EV103A_UConcentrator1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PassThrough</t>
+          <t>SplitUnit</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>in=U67_src</t>
+          <t>in=F-57</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>out=F-67</t>
+          <t>vapour=F-65, to_raw=F-64_raw</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -34321,7 +34321,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EV103A_UConcentrator1</t>
+          <t>EV103A_InternalCleaner</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -34331,12 +34331,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>in=F-57T</t>
+          <t>in=F-64_raw</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>vapour=F-65, to_raw=F-64_raw</t>
+          <t>aux=F-64_aux, clean=F-64</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -34344,22 +34344,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>EV103A_InternalCleaner</t>
+          <t>EV103A_CondensatePass</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SplitUnit</t>
+          <t>PassThrough</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>in=F-64_raw</t>
+          <t>in=F-67</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>aux=F-64_aux, clean=F-64</t>
+          <t>out=F-69</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -34367,22 +34367,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>EV103A_CondensatePass</t>
+          <t>EV103B_UConcentrator2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PassThrough</t>
+          <t>SplitUnit</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>in=F-67</t>
+          <t>in=F-64</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>out=F-69</t>
+          <t>to_C1=F-66, to_C2=F-68</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -34390,22 +34390,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EV103B_UConcentrator2</t>
+          <t>EV103B_OverheadPass</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SplitUnit</t>
+          <t>PassThrough</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>in=F-64</t>
+          <t>in=F-65</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>to_C1=F-66, to_C2=F-68</t>
+          <t>out=F-72</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -34413,22 +34413,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EV103B_OverheadPass</t>
+          <t>EV103C_UConcentrator3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PassThrough</t>
+          <t>EV103CPerformanceStage</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>in=F-65</t>
+          <t>light=F-66, heavy=F-68, aux=F-64_aux</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>out=F-72</t>
+          <t>product=F-24, vapour=F-25, waste=F-70, sink=F-70_sink</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -34436,22 +34436,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EV103C_UConcentrator3</t>
+          <t>M272_EV103_WasteMixer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EV103CPerformanceStage</t>
+          <t>Mixer</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>light=F-66, heavy=F-68, aux=F-64_aux</t>
+          <t>a=F-69, b=F-72, c=F-70</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>product=F-24, vapour=F-25, waste=F-70, sink=F-70_sink</t>
+          <t>out=F-71</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -34459,22 +34459,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>M272_EV103_WasteMixer</t>
+          <t>P105_UProductPump</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>a=F-69, b=F-72, c=F-70</t>
+          <t>in=F-24</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>out=F-71</t>
+          <t>out=F-24P</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -34482,7 +34482,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>P105_UProductPump</t>
+          <t>E109_UProductHeater</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -34492,12 +34492,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>in=F-24</t>
+          <t>in=F-24P</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>out=F-24P</t>
+          <t>out=F-24PT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -34505,22 +34505,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>E109_UProductHeater</t>
+          <t>R101_ThermalReactor</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>CalcinerReactor</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>in=F-24P</t>
+          <t>in=F-24PT, air=F-73</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>out=F-24PT</t>
+          <t>solids=F-26, offgas=F-29</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -34528,22 +34528,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>R101_ThermalReactor</t>
+          <t>P106_ReactorOffgasBlower</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CalcinerReactor</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>in=F-24PT, air=F-73</t>
+          <t>in=F-29</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>solids=F-26, offgas=F-29</t>
+          <t>out=F-29P</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -34551,7 +34551,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>P106_ReactorOffgasBlower</t>
+          <t>E111_ReactorOffgasCooler</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -34561,12 +34561,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>in=F-29</t>
+          <t>in=F-29P</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>out=F-29P</t>
+          <t>out=F-29TP</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -34574,7 +34574,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>E111_ReactorOffgasCooler</t>
+          <t>E110_ProductCooler</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -34584,12 +34584,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>in=F-29P</t>
+          <t>in=F-26</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>out=F-29TP</t>
+          <t>out=F-26T</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -34597,22 +34597,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>E110_ProductCooler</t>
+          <t>K101_UProductSeparator</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>ConversionReactor</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>in=F-26</t>
+          <t>in=F-26T</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>out=F-26T</t>
+          <t>solid=F-27, gas=F-28, liquid=F-28</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -34620,22 +34620,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>K101_UProductSeparator</t>
+          <t>M301_HotVapourMixer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ConversionReactor</t>
+          <t>Mixer</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>in=F-26T</t>
+          <t>evaps=F-23TP, ucon=F-25, calc=F-29TP</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>solid=F-27, gas=F-28, liquid=F-28</t>
+          <t>out=F-30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -34643,22 +34643,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>M301_HotVapourMixer</t>
+          <t>P101_HotVapourBlower</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>evaps=F-23TP, ucon=F-25, calc=F-29TP</t>
+          <t>in=F-30</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>out=F-30</t>
+          <t>out=F-30P</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -34666,7 +34666,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>P101_HotVapourBlower</t>
+          <t>E112_HotVapourCooler</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -34676,12 +34676,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>in=F-30</t>
+          <t>in=F-30P</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>out=F-30P</t>
+          <t>out=F-30TP</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -34689,22 +34689,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>E112_HotVapourCooler</t>
+          <t>K301_Condenser</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>PhaseCondenser</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>in=F-30P</t>
+          <t>in=F-30TP</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>out=F-30TP</t>
+          <t>liquid=F-31, gas=F-32</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -34712,22 +34712,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>K301_Condenser</t>
+          <t>P103_CondensatePump</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PhaseCondenser</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>in=F-30TP</t>
+          <t>in=F-31</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>liquid=F-31, gas=F-32</t>
+          <t>out=F-31P</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -34735,7 +34735,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>P103_CondensatePump</t>
+          <t>P102_OffgasBlower</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -34745,12 +34745,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>in=F-31</t>
+          <t>in=F-32</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>out=F-31P</t>
+          <t>out=F-32P</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -34758,22 +34758,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>P102_OffgasBlower</t>
+          <t>M302_OffgasMixer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>Mixer</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>in=F-32</t>
+          <t>cond=F-32P, diss=F-63P, air=F-40</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>out=F-32P</t>
+          <t>out=F-41</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -34781,22 +34781,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>M302_OffgasMixer</t>
+          <t>E113_OffgasCooler</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>cond=F-32P, diss=F-63P, air=F-40</t>
+          <t>in=F-41</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>out=F-41</t>
+          <t>out=F-41T</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -34804,57 +34804,57 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>E113_OffgasCooler</t>
+          <t>D101_NO2_Absorber</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>NOxAbsorber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>in=F-41</t>
+          <t>gas=F-41T, water=F-39</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>out=F-41T</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+          <t>gas_out=F-42, aqueous=F-35</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>NO2_captured_mol_s=1.91; NO_captured_mol_s=1.026; HNO3_produced_mol_s=2.299</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>D101_NO2_Absorber</t>
+          <t>E115_SCRGasHeater</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NOxAbsorber</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>gas=F-41T, water=F-39</t>
+          <t>in=F-42</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>gas_out=F-42, aqueous=F-35</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>NO2_captured_mol_s=1.91; NO_captured_mol_s=1.026; HNO3_produced_mol_s=2.299</t>
-        </is>
-      </c>
+          <t>out=F-42T</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>E115_SCRGasHeater</t>
+          <t>E114_NH3Heater</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -34864,12 +34864,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>in=F-42</t>
+          <t>in=F-43</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>out=F-42T</t>
+          <t>out=F-43T</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -34877,22 +34877,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>E114_NH3Heater</t>
+          <t>M303_AcidMixer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>Mixer</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>in=F-43</t>
+          <t>abs=F-35, cond=F-31P</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>out=F-43T</t>
+          <t>out=F-36</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -34900,22 +34900,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>M303_AcidMixer</t>
+          <t>E118_AcidTrimHeater</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mixer</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>abs=F-35, cond=F-31P</t>
+          <t>in=F-36</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>out=F-36</t>
+          <t>out=F-36T</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -34923,102 +34923,102 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>E118_AcidTrimHeater</t>
+          <t>E104_HNO3_Concentrator</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Conditioner</t>
+          <t>AcidConcentrator</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>in=F-36</t>
+          <t>in=F-36T</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>out=F-36T</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
+          <t>concentrated=F-38, steam=F-37</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>H2O_evaporated_mol_s=24.39; HNO3_conc_mol_s=2.564; actual_HNO3_mass_frac=0.74</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>E104_HNO3_Concentrator</t>
+          <t>V104_AcidPurge</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AcidConcentrator</t>
+          <t>PurgeSplitter</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>in=F-36T</t>
+          <t>in=F-38</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>concentrated=F-38, steam=F-37</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>H2O_evaporated_mol_s=24.39; HNO3_conc_mol_s=2.564; actual_HNO3_mass_frac=0.74</t>
-        </is>
-      </c>
+          <t>purge=F-59, recycle=F-2R</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>V104_AcidPurge</t>
+          <t>R103_NOxReduction</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PurgeSplitter</t>
+          <t>SCRReactor</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>in=F-38</t>
+          <t>gas=F-42T, nh3=F-43T</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>purge=F-59, recycle=F-2R</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
+          <t>out=F-44</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>NO_removed_mol_s=0.05061; NO2_removed_mol_s=0.01809; NH3_consumed_mol_s=0.0868; N2_produced_mol_s=0.07775</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>R103_NOxReduction</t>
+          <t>E119_KOPreCooler</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SCRReactor</t>
+          <t>Conditioner</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>gas=F-42T, nh3=F-43T</t>
+          <t>in=F-44</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>out=F-44</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>NO_removed_mol_s=0.05061; NO2_removed_mol_s=0.01809; NH3_consumed_mol_s=0.0868; N2_produced_mol_s=0.07775</t>
-        </is>
-      </c>
+          <t>out=F-44T</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -35033,7 +35033,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>in=F-44</t>
+          <t>in=F-44T</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">

--- a/process_sim/results/stream_results.xlsx
+++ b/process_sim/results/stream_results.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F113"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>414</v>
+        <v>298.15</v>
       </c>
       <c r="C111" t="n">
         <v>100000</v>
@@ -3114,31 +3114,31 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>F-8</t>
+          <t>F-73T</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>298.15</v>
+        <v>475</v>
       </c>
       <c r="C112" t="n">
         <v>100000</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>8.814462000000001</v>
+        <v>4.17976</v>
       </c>
       <c r="F112" t="n">
-        <v>1849.908327</v>
+        <v>121.859939</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>F-9</t>
+          <t>F-8</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -3153,9 +3153,33 @@
         </is>
       </c>
       <c r="E113" t="n">
+        <v>8.814462000000001</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1849.908327</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>F-9</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>298.15</v>
+      </c>
+      <c r="C114" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
         <v>0.881446</v>
       </c>
-      <c r="F113" t="n">
+      <c r="F114" t="n">
         <v>16.463097</v>
       </c>
     </row>
@@ -3170,7 +3194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ113"/>
+  <dimension ref="A1:AQ114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -18068,7 +18092,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>F-8</t>
+          <t>F-73T</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -18135,10 +18159,10 @@
         <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>0</v>
+        <v>2.982937</v>
       </c>
       <c r="X112" t="n">
-        <v>0</v>
+        <v>1.196823</v>
       </c>
       <c r="Y112" t="n">
         <v>0</v>
@@ -18147,10 +18171,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.71857377</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>6.27751246</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -18159,13 +18183,13 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>0.80980442</v>
+        <v>0</v>
       </c>
       <c r="AF112" t="n">
-        <v>0.00710324</v>
+        <v>0</v>
       </c>
       <c r="AG112" t="n">
-        <v>0.00036732</v>
+        <v>0</v>
       </c>
       <c r="AH112" t="n">
         <v>0</v>
@@ -18189,7 +18213,7 @@
         <v>0</v>
       </c>
       <c r="AO112" t="n">
-        <v>0.00110122</v>
+        <v>0</v>
       </c>
       <c r="AP112" t="n">
         <v>0</v>
@@ -18201,133 +18225,266 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>F-8</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" t="n">
+        <v>0</v>
+      </c>
+      <c r="X113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>1.71857377</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>6.27751246</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>0.80980442</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>0.00710324</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>0.00036732</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>0.00110122</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>F-9</t>
         </is>
       </c>
-      <c r="B113" t="n">
-        <v>0</v>
-      </c>
-      <c r="C113" t="n">
-        <v>0</v>
-      </c>
-      <c r="D113" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" t="n">
-        <v>0</v>
-      </c>
-      <c r="M113" t="n">
-        <v>0</v>
-      </c>
-      <c r="N113" t="n">
-        <v>0</v>
-      </c>
-      <c r="O113" t="n">
-        <v>0</v>
-      </c>
-      <c r="P113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
-      <c r="R113" t="n">
-        <v>0</v>
-      </c>
-      <c r="S113" t="n">
+      <c r="B114" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="n">
         <v>0.86953481</v>
       </c>
-      <c r="T113" t="n">
+      <c r="T114" t="n">
         <v>0.00794096</v>
       </c>
-      <c r="U113" t="n">
-        <v>0</v>
-      </c>
-      <c r="V113" t="n">
-        <v>0</v>
-      </c>
-      <c r="W113" t="n">
-        <v>0</v>
-      </c>
-      <c r="X113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC113" t="n">
+      <c r="U114" t="n">
+        <v>0</v>
+      </c>
+      <c r="V114" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" t="n">
+        <v>0</v>
+      </c>
+      <c r="X114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC114" t="n">
         <v>0.00397048</v>
       </c>
-      <c r="AD113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ113" t="n">
+      <c r="AD114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ114" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18342,7 +18499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ113"/>
+  <dimension ref="A1:AQ114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -33240,7 +33397,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>F-8</t>
+          <t>F-73T</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -33307,10 +33464,10 @@
         <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>0</v>
+        <v>0.71366227</v>
       </c>
       <c r="X112" t="n">
-        <v>0</v>
+        <v>0.28633773</v>
       </c>
       <c r="Y112" t="n">
         <v>0</v>
@@ -33319,10 +33476,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0.19497205</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>0.71218324</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -33331,13 +33488,13 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>0.09187223999999999</v>
+        <v>0</v>
       </c>
       <c r="AF112" t="n">
-        <v>0.00080586</v>
+        <v>0</v>
       </c>
       <c r="AG112" t="n">
-        <v>4.167e-05</v>
+        <v>0</v>
       </c>
       <c r="AH112" t="n">
         <v>0</v>
@@ -33361,7 +33518,7 @@
         <v>0</v>
       </c>
       <c r="AO112" t="n">
-        <v>0.00012493</v>
+        <v>0</v>
       </c>
       <c r="AP112" t="n">
         <v>0</v>
@@ -33373,133 +33530,266 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>F-8</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" t="n">
+        <v>0</v>
+      </c>
+      <c r="X113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>0.19497205</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>0.71218324</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>0.09187223999999999</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>0.00080586</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>4.167e-05</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>0.00012493</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>F-9</t>
         </is>
       </c>
-      <c r="B113" t="n">
-        <v>0</v>
-      </c>
-      <c r="C113" t="n">
-        <v>0</v>
-      </c>
-      <c r="D113" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" t="n">
-        <v>0</v>
-      </c>
-      <c r="M113" t="n">
-        <v>0</v>
-      </c>
-      <c r="N113" t="n">
-        <v>0</v>
-      </c>
-      <c r="O113" t="n">
-        <v>0</v>
-      </c>
-      <c r="P113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
-      <c r="R113" t="n">
-        <v>0</v>
-      </c>
-      <c r="S113" t="n">
+      <c r="B114" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="n">
         <v>0.98648649</v>
       </c>
-      <c r="T113" t="n">
+      <c r="T114" t="n">
         <v>0.00900901</v>
       </c>
-      <c r="U113" t="n">
-        <v>0</v>
-      </c>
-      <c r="V113" t="n">
-        <v>0</v>
-      </c>
-      <c r="W113" t="n">
-        <v>0</v>
-      </c>
-      <c r="X113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC113" t="n">
+      <c r="U114" t="n">
+        <v>0</v>
+      </c>
+      <c r="V114" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" t="n">
+        <v>0</v>
+      </c>
+      <c r="X114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC114" t="n">
         <v>0.0045045</v>
       </c>
-      <c r="AD113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ113" t="n">
+      <c r="AD114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ114" t="n">
         <v>0</v>
       </c>
     </row>
@@ -34515,7 +34805,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>in=F-24PT, air=F-73</t>
+          <t>in=F-24PT, air=F-73T</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
